--- a/apps/web/.qa/e2e-journey/journey-20260903.xlsx
+++ b/apps/web/.qa/e2e-journey/journey-20260903.xlsx
@@ -35,7 +35,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -57,6 +57,16 @@
         <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE0B2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -70,13 +80,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -556,7 +569,6 @@
           <t>empty</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>空のデータベースで起動して壊れないことを見る</t>
@@ -574,15 +586,19 @@
           <t>500 や白画面にならず、各画面が 0 件の状態として表示される。API は空配列を返し、サーバのエラーログに例外が記録されない</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J00-01.png</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 500 や白画面にならず各画面が 0 件で表示 / 実測 (前提の「全テーブルを空にする」は本番 DB のため不可 → データ 0 件の新規アカウントで代替): 19 画面とも白画面ではなく 0 件表示だが、9/19 画面で画面が同時に叩く API のどれかが断続的に 500 (参照 ID 付き) を返す: [["/projects/dashboard", ["GET /me/consents 500"]], ["/employees", ["GET /ai-employees 500"]], ["/workflow", ["GET /approval-inbox?status=pending 500"]], ["/knowledge/review", ["GET /approval-inbox?status=pending 500"]], ["/meetings", ["GET /me/consents 500"]], ["/sales", ["GET /me 500"]], ["/chat", ["GET /me 500"]], ["/projects/settings", ["GET /approval-inbox?status=pending 500"]], ["/projects/vault", ["GET /me 500"]]]。同一 API は直列 30 回だと全 200、同時 10 本だと 1〜2 本が 500 (fly-request-id を証拠に記録)。サーバのエラーログは運営画面でしか見られず未観測</t>
         </is>
       </c>
     </row>
@@ -635,15 +651,19 @@
           <t>「メールまたはパスワードが違います」として断られ、存在の有無が応答に漏れない。監査ログに login_failed が記録される</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr"/>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J00-02.png</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>観測できた部分は期待どおり: 存在しないアカウント -&gt; 401「メールアドレスまたはパスワードが違います。」、存在するアカウント+誤パスワード -&gt; 401 同一文言 (存在の有無は応答に漏れない)、UI (S-A01) も同じ日本語の role=alert。監査ログ login_failed (実装名 auth.signin_failed) は /admin/audit-logs (運営) でしか読めず未観測 / 解除条件: 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -697,15 +717,19 @@
           <t>運営としてサインインでき、運営画面 (S-T01) に遷移する。DB の auth.users に role=admin が記録され、「認証はできるが権限が無い」で詰まらない</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="K4" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J00-03.png</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。一般利用者側の観察: owner で /admin と /admin/s_t01 を開くと URL はそのままで「この画面は運営専用です (ACCESS DENIED)」に差し替わり、運営メニューは描画されず /admin API も叩かれない (GAP-219 の門は機能)</t>
         </is>
       </c>
     </row>
@@ -760,15 +784,19 @@
           <t>手動補正なしでサインインが成立し、プロジェクト一覧に遷移する。seed が必須項目 (パスワード等) をDB に残している</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#SETUP</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>場所=cloud / seed 済み DB では原理的に出ないバグ</t>
+          <t>「全テーブルを空にして seed のみ実行」は本番 DB では不可 / 解除条件: 使い捨ての staging DB (ADR-021 案 A) と seed 実行権限</t>
         </is>
       </c>
     </row>
@@ -823,15 +851,19 @@
           <t>その種類の版 v1 が 1 つ生まれ、一覧 (GET /admin/design-templates) に最新版として出る。プレビューに生成した HTML が反映される</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="K6" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行 + 場所=mac (Bridge + 本人の Claude 契約で AI が動く) / 解除条件: Mac の Bridge ハーネス。観察: owner で GET /admin/design-templates -&gt; 403。GET /workspaces/{ws}/design-templates は {"data":[]} = 運営既定が本番に 1 件も無い</t>
         </is>
       </c>
     </row>
@@ -884,15 +916,19 @@
           <t>新版 v2 が積まれ、一覧の最新版が v2 に切り替わる。v1 は版履歴 (GET …/versions) に消えず残る</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+      <c r="K7" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行 + 場所=mac (Bridge + 本人の Claude 契約で AI が動く) / 解除条件: Mac の Bridge ハーネス</t>
         </is>
       </c>
     </row>
@@ -946,15 +982,19 @@
           <t>署名付き URL (GET /design-templates/{id}/content-url) で最新版の HTML がプレビューに反映される。期限切れの URL は拒否され、再取得で復旧する</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#J01-04</t>
+        </is>
+      </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/design-templates/estimate/versions -&gt; 403 (owner)。署名付き URL は GET /design-templates/{id}/content-url -&gt; 404 (運営既定が存在しないため id が無い)。期限切れ URL の拒否は未観測</t>
         </is>
       </c>
     </row>
@@ -1008,15 +1048,19 @@
           <t>運営固定 10 名のテンプレが一覧に出る。展開先 (GET …/deployment) に実際に複製されているワークスペース数が記録されている</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: owner で GET /admin/ai-employee-templates -&gt; 403、…/deployment -&gt; 403。利用者向け GET /ai-employees/templates は 200 で運営固定 10 名 (jarvis〜tchalla) が返る (※この利用者向け応答に system_prompt 本文が含まれる — 報告の追加観点参照)</t>
         </is>
       </c>
     </row>
@@ -1070,15 +1114,19 @@
           <t>保存で version が 1 増え、展開先の全ワークスペースの AI 社員に反映される (展開先カウントと一致)。監査ログに記録される</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: PATCH /admin/ai-employee-templates/{id} (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -1131,15 +1179,19 @@
           <t>日本語のエラーで拒否され、DB の版は増えない</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: owner の不正 tone 送信は 403 (検証より先に運営判定)</t>
         </is>
       </c>
     </row>
@@ -1192,15 +1244,19 @@
           <t>スキルが一覧に出て、版 1 として記録される。監査ログに記録される</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>場所=cloud / 「整備済みを確認」で済ませず実際に 1 件回す</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: POST /admin/skills (owner, 正しい body) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -1253,15 +1309,19 @@
           <t>編集内容が一覧と詳細に反映され、版が増える</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: PATCH /admin/skills/{id} (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -1314,15 +1374,19 @@
           <t>装着状態が一覧に反映される。利用者側 (S-C02) では「できること」に変換されて出る。監査ログ skill_attached が記録される</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: POST /admin/skills/{id}/attach (owner, body {employee_id}) -&gt; 422 (422 = 運営判定の前に body 検証が走り、一般利用者にスキーマ形状が漏れる。拒否自体は保たれる)</t>
         </is>
       </c>
     </row>
@@ -1375,15 +1439,19 @@
           <t>解除が一覧に反映され、利用者側の「できること」から消える。監査ログ skill_detached が記録される</t>
         </is>
       </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行</t>
         </is>
       </c>
     </row>
@@ -1436,15 +1504,19 @@
           <t>取り込まれた件数が一覧に反映される。同名は重複せず更新として記録される</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: POST /admin/skills/reimport (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -1497,15 +1569,19 @@
           <t>一覧から消え、再読み込みしても復活しない。装着していた AI 社員の「できること」からも消えた状態になる</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr"/>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: DELETE /admin/skills/{id} (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -1560,15 +1636,19 @@
           <t>現行が 1 件だけの状態になる。旧版は消えず残り、公開 API (GET /public/legal-documents/{type}) が新版を返す</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#J03</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>場所=cloud / 順序を誤ると一意制約で失敗する</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察 (公開 API 側): GET /public/legal-documents と /{type} が 5 URL とも 500 (参照 ID 付き)。認証付き GET /me/consents は legal_documents の現行版 2026-08-22 を返すので、表は存在し anon 経路だけが壊れている</t>
         </is>
       </c>
     </row>
@@ -1621,15 +1701,19 @@
           <t>改訂した内容がそのまま反映されて読める。ダミーの連絡先や存在しないプランが残っていない</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J03-02.png</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 改訂内容がそのまま読める・ダミー連絡先や存在しないプランが残っていない / 実測: 3 ページとも本文が出ず role=alert「文書の取得に失敗しました。時間をおいて再度お試しください。」(画面が叩く GET /public/legal-documents/{type} が全て 500・参照 ID 付き)。認証付き経路 GET /me/consents では legal_documents 2026-08-22 版が読めるので、anon 経路 (set local role anon) 固有の障害 = G-11 (本番 DB の anon ロール/権限) の疑い。文面の内容 (ダミー連絡先の有無) は本文が出ないため未判定</t>
         </is>
       </c>
     </row>
@@ -1682,15 +1766,19 @@
           <t>一意制約で拒否され、現行が 2 件の状態は DB に残らない。画面に日本語で理由が出る</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#J03</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行 (一意制約 legal_documents_current_uidx の実挙動は運営の書き込みが要る)</t>
         </is>
       </c>
     </row>
@@ -1744,15 +1832,19 @@
           <t>3 種 (規約/プライバシー/特商法) が版番号つきで一覧に出て、未サインインで読める</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J03-04.png</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 3 種が版番号つきで一覧に出て未サインインで読める / 実測: GET /public/legal-documents -&gt; 500 サーバー側で問題が発生しました。時間をおいて、もう一度お試しください。（参照 ID: fcf2c584-cb32-4a60-8070-ccc279f3dcc7）; 画面 /terms (S-A01 新規登録タブの「利用規約」リンクから到達) は role=alert「文書の取得に失敗しました。時間をおいて再度お試しください。|利用規約 | Atelier | Atelier」で本文が出ない (画面が叩いた GET /public/legal-documents/terms_of_service -&gt; 500). 版番号=false</t>
         </is>
       </c>
     </row>
@@ -1809,15 +1901,19 @@
           <t>各ケースで日本語のエラーが出て送信されない (DB のユーザーが増えない)。英語の既定メッセージが出ない</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J10-01.png</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-210</t>
+          <t>5 ケース全て日本語エラー表示・POST /auth/signup 未送信 (英語の既定メッセージ無し): 未入力=メール形式で入力してください|パスワードは 8 文字以上|パスワード確認を入力してください|利用規約とプライバシーポリシーへの同意が必要です / 不正メール=メール形式で入力してください / 7文字パスワード=パスワードは 8 文字以上|パスワード確認を入力してください / 確認不一致=パスワード確認が一致しません / 同意なし=利用規約とプライバシーポリシーへの同意が必要です</t>
         </is>
       </c>
     </row>
@@ -1870,15 +1966,19 @@
           <t>サーバーが 4xx で拒否し、ユーザーも同意記録も DB に作られない。画面だけの防御になっていない</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J10-02</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>consents=[] → 422, accepted=false ×2 → 422, 片方のみ → 422 (全 4xx)。同メールで signin → 401 = ユーザー未作成 (同意記録も当然無し)。画面だけの防御ではない</t>
         </is>
       </c>
     </row>
@@ -1933,15 +2033,19 @@
           <t>登録が通り、サインイン画面から抜けて中の画面に遷移する。DB に users 行が作られ、HTTP-only cookie で JWT が発行されている</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J10-03.png</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: HTTP-only cookie で JWT 発行 / 実測: 登録は通り /projects へ遷移し GET /me 200 (id=f5e91e52-a38b-4531-a7fa-61f754609b9f) だが、cookie atelier_access は httpOnly=false (document.cookie で JS から設定・読み取り可能 = XSS で窃取可能)。secure=false</t>
         </is>
       </c>
     </row>
@@ -1995,15 +2099,19 @@
           <t>記録された版が現行版と一致する。登録日など別の値になっていない</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J10-04</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-210</t>
+          <t>GET /me/consents: privacy_policy: 記録版 2026-08-22 = 現行版 2026-08-22 / terms_of_service: 記録版 2026-08-22 = 現行版 2026-08-22 (登録日 2026-09-03 ではない・再同意不要)</t>
         </is>
       </c>
     </row>
@@ -2056,15 +2164,19 @@
           <t>サイドバー・検索・通知など押しても何も起きない導線が出ていない。ワークスペース作成の導線だけが出ている状態である</t>
         </is>
       </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J10-05.png</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-207</t>
+          <t>サイドバーのナビ 0 件・検索 0・通知 0、出ている導線は ["ワークスペースを作成"] のみ (その他ボタン: メインコンテンツへスキップ,アカウント: qa-jA-20260903-1,ワークスペースを作成)</t>
         </is>
       </c>
     </row>
@@ -2117,15 +2229,19 @@
           <t>再読み込みせずにサイドバーとワークスペース名に反映される。既定の AI 社員 10 名が複製され、監査ログ workspace_created が記録される</t>
         </is>
       </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J10-06.png</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-207</t>
+          <t>観測できた部分は全て期待どおり: 再読み込みなしでサイドバー (6 項目) と WS 名「QA jA WS1」が反映、GET /workspaces 1 件、AI 社員 10 名複製。監査ログ workspace_created は /admin/audit-logs (運営) でしか読めず未観測 / 解除条件: 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -2178,15 +2294,19 @@
           <t>日本語のエラーで拒否され、ワークスペースは増えない</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J10-07.png</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 日本語エラーで拒否・WS 増えない / 実測: errors=[] native={"noValidate":false,"vm":"","req":false} POST= WS 件数=0</t>
         </is>
       </c>
     </row>
@@ -2239,15 +2359,19 @@
           <t>0 件の案内と新規作成の導線が出る状態になる。エラーや白画面にならない</t>
         </is>
       </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J10-08.png</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>0 件の案内「0 件のアクティブプロジェクト」と新規作成導線 (1) が出る。白画面・エラー無し</t>
         </is>
       </c>
     </row>
@@ -2301,15 +2425,19 @@
           <t>利用者側 API は能力に変換された名前だけを返し、スキル本文が応答に含まれない状態である。画面側 JS にも含まれない</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J02-10.png</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T06</t>
+          <t>GET /skills (owner, active_only=false) は 23 件とも id/name/version/description/is_active のみで本文系キー無し。S-C02 (jarvis) の「できること」は task-management / weekly-review の能力名だけ。S-C02 が受けた API 応答 9 件に content_md/SKILL.md 無し。配布 JS 29 本を検査: 'content_md' の一致はナレッジ画面の API フィールド名 (POST /knowledge body) のみで、SKILL.md 本文・frontmatter・スキル名の長文は含まれない</t>
         </is>
       </c>
     </row>
@@ -2363,15 +2491,19 @@
           <t>API は 403 で拒否され、画面は access-denied に遷移する。監査ログに拒否が記録される</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J02-11.png</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>観測できた部分は期待どおり: GET /admin/skills (owner) -&gt; 403「この操作は運営のみが行えます。」、/admin/s_t02 → /admin/skills に 308 後 URL のまま access-denied (「この画面は運営専用です」) に差し替え。「監査ログに拒否が記録される」は運営 API でしか読めず未観測 (実装上 _require_admin は HTTPException を投げるだけで監査書き込みが無い) / 解除条件: 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -2425,15 +2557,19 @@
           <t>サインイン画面に遷移し、cookie と手元の文脈が消える。監査ログ logout が記録される</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr"/>
+      <c r="K32" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J11-01.png</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-209</t>
+          <t>観測できた部分は全て期待どおり: アバター→サインアウトで /signin へ遷移、cookie atelier_access 消去、localStorage の atelier_* (atelier_current_project,atelier_current_workspace) 消去、POST /auth/signout 204。監査ログ logout は /admin/audit-logs (運営) でしか読めず未観測 (実装は auth.refresh.revoked_all を書く) / 解除条件: 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -2487,15 +2623,19 @@
           <t>サインインへ遷移させられる。古い更新用トークンも通らない (この人の refresh token が全部失効した状態)</t>
         </is>
       </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J11-02.png</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-209</t>
+          <t>/projects 直開き → /signin?redirect=%2Fprojects (サインインへ遷移)。更新用トークン: パスワード signin は refresh_token=null を返し発行しない (Magic Link 経路のみ発行) ため「失効した refresh token」は存在しない = 全失効状態。※観点候補 (G-14): サインアウト前に発行済の access JWT (有効 1h・stateless) は GET /me → 200 で残効</t>
         </is>
       </c>
     </row>
@@ -2549,15 +2689,19 @@
           <t>作ったワークスペースと案件が残っている。サイドバーの現在のワークスペースが復元されて反映される</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr"/>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J11-03.png</t>
+        </is>
+      </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>同じメール/パスワードで再サインイン → /projects。WS「QA jA2 WS1」(サイドバーに現在 WS として復元 localStorage=true) と案件「QA jA2 案件1 Nebula」が残っている (API: WS 1 件 / 案件 1 件)</t>
         </is>
       </c>
     </row>
@@ -2611,15 +2755,19 @@
           <t>「更新しました。同意をお願いします」の帯が出る。GET /me/consents が再同意要の状態を返す</t>
         </is>
       </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J12-01.png</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-206</t>
+          <t>「現行版を新しくする」は法務文書の版更新 (運営/DB 操作) で本番では実行不可。観測できた部分: 現行版に同意済の状態は needs_consent=false で帯は出ない (正)、現行でない版の同意 POST は 409 で拒否 / 解除条件: staging で legal_documents に新版を投入できる運営操作</t>
         </is>
       </c>
     </row>
@@ -2673,15 +2821,19 @@
           <t>帯が消え、再読み込みしても出ない。旧版の記録は消えず新版の同意記録が増える</t>
         </is>
       </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J12-01.png</t>
+        </is>
+      </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-206</t>
+          <t>J12-01 (新版投入) が BLOCKED のため帯が出せず未実行 / 解除条件: J12-01 と同じ</t>
         </is>
       </c>
     </row>
@@ -2735,15 +2887,19 @@
           <t>同意していない状態のまま (DB に新版の同意記録が増えない)。次のサインインで帯がまた出る</t>
         </is>
       </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
+      <c r="K37" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J12-01.png</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>J12-01 (新版投入) が BLOCKED のため帯が出せず未実行 / 解除条件: J12-01 と同じ</t>
         </is>
       </c>
     </row>
@@ -2797,15 +2953,19 @@
           <t>再設定用のメールが届く (実送信できない環境では送信ログ/キュー投入で代替)。新しいパスワードでサインインでき、古いパスワードでは入れない状態になる。監査ログ password_reset が記録される</t>
         </is>
       </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
+      <c r="K38" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J13-01</t>
+        </is>
+      </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>受信箱なし: 再設定トークンはメール本文にしか無く、送信ログ (Resend / fly logs) にも到達できない。観測できた部分: POST /auth/password-reset/request 登録済=202 未登録=202 (応答同一・存在は漏れない)、偽トークンの confirm は 401 で拒否 / 解除条件: QA 用受信箱 or Resend 送信ログ閲覧権限</t>
         </is>
       </c>
     </row>
@@ -2858,15 +3018,19 @@
           <t>通らない (401 に遷移)。パスワードを変えたのに古いセッションが生き続けない</t>
         </is>
       </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr"/>
+      <c r="K39" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J13-01</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-209 で見つけた回帰</t>
+          <t>J13-01 (再設定の完了) が BLOCKED のため未実行。※同じ失効機構 (auth.refresh.revoked_all) はサインアウト経路で J11-02 として PASS 実測済 / 解除条件: J13-01 と同じ</t>
         </is>
       </c>
     </row>
@@ -2920,15 +3084,19 @@
           <t>5 回目以降は 15 分間ロックされ、正しいパスワードでも入れない状態になる。監査ログに login_failed が 5 件記録され、存在の有無は漏れない</t>
         </is>
       </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J13-03</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>誤パスワードを累計 5 回 (401「メールアドレスまたはパスワードが違います。」= 未登録メールの応答と同一で存在は漏れない) の後、正しいパスワードでも 429「サインインの失敗が続いたため、一時的に受け付けを止めています。しばらく時間をおいてからお試しください。」でロック。ロック判定は audit_logs の auth.signin_failed を直近 15 分で数える実装のため、ロックが効いた事実 = login_failed 5 件が記録された証拠 (rate_limited 「短い間に…」とは別文言)</t>
         </is>
       </c>
     </row>
@@ -2982,15 +3150,19 @@
           <t>env が設定済みのプロバイダだけボタンが出る。未設定のものは表示されない状態 (死にボタンなし)</t>
         </is>
       </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J14-01.png</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>GET /auth/oauth/providers = [] (env 未設定) で、S-A01 に Google/GitHub 等のボタンは 0 個。死にボタン無し</t>
         </is>
       </c>
     </row>
@@ -3044,15 +3216,19 @@
           <t>認可後に oauth-complete に戻り、JWT が発行されてプロジェクト一覧に遷移する。監査ログ oauth_link が記録され、外部アカウントと紐づいた状態になる</t>
         </is>
       </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J14-02</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>OAuth プロバイダ未設定 (GET /auth/oauth/providers = [], /auth/oauth/google/start → 503, /auth/oauth/github/redirect-url → 200)。プロバイダ側の認可画面に到達できない / 解除条件: 本番 env に Google/GitHub の client_id/secret を設定</t>
         </is>
       </c>
     </row>
@@ -3106,15 +3282,19 @@
           <t>エラー画面に遷移し、日本語で理由が出る。アカウントは作られない (DB に増えない)</t>
         </is>
       </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J14-03.png</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>プロバイダ未設定でキャンセル操作自体ができない。観測できた部分: callback が拒否時に返す /auth/oauth-complete?error=access_denied を直接開くと日本語の理由 ["サインインできませんでした","プロバイダでの認可がキャンセルされました。もう一度お試しいただくか、メールアドレスでサインインしてください。"] が出る / 解除条件: J14-02 と同じ</t>
         </is>
       </c>
     </row>
@@ -3168,15 +3348,19 @@
           <t>登録済みのメールにはリンクが届く (実送信できない環境では送信ログ/キュー投入で代替)。存在しないメールでも同じ応答で、存在の有無が漏れない</t>
         </is>
       </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr"/>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J14-04</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>受信箱なし: リンク到達 (送信ログ/キュー) を確認する手段が無い。観測できた部分: 登録済 202 / 未登録 202 で応答同一 (true) = 存在の有無は漏れない / 解除条件: QA 用受信箱 or Resend 送信ログ閲覧権限</t>
         </is>
       </c>
     </row>
@@ -3230,15 +3414,19 @@
           <t>1 回目でサインイン状態になりプロジェクト一覧に遷移する。同じリンクの 2 回目は拒否される</t>
         </is>
       </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr"/>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J14-05.png</t>
+        </is>
+      </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>リンクを受信できないため未実行。観測できた部分: 偽トークンの verify は API 401 で拒否、画面は /auth/magic-link/verify?email=qa-jA2-20260903-1%40example.com&amp;token=bogus-magic-token / 解除条件: J14-04 と同じ</t>
         </is>
       </c>
     </row>
@@ -3293,15 +3481,19 @@
           <t>初回だけ 3 ステップのウォークスルーが出る。完了すると次回から出ない状態が記録される</t>
         </is>
       </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr"/>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-01.png</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 登録直後に 3 ステップのウォークスルーが出て、完了すると次回から出ない状態が記録される / 実測: 登録直後は /projects に着地しウォークスルーは出ない (sawWalk=false)。/t-uc-35 を直接開くと 3 ステップ (ようこそ Atelier へ→ワークスペースを作成→プロジェクトを始める) は進めるが「完了」ボタンは無く (最終: 戻る,次へ(disabled))、再読み込みすると先頭「ようこそ Atelier へ」に戻る。完了状態の記録 (API 呼び出し/localStorage) は無し</t>
         </is>
       </c>
     </row>
@@ -3354,15 +3546,19 @@
           <t>保存後にヘッダーの表示名に反映され、再読み込みしても残る。監査ログに記録される</t>
         </is>
       </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr"/>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-03.png</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 保存後にヘッダーの表示名に反映され、再読み込みしても残る / 実測: PATCH /me 200 で保存は成功し GET /me・再読み込み後の入力値/ヘッダーは「QA jA2 改名太郎」だが、保存直後 (再読み込み前) のヘッダーは旧名「アカウント: QA jA2 1」のまま (G-12: 切替直後に反映されない)。監査ログは未観測</t>
         </is>
       </c>
     </row>
@@ -3415,15 +3611,19 @@
           <t>日本語のエラーで拒否され、DB の表示名は変わらない</t>
         </is>
       </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-04.png</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>日本語エラー ["入力必須"] で拒否 (画面 PATCH=未送信)、API 直接でも 422、GET /me の表示名は「QA jA2 改名太郎」のまま</t>
         </is>
       </c>
     </row>
@@ -3478,15 +3678,19 @@
           <t>選んだワークスペースが現在のワークスペースとして反映され、案件一覧がそのワークスペースのものに切り替わる。再読み込み後も残る</t>
         </is>
       </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-05.png</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 選んだ WS が現在 WS になり、案件一覧がその WS のものに切り替わる / 実測: t-uc-38 で WS2 を選ぶとヘッダーの現在 WS は「QA jA2 WS2」になり localStorage も WS2 で再読み込み後も残る (正) が、/projects の一覧は GET /projects?limit=20 (workspace_id 無し) を叩き「3 件のアクティブプロジェクト」= WS1 の Nebula/Sirius + WS2 の Vega を全部出す = 案件一覧が WS に切り替わらない。加えてヘッダーの現在プロジェクトは WS1 の Nebula のまま (G-13: WS 切替 × 現在案件の組み合わせ)</t>
         </is>
       </c>
     </row>
@@ -3540,15 +3744,19 @@
           <t>一覧に出て開ける。DB に ai_training_optout=true (学習しない) で作られ、監査ログ project_created が記録される</t>
         </is>
       </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>一覧に出る=True, GET /projects/{id} ai_learning_opt_out=True, dashboard.recent_activities=['workflow.phases.seed', 'project.create'] (監査 action 名は project.create 系)</t>
         </is>
       </c>
     </row>
@@ -3601,15 +3809,19 @@
           <t>9 工程が並び、先頭が進行中の状態になっている (GET /workflow/phases と一致)</t>
         </is>
       </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J30-02.png</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>API /workflow/phases: 9 工程, 先頭=["ヒアリング","in_progress"]; S-F01 画面に 9/9 工程名が出る, 進行中表記=true</t>
         </is>
       </c>
     </row>
@@ -3662,15 +3874,19 @@
           <t>次の工程が進行中に遷移し、前の工程が完了になる。画面と DB の両方で一致し、監査ログ stage_completed が記録される</t>
         </is>
       </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>再取得: hearing=('done', False), proposal=('pending', True) (次工程が current)。監査 recent_activities に project.flow.complete あり=True。※監査 action 名は 'stage_completed' ではなく 'project.flow.complete'。画面側は別途 Playwright で確認</t>
         </is>
       </c>
     </row>
@@ -3723,15 +3939,19 @@
           <t>変えられないか、変えるには明示の操作が要る。黙って書き換わらない (DB の状態が変わらない)</t>
         </is>
       </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>done 工程へ complete 再送 -&gt; 409 'この工程はすでに完了しています。', skip -&gt; 409; 再取得で completed_at 不変。変更は明示の reopen 操作のみ (J30-08)</t>
         </is>
       </c>
     </row>
@@ -3785,15 +4005,19 @@
           <t>各カードが実データと一致して反映される。承認待ちの件数は GET /approval-inbox の件数と同じ</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J30-05.png</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>S-B02: 承認待ち 0 (GET /approval-inbox と一致=true), 未解決コメント 1 (一致=true), 最新成果物「要件定義書v2」表示=true, 工程進捗 2/10 表示=false; API task_counts={"triage":2,"ready":0,"in_progress":0,"blocked":0,"awaiting":0,"done":0,"total":2}</t>
         </is>
       </c>
     </row>
@@ -3846,15 +4070,19 @@
           <t>成果物 0 件・承認待ち 0 件でも各カードが 0 件の状態として出る。エラーにならない</t>
         </is>
       </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J30-06.png</t>
+        </is>
+      </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>S-B02 空案件: 全体進捗 0% (工程 0/9)・未承認 INBOX 0 (すべて処理済み)・今日の活動 0・未解決コメント 0・最新成果物「成果物はまだありません」・活動「まだ活動がありません」が 0 件状態として描画。生エラー無し, JS エラー 0, API 4xx/5xx 0 (API dashboard/inbox/outputs も全部 0)</t>
         </is>
       </c>
     </row>
@@ -3909,15 +4137,19 @@
           <t>理由なしは拒否される。理由を入れると skipped に遷移し、理由が記録される</t>
         </is>
       </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>理由空 -&gt; 422 (拒否), 理由あり -&gt; 200; 再取得 proposal=('skipped', '提案は口頭で合意済みのため省略')</t>
         </is>
       </c>
     </row>
@@ -3970,15 +4202,19 @@
           <t>done/skipped から pending に遷移し、監査ログに記録される</t>
         </is>
       </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>reopen 後 proposal=('pending', None); 監査 recent_activities に project.flow.reopen=True</t>
         </is>
       </c>
     </row>
@@ -4032,15 +4268,19 @@
           <t>確認なしは拒否され状態が変わらない。確認つきで done に遷移する</t>
         </is>
       </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>確認なし -&gt; 403 (この工程は重要な確認が必要です。内容をご確認のうえ承認してください。) 状態=pending; 確認つき -&gt; 200 状態=done</t>
         </is>
       </c>
     </row>
@@ -4093,15 +4333,19 @@
           <t>未完了工程・タスク・未解決コメントの実数が出る。0 でない間は確定できない状態である</t>
         </is>
       </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr"/>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J30-10.png</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>実数表示=true (未完了工程 8 / タスク 2 / 未解決コメント 1 が UI 確認事項と API freeze-check で一致) ; しかし「0 でない間は確定できない」は不成立: UI の確定ボタンは enabled=true、API も残件ありで confirm=true → 200 (捨て案件でフェーズ1 frozen/フェーズ2 active に遷移)</t>
         </is>
       </c>
     </row>
@@ -4155,15 +4399,19 @@
           <t>成果物が凍結され、次フェーズが開始状態に遷移する。凍結後の成果物は編集不可の状態になる</t>
         </is>
       </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>未完了工程 8→0・タスク 2→done に処理 (未解決コメントは member 作成分を owner が resolve できず 403 で 1 件残る — 正本に足すべき観点)。freeze confirm なし 403 / confirm あり 200 → フェーズ1 frozen (成果物 7・工程 10/10)、フェーズ2 active で flow が全 pending に再初期化 (UI: フェーズ1 ✓確定済み / フェーズ2 進行中)。凍結後に同名資料を再取り込み・restore しても凍結側の提案書は v1 のまま (新版はフェーズ2 に別出力 v3/v4 として作成) = 凍結成果物は変更されない。凍結成果物へのコメント投稿は 201 (閲覧・コメントは可)</t>
         </is>
       </c>
     </row>
@@ -4217,15 +4465,19 @@
           <t>工程ごとにスレッドが 1 つ作られる。2 回目は同じスレッドに遷移し、増えない</t>
         </is>
       </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr"/>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>1回目=200 thread=fa1909fa-6479-40cf-aa42-9e0ba3344783, 2回目=200 thread=fa1909fa-6479-40cf-aa42-9e0ba3344783 同一=True; GET /chat/threads 件数=1</t>
         </is>
       </c>
     </row>
@@ -4279,15 +4531,19 @@
           <t>作成した確定事項が一覧に出る。状態遷移がチャットの文脈パネルに反映される</t>
         </is>
       </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J30-13.png</t>
+        </is>
+      </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>API: 作成→PATCH decided→GET /decisions に (自分の件, decided) で一覧=[[true,"decided"]]; チャット S-E01 文脈パネル「主力決定」タブに本文あり=true, 確定表記=true (context-preview の system_prompt には入らないが画面パネルには反映)</t>
         </is>
       </c>
     </row>
@@ -4342,15 +4598,19 @@
           <t>条件に合う案件だけが一覧に出る。カーソルで次ページが取れ、重複も抜けも無い</t>
         </is>
       </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr"/>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>status=paused フィルタ -&gt; ['QA-B 停止案件'] (該当 1 件のみ); limit=1 カーソル (URL エンコード必須) で 3 ページ 3 件, 重複 0, 全件 3 と集合一致。API に sort パラメータは無く created_at desc 固定</t>
         </is>
       </c>
     </row>
@@ -4403,15 +4663,19 @@
           <t>選んだ案件が現在の案件として反映され、工程/チャットがその案件の文脈に切り替わる</t>
         </is>
       </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-06.png</t>
+        </is>
+      </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>t-uc-39 で「案件2 Sirius」を選ぶと現在案件が Sirius になり、工程 (/workflow) とチャット (/chat) の文脈が Sirius に切り替わる (Nebula は出ない)</t>
         </is>
       </c>
     </row>
@@ -4464,15 +4728,19 @@
           <t>運営の既定が最初から一覧に出る。ワークスペース側の版履歴は空で、参照している既定版が記録されている</t>
         </is>
       </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr"/>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J01-04.png</t>
+        </is>
+      </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>依存 J01-01 (運営既定の作成 = admin+mac) 未達で、本番には運営既定が 0 件。観察: 新 WS で /templates を開くと 10 種類 (見積書〜納品書) が並び「版履歴（0）」、API GET /workspaces/{ws}/design-templates=[] / …/estimate/versions=[] (200、ただし 1 回は 500)。「運営既定を継承中」の表示も参照既定版の記録も出ない (既定が無いので出せない) / 解除条件: J01-01</t>
         </is>
       </c>
     </row>
@@ -4526,15 +4794,19 @@
           <t>ワークスペース版 v1 が積まれ、一覧の最新版が自分の版に切り替わる。以後の成果物プレビューに反映される</t>
         </is>
       </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr"/>
+      <c r="K66" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J01-05.png</t>
+        </is>
+      </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac (Bridge + 本人の Claude 契約で AI が動く) / 解除条件: Mac の Bridge ハーネス。AI 不要部分の観察: /templates で「提案書」に指示を書いて送ると POST /workspaces/{ws}/design-templates/proposal -&gt; 503 で、画面に「お使いのパソコン (Bridge) が未接続のためテンプレの作成を実行できません」+ 接続手順が出る (入力は保持)。API 直叩きも 503「Bridge がオフライン」</t>
         </is>
       </c>
     </row>
@@ -4587,15 +4859,19 @@
           <t>自分の版が作成者・日時つきで記録され、運営既定とは別の履歴として残っている</t>
         </is>
       </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L67" t="inlineStr"/>
+      <c r="K67" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J01-06.png</t>
+        </is>
+      </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>依存 J01-05 (WS 版の作成 = mac) 未達で自分の版が無い。観察: 版履歴 API は [] で「版履歴（0）」表示 / 解除条件: J01-05</t>
         </is>
       </c>
     </row>
@@ -4650,15 +4926,19 @@
           <t>上書き済みワークスペースの最新版は変わらない (勝手に上書きし返さない)。上書きしていないワークスペースだけ新しい既定が最新版として反映される</t>
         </is>
       </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr"/>
+      <c r="K68" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行 + 場所=mac (Bridge + 本人の Claude 契約で AI が動く) / 解除条件: Mac の Bridge ハーネス</t>
         </is>
       </c>
     </row>
@@ -4711,15 +4991,19 @@
           <t>既定に戻した版が新版として積まれ、自分の旧版は履歴に残る。プレビューが既定の見た目に戻る</t>
         </is>
       </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr"/>
+      <c r="K69" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J01-08.png</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>依存 J01-05 未達 (上書きが無い)。観察: 上書きが無い状態では「運営の既定デザインに戻す」ボタン自体が出ない (仕様どおり)。API 直叩き POST …/estimate/reset-to-default -&gt; 404「この種類の運営既定デザインはまだ設定されていません。」(既定が無い場合の 404; 継承中なら 409 の設計) / 解除条件: J01-01 + J01-05</t>
         </is>
       </c>
     </row>
@@ -4772,15 +5056,19 @@
           <t>サイドバーのワークスペース名に反映され、監査ログ workspace_updated が記録される</t>
         </is>
       </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr"/>
+      <c r="K70" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-01.png</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: サイドバーの WS 名に反映 / 実測: PATCH /workspaces 200 で保存され GET も新名だが、保存直後のサイドバー「ワークスペース · QA JA2 WS1 改名」とヘッダー「ワークスペース: QA jA2 WS1 改名」は旧名のまま。再読み込みで初めて「再改名」に変わる (G-12: 直後に反映されない。J15-03 と同型)。※基本情報の保存は POST /account/ai-learning も同時に送る。監査ログ workspace_updated は未観測</t>
         </is>
       </c>
     </row>
@@ -4833,15 +5121,19 @@
           <t>日本語のエラーで拒否され、DB の名前は変わらない</t>
         </is>
       </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-02.png</t>
+        </is>
+      </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>日本語エラー ["2 文字以上で入力してください","退会手続きへ進む"] で拒否 (画面 PATCH=未送信 / API 直接 422)、DB の名前は「QA jA2 WS1 改名」のまま</t>
         </is>
       </c>
     </row>
@@ -4896,15 +5188,19 @@
           <t>既定は OFF (学習しない) で表示される。切替が DB に反映され、監査ログ ai_training_optin_changed が記録される</t>
         </is>
       </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr"/>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-03.png</t>
+        </is>
+      </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>場所=cloud / 絶対ルール 6</t>
+          <t>観測できた部分は全て期待どおり: 既定は OFF (checkbox 未チェック・GET /me ai_learning_opt_out=true)、ON で保存 → POST /account/ai-learning 200・GET /me opt_out=false・再読み込み後も ON、OFF に戻すと opt_out=true。監査ログ ai_training_optin_changed は運営でしか読めず未観測 / 解除条件: 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -4958,15 +5254,19 @@
           <t>平文が 1 度だけ表示され、一覧に出る。再読み込み後は平文が二度と出ない。監査ログ mcp_token_issued が記録される</t>
         </is>
       </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr"/>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-04.png</t>
+        </is>
+      </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>観測できた部分は全て期待どおり: 発行 (POST /mcp-tokens 201) 直後に平文が 1 度表示され一覧に「QA jA2 Claude Desktop」が出る。再読み込み後は平文が出ず、GET 一覧/詳細にも token フィールド無し。監査ログ mcp_token_issued は運営でしか読めず未観測 / 解除条件: 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -5019,15 +5319,19 @@
           <t>一覧に失効として反映され、そのトークンでの MCP 接続は拒否される。監査ログ mcp_token_revoked が記録される</t>
         </is>
       </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr"/>
+      <c r="K74" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-05.png</t>
+        </is>
+      </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>観測できた部分は期待どおり: DELETE /mcp-tokens 204、一覧に失効として反映 (active 一覧から消える)、API revoked_at 記録。未観測: 「そのトークンでの MCP 接続が拒否される」は MCP 接続を受ける側 (Bridge/MCP サーバ) が API 側に無く本環境で試せない、監査ログ mcp_token_revoked は運営限定 / 解除条件: Mac の Bridge (MCP 接続) + 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -5081,15 +5385,19 @@
           <t>30 日保持の案内が出て一覧から消える。DB に deleted_at が記録され、そのワークスペースのデータへのアクセスは拒否される。監査ログ workspace_deleted が記録される</t>
         </is>
       </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr"/>
+      <c r="K75" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-07.png</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 30 日案内・一覧から消える・deleted_at 記録・配下データへのアクセス拒否 / 実測: DELETE=204 30日案内=true 一覧から消えた=true GET ws=404 deleted_at=undefined 配下 projects=200/1 詳細=200 employees=200/10。追加: 削除した WS の案件「QA jA2 使い捨て案件」は /projects 一覧 (GET /projects?limit=20) にも出続ける</t>
         </is>
       </c>
     </row>
@@ -5143,15 +5451,19 @@
           <t>運営固定の 10 名が組織図とリストの両方に出る。雇用/追加/削除の導線は出ない状態 (固定編成)</t>
         </is>
       </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr"/>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J37-01.png</t>
+        </is>
+      </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営固定の 10 名 (ジャービス,トニー,ナターシャ,スティーブ,ピーター,ストレンジ,ワンダ,ヴィジョン,ソー,ティチャラ) が組織図・リストの両方に出る (ビュー切替で確認)。雇用/追加/削除の導線は 0 件 (固定編成)</t>
         </is>
       </c>
     </row>
@@ -5204,15 +5516,19 @@
           <t>名前・口調・「できること」が出る。スキル名や本文は画面と API 応答のどちらにも含まれない状態である</t>
         </is>
       </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr"/>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J37-02.png</t>
+        </is>
+      </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T06</t>
+          <t>期待: 名前・口調・「できること」が出て、スキル名や本文は画面と API のどちらにも含まれない (R-T06) / 実測: 名前・口調プリセット・「できること」は出るが、「できること」欄にスキル名 sales-email / proposal / estimate がそのまま列挙され、画面は GET /skills?limit=200 (スキル台帳) も取得。API: GET /ai-employees/{id} は attached_skills にスキル ID 3 件、GET /ai-employees/templates と /templates/{id} は system_prompt 本文 (「あなたは営業・契約部の部長トニーです。…」43 字) を一般利用者に返す = スキル名・本文が漏れる</t>
         </is>
       </c>
     </row>
@@ -5266,15 +5582,19 @@
           <t>一覧と組織図とチャットの発言者名に反映される。監査ログ ai_employee_customized が記録される</t>
         </is>
       </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L78" t="inlineStr"/>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J37-03.png</t>
+        </is>
+      </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>観測できた部分は全て期待どおり: 表示名「トニー改」・口調 polite→casual を下部バーで保存 (PATCH 200)、一覧・組織図・チャット画面 (スレッドの発言者名) に反映。監査ログ ai_employee_customized は運営でしか読めず未観測 / 解除条件: 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -5327,15 +5647,19 @@
           <t>FORBIDDEN_FIELD で拒否され、DB は変わらない</t>
         </is>
       </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr"/>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J37-04</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: FORBIDDEN_FIELD で拒否・DB 不変 / 実測: 200 {"data":{"id":"2fd8c87c-011a-4419-9d32-6d0be141f908","workspace_id":"3adaebaa-1a52-41c9-8305-b1da3af / 200 {"data":{"id":"2fd8c87c-011a-4419-9d32-6d0be141f908","workspace_id":"3adaebaa-1a52-41c9-8305-b1da3af / 200 / 注入混入=false</t>
         </is>
       </c>
     </row>
@@ -5389,15 +5713,19 @@
           <t>署名付き URL でアップロードした画像が組織図とチャットに反映される。Storage に実体が存在する (G-11)</t>
         </is>
       </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L80" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J37-05.png</t>
+        </is>
+      </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 署名付き URL でアップロードした画像が組織図とチャットに反映され Storage に実体がある / 実測: POST icon-upload-url 200 → 署名付き URL へ PUT 200 → PATCH icon=storage_path 200 → GET icon-url 200 で取得した URL は 200 image/png 79B (Storage に実体あり = G-11 OK)。しかし組織図のノードは頭文字「TO」のまま (img 無し・icon-url の呼び出し無し)、チャット画面も頭文字「ト」= アップロードした画像が画面に反映されない</t>
         </is>
       </c>
     </row>
@@ -5450,15 +5778,19 @@
           <t>0 件の案内が出る状態になる。エラーにならない</t>
         </is>
       </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J37-07.png</t>
+        </is>
+      </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>未使用の「ヴィジョン」の活動履歴: API 200 / 0 件、画面は「まだ活動がありません。タスク割当・チャット・確定事項がここに並びます。」の案内でエラー無し</t>
         </is>
       </c>
     </row>
@@ -5512,15 +5844,19 @@
           <t>利用者が編集した表示名・口調は残り、編集していない項目 (専門分野等) だけ新版が反映される</t>
         </is>
       </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr"/>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J37-08</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限なし: テンプレ改訂は /admin/ai-employee-templates (運営) が要る / 解除条件: 運営アカウント (scripts/grant-admin.sh)</t>
         </is>
       </c>
     </row>
@@ -5573,15 +5909,19 @@
           <t>一覧と見出しに反映され、監査ログ project_updated が記録される</t>
         </is>
       </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr"/>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-01.png</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>案件設定で名前「QA jA2 案件1 Nebula 改」・説明を保存 (PATCH 200)。一覧のカードとダッシュボードの見出し直下 (「QA jA2 案件1 Nebula 改 · クライアント案件 · 第 1 段階」) に反映。監査 project.update をダッシュボード recent_activities (audit_logs 由来) で確認</t>
         </is>
       </c>
     </row>
@@ -5635,15 +5975,19 @@
           <t>既定は OFF で表示される。切替が DB に反映され、記録される</t>
         </is>
       </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr"/>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-02.png</t>
+        </is>
+      </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>場所=cloud / 絶対ルール 6</t>
+          <t>既定 OFF (未チェック・ai_learning_opt_out=true)。ON で保存 → POST /projects/{id}/ai-learning 200・GET opt_out=false・再読み込み後も ON、監査 project.ai_learning_set を recent_activities で確認。OFF に戻すと opt_out=true</t>
         </is>
       </c>
     </row>
@@ -5697,15 +6041,19 @@
           <t>アクティブ一覧から消えアーカイブ一覧に出る。戻すとアクティブ一覧に反映される</t>
         </is>
       </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr"/>
+      <c r="K85" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-06.png</t>
+        </is>
+      </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 一覧からアーカイブ → アクティブ一覧から消えアーカイブ一覧に出る → 戻すと復帰 / 実測: 一覧のカードにアーカイブ/戻す操作が無い (導線: 新規プロジェクト・絞込 すべて/進行中/アーカイブ のみ)。API PATCH status=archived にすると「進行中」絞込からは消え「アーカイブ」絞込に出るが、既定の「すべて」には残り、見出しの件数「3 件のアクティブプロジェクト」も変わらない (GET /projects?limit=20 を 1 回取りクライアント側で絞る)。PATCH status=in_progress で「進行中」に復帰</t>
         </is>
       </c>
     </row>
@@ -5758,15 +6106,19 @@
           <t>一覧にマスク表示で出る。応答と DB に平文が無い (暗号化保存)。監査ログ credential_created が記録される</t>
         </is>
       </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr"/>
+      <c r="K86" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J39-01.png</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 一覧にマスク表示・応答/DB に平文無し・監査 credential_created / 実測: 画面の「暗号化して保存」→ POST /projects/{id}/credentials が 500 {"detail":"サーバー側の設定に問題があります。運営にお問い合わせください。"} (API 直接・kind を変えても同じ)。本番に暗号化鍵 (vault key) 等のサーバー設定が無く登録できない (G-11: 外部リソース/秘密の実在)。一覧は 0 件のまま</t>
         </is>
       </c>
     </row>
@@ -5819,15 +6171,19 @@
           <t>権限者だけ一時復号した値が出る。監査ログ credential_revealed が記録される</t>
         </is>
       </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr"/>
+      <c r="K87" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J39-01</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>J39-01 (登録) が本番のサーバー設定不備で 500 のためシークレットが 1 件も作れず未実行 / 解除条件: 本番 API に暗号化鍵 (vault) を設定して J39-01 を通す</t>
         </is>
       </c>
     </row>
@@ -5880,15 +6236,19 @@
           <t>名前が一覧に反映され、値は変わらない (reveal で同じ値)</t>
         </is>
       </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr"/>
+      <c r="K88" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J39-01</t>
+        </is>
+      </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>J39-01 (登録) が本番のサーバー設定不備で 500 のためシークレットが 1 件も作れず未実行 / 解除条件: 本番 API に暗号化鍵 (vault) を設定して J39-01 を通す</t>
         </is>
       </c>
     </row>
@@ -5941,15 +6301,19 @@
           <t>一覧から消え、soft delete が記録される。reveal もできない状態になる</t>
         </is>
       </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr"/>
+      <c r="K89" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J39-01</t>
+        </is>
+      </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>J39-01 (登録) が本番のサーバー設定不備で 500 のためシークレットが 1 件も作れず未実行 / 解除条件: 本番 API に暗号化鍵 (vault) を設定して J39-01 を通す</t>
         </is>
       </c>
     </row>
@@ -6002,15 +6366,19 @@
           <t>招待が一覧に出て、相手に招待メールが届く (実送信できない環境では送信ログ/キュー投入で代替)。監査ログ invitation_sent が記録される</t>
         </is>
       </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L90" t="inlineStr"/>
+      <c r="K90" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-01.png</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>一覧に出る=true (role=member, membership 即時作成)。しかし招待メールは送られない (送信ログ/キュー/API 応答のいずれにも送信の痕跡なし — 実装は登録済みメールを即時 membership 化する方式で、メール送信コードが無い)。監査 workspace_member.invite は admin 専用 API のため未確認</t>
         </is>
       </c>
     </row>
@@ -6064,15 +6432,19 @@
           <t>参加でき membership が作られる。案件とタスクが一覧に出る。監査ログ invitation_accepted が記録される</t>
         </is>
       </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr"/>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-02.png</t>
+        </is>
+      </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>招待リンクは存在せず membership が即時作成 (member の GET /workspaces に WS あり=true)。案件一覧に案件=true, タスク画面に owner のタスク=true (API projects=3, tasks=2)。監査 invitation_accepted に相当する操作は無い (即時参加)</t>
         </is>
       </c>
     </row>
@@ -6125,15 +6497,19 @@
           <t>権限が無いことが日本語で分かる (access-denied に遷移)。白画面や生のエラーにしない</t>
         </is>
       </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr"/>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-03.png</t>
+        </is>
+      </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営画面 /admin → access-denied 相当 (日本語で権限なし表示=true); 設定の課金/退会タブは描画されるが owner 専用 API は全部拒否 {"WS 設定変更":"403 このワークスペースを変更する権限がありません。","WS 削除":"403 このワークスペースを削除する権限がありません。","課金 checkout":"503 お支払いの取り扱いがまだ設定されていません。運営にお問い合わせください。","運営 dashboard":"403 この操作は運営のみが行えます。","メンバー招待":"403 メンバーを招待できるのはワークスペースのオーナーだけです。"}; WS 名不変=true; 日本語文言=true</t>
         </is>
       </c>
     </row>
@@ -6187,15 +6563,19 @@
           <t>member として案件とタスクを作成でき、owner 側の一覧にも反映される</t>
         </is>
       </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L93" t="inlineStr"/>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-04.png</t>
+        </is>
+      </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>member: 案件作成=201, タスク作成=201; owner 側: 案件一覧に反映=true, タスク一覧 (API/画面) に反映=true/true</t>
         </is>
       </c>
     </row>
@@ -6248,15 +6628,19 @@
           <t>一覧に viewer として反映され、監査ログ role_changed が記録される。相手側は次の操作から閲覧のみに遷移する</t>
         </is>
       </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L94" t="inlineStr"/>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-05.png</t>
+        </is>
+      </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>ロール変更 (UI select) → GET members role=viewer, 一覧に閲覧者表記=true。監査 workspace_member.role_update は admin 専用 API のため未確認。相手側の即時反映は J31-06 で確認</t>
         </is>
       </c>
     </row>
@@ -6309,15 +6693,19 @@
           <t>編集操作は 403 で拒否され、閲覧は引き続きできる状態である</t>
         </is>
       </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L95" t="inlineStr"/>
+      <c r="K95" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-06.png</t>
+        </is>
+      </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>ロール変更直後・同じトークンで: 案件名変更=403, タスク作成=500 (403 期待), 閲覧 GET project=200 tasks=200; 案件名不変=true</t>
         </is>
       </c>
     </row>
@@ -6370,15 +6758,19 @@
           <t>どちらも 403 で拒否され、値は漏れない。監査ログに拒否が記録される</t>
         </is>
       </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L96" t="inlineStr"/>
+      <c r="K96" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-07.png</t>
+        </is>
+      </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>閲覧者: シークレット追加=500「サーバー側の設定に問題があります」(403 期待), reveal=404 (対象なし)。根本原因: owner による事前登録 (J39-01 相当) も 500 → 本番にシークレット暗号鍵 (Fernet) が未設定 (G-11)。認可 (403) より先に設定エラーが返るため、閲覧者判定も未達。値漏れ=false, 一覧 GET=200 (0 件)。監査の拒否記録は admin 専用 API のため未確認</t>
         </is>
       </c>
     </row>
@@ -6432,15 +6824,19 @@
           <t>拒否され、期限切れであることが日本語で分かる。membership は増えない</t>
         </is>
       </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L97" t="inlineStr"/>
+      <c r="K97" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-08.png</t>
+        </is>
+      </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>招待リンク・expires_at を持つ招待エンティティが実装に存在しない (POST /workspaces/{id}/members は登録済みメールを即時 membership 化し、招待一覧/期限/リンクの API・UI が無い)。「7 日で期限切れ」の仕様を満たす対象が無いため期待未達</t>
         </is>
       </c>
     </row>
@@ -6493,15 +6889,19 @@
           <t>既にメンバーとして拒否され、招待は増えない</t>
         </is>
       </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr"/>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-09.png</t>
+        </is>
+      </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>再招待 API=409 「この方は、すでにメンバーです。」, UI にも「すでにメンバーです。」; メンバー数 2→2 (増えない)</t>
         </is>
       </c>
     </row>
@@ -6554,15 +6954,19 @@
           <t>一覧から消え、監査ログ member_removed が記録される。相手の既存セッションは次のリクエストから拒否される (G-14)</t>
         </is>
       </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L99" t="inlineStr"/>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-10.png</t>
+        </is>
+      </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>除名 (UI 削除ボタン) → 一覧から消える=true; 除名直後・既存トークンで案件 GET=404, WS 案件一覧=200/0 件, タスク=200/0 件 (拒否=true)。監査 workspace_member.remove は admin 専用 API のため未確認</t>
         </is>
       </c>
     </row>
@@ -6616,15 +7020,19 @@
           <t>ワークスペースのデータが見えなくなる。サインインはできるが所属なしの状態になる</t>
         </is>
       </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L100" t="inlineStr"/>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-11.png</t>
+        </is>
+      </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>除名前の画面: WS データ見える=false; 再サインイン可=true, 所属 WS=[] (元 WS 含む=false), 案件 GET=404, 画面に案件=false</t>
         </is>
       </c>
     </row>
@@ -6677,15 +7085,19 @@
           <t>LAST_OWNER エラーで拒否され、メンバー一覧は変わらない (DB の membership も残る)</t>
         </is>
       </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L101" t="inlineStr"/>
+      <c r="K101" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-06.png</t>
+        </is>
+      </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: LAST_OWNER エラーで拒否され一覧不変 / 実測: 画面のメンバー一覧には自分 (唯一の owner) の削除ボタンが無い。API 直接 DELETE /workspaces/{ws}/members/{自分} は 204 (2 回実行とも) を返すが membership は残る (1 名 owner のまま) = エラーではなく「成功したふりの no-op」。期待の LAST_OWNER エラーが返らない</t>
         </is>
       </c>
     </row>
@@ -6739,15 +7151,19 @@
           <t>5 種 (task/phase/knowledge/comment/scope_change) の承認待ちが種別つきで一覧に出て、フィルタで絞れる。本人宛以外は出ない</t>
         </is>
       </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr"/>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J32-01.png</t>
+        </is>
+      </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>5 種の承認待ちを発生させる手段が利用者側に無い (発生源は AI ツール実行 / Bridge / 運営 cron のみ)。画面 S-J01 には種別チップ (タスク/工程/ナレッジ/コメント/スコープ変更) が実装されているが 0 件のため絞り込みを判定できない / 解除条件: Mac の Bridge ハーネスで AI 社員に書込系ツールを実行させて approval_inbox を発生させる (または運営 cron integrity-check)</t>
         </is>
       </c>
     </row>
@@ -6800,15 +7216,19 @@
           <t>一覧から消え、DB 上も承認済みに遷移する。対象 (タスク/フェーズ/ナレッジ) の状態が変わる。監査ログ inbox_entry_resolved が記録される</t>
         </is>
       </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L103" t="inlineStr"/>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J32-02.png</t>
+        </is>
+      </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>承認対象の承認待ちを作れない (発生源は AI/Bridge/運営 cron のみ) / 解除条件: Mac の Bridge ハーネスで AI 社員に書込系ツールを実行させて approval_inbox を発生させる (または運営 cron integrity-check)</t>
         </is>
       </c>
     </row>
@@ -6861,15 +7281,19 @@
           <t>却下として記録され、承認済みと区別できる。対象は変わらない (ナレッジなら書き込まれない)</t>
         </is>
       </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr"/>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J32-03.png</t>
+        </is>
+      </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>却下対象の承認待ちを作れない (発生源は AI/Bridge/運営 cron のみ) / 解除条件: Mac の Bridge ハーネスで AI 社員に書込系ツールを実行させて approval_inbox を発生させる (または運営 cron integrity-check)</t>
         </is>
       </c>
     </row>
@@ -6922,15 +7346,19 @@
           <t>選んだ件だけ承認済みに遷移し、選んでいないものは一覧に残る</t>
         </is>
       </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L105" t="inlineStr"/>
+      <c r="K105" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J32-04.png</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>一括承認する複数件の承認待ちを作れない (発生源は AI/Bridge/運営 cron のみ) / 解除条件: Mac の Bridge ハーネスで AI 社員に書込系ツールを実行させて approval_inbox を発生させる (または運営 cron integrity-check)</t>
         </is>
       </c>
     </row>
@@ -6983,15 +7411,19 @@
           <t>0 件の案内が出る状態になり、バッジも 0 に反映される</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L106" t="inlineStr"/>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J32-05.png</t>
+        </is>
+      </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>GET /approval-inbox pending=0 の状態で S-J01 を開く → 0 件の案内表示=true (「承認待ち / WS設定 / Q / QA-B2 WS 20260903 / / / 承認待ち / Q / 承認待ち / 承認待ち — あなたの判断を待っている案件をまとめて処理する場所 / AI 」), 生エラー無し。※承認待ちを発生させる手段が無いので「全部処理してから」ではなく最初から 0 件の状態で確認</t>
         </is>
       </c>
     </row>
@@ -7045,15 +7477,19 @@
           <t>ON では承認待ちの通知メールが届く (実送信できない環境では送信ログ/キュー投入で代替)。OFF では届かない</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L107" t="inlineStr"/>
+      <c r="K107" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J32-06.png</t>
+        </is>
+      </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>承認待ちを発生させられず、通知メールの送信ログ/キューを見る手段も無い (受信箱なし) / 解除条件: Mac の Bridge ハーネスで AI 社員に書込系ツールを実行させて approval_inbox を発生させる (または運営 cron integrity-check)</t>
         </is>
       </c>
     </row>
@@ -7106,15 +7542,19 @@
           <t>バッジの件数が一覧の件数と一致し、押すと承認待ち一覧に遷移する</t>
         </is>
       </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L108" t="inlineStr"/>
+      <c r="K108" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J32-07.png</t>
+        </is>
+      </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>S-B02 の「未承認 INBOX 件数 0 / すべて処理済み」は GET /approval-inbox pending 0 件と一致。ただし承認待ちへのリンク (/approvals) はカードに 1 件以上ある時しか描画されず、0 件では押す対象が無い (押下できた要素は通知センター /t-uc-36 だった)。承認待ちを発生させる手段が利用者側に無い / 解除条件: Bridge ハーネスで承認待ちを 1 件以上発生させる</t>
         </is>
       </c>
     </row>
@@ -7167,15 +7607,19 @@
           <t>自分宛の承認待ちが通知として一覧に出る。件数がバッジに反映され、他人宛のものは 1 件も出ない</t>
         </is>
       </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr"/>
+      <c r="K109" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-02.png</t>
+        </is>
+      </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>依存 J32-02 (承認待ちの発生) は AI 実行 (Bridge) が要る (承認は chat-relay の AI ジョブからしか生まれない) ため、自分宛の承認待ちを作れない。観測できた部分: 承認待ち 0 件の状態で t-uc-36 は ["未読 0","通知はありません"] と表示しエラー無し、GET /approval-inbox=0 件 / 解除条件: Mac の Bridge で J32-02 を先に流す</t>
         </is>
       </c>
     </row>
@@ -7228,15 +7672,19 @@
           <t>提案が一覧に出て、承認待ちに通知される。実フェーズはまだ作られない状態である</t>
         </is>
       </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L110" t="inlineStr"/>
+      <c r="K110" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J49-01</t>
+        </is>
+      </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>提案生成は本人の Claude (Bridge) 経由の LLM が要る (場所=mac)。実測: POST /workflow/phase-proposals → 503 {"detail":"お使いの PC の Bridge がオフラインです。Bridge アプリを起動してから、もう一度お試しください。"} (未接続を正直に断り、提案一覧は 0 件・実フェーズも増えない) / 解除条件: Mac の Bridge を接続</t>
         </is>
       </c>
     </row>
@@ -7289,15 +7737,19 @@
           <t>実フェーズが確定して一覧に出る。監査ログ phase_approved が記録される</t>
         </is>
       </c>
-      <c r="K111" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L111" t="inlineStr"/>
+      <c r="K111" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J49-02</t>
+        </is>
+      </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>承認する提案が作れない (J49-01 が場所=mac: POST /workflow/phase-proposals → 503)。承認/却下/重複拒否の API 自体は実装されている (approve/reject → 409「すでに処理済み」/ pending 重複 409 のコード有) が実データで未確認 / 解除条件: Mac の Bridge で提案を 1 件作る</t>
         </is>
       </c>
     </row>
@@ -7350,15 +7802,19 @@
           <t>フェーズは作られず、却下が記録される</t>
         </is>
       </c>
-      <c r="K112" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr"/>
+      <c r="K112" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J49-03</t>
+        </is>
+      </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>却下する提案が作れない (J49-01 が場所=mac: POST /workflow/phase-proposals → 503)。承認/却下/重複拒否の API 自体は実装されている (approve/reject → 409「すでに処理済み」/ pending 重複 409 のコード有) が実データで未確認 / 解除条件: Mac の Bridge で提案を 1 件作る</t>
         </is>
       </c>
     </row>
@@ -7411,15 +7867,19 @@
           <t>同じ提案が 2 件にならず、既存の pending 提案に案内される状態である</t>
         </is>
       </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr"/>
+      <c r="K113" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J49-07</t>
+        </is>
+      </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>pending 中の再依頼する提案が作れない (J49-01 が場所=mac: POST /workflow/phase-proposals → 503)。承認/却下/重複拒否の API 自体は実装されている (approve/reject → 409「すでに処理済み」/ pending 重複 409 のコード有) が実データで未確認 / 解除条件: Mac の Bridge で提案を 1 件作る</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7937,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -7538,7 +7997,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -7599,7 +8057,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -7660,7 +8117,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -7721,7 +8177,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -7782,7 +8237,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -7843,7 +8297,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -7900,15 +8353,19 @@
           <t>影響を受ける下流タスクが件数つきで出る。適用前は実移動しない状態である</t>
         </is>
       </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr"/>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J49-04.png</t>
+        </is>
+      </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI「影響を解析」→ POST 201、画面に「0 タスクへの影響を検出（実装済み 0 / その他 0）」と件数つきで表示、applied=false・タスク A の phase (null) は未変更 (実移動していない)。所見: tasks.dependencies を設定する API/UI が無いため影響 0 件しか作れず、下流タスクが実際に列挙される経路は本番の使い方では存在しない (G-13 の穴)</t>
         </is>
       </c>
     </row>
@@ -7961,15 +8418,19 @@
           <t>実移動が反映され、完了済みの影響タスクにリファクタタスクが parent_task 紐付けで自動起票される</t>
         </is>
       </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L122" t="inlineStr"/>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J49-05.png</t>
+        </is>
+      </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>場所=cloud / F-CUC02</t>
+          <t>前半 (実移動) は実測 PASS: 「承認して移動」→ POST apply 200、タスク A の phase が移動先「アーキ設計」に変わり画面も「適用済み」。後半 (完了済み影響タスクへのリファクタ自動起票 parent_task 紐付け) は、影響タスクを作る手段 (tasks.dependencies を書く API/UI) が無く影響 0 件 → refactor_task_ids=[] で未検証 / 解除条件: dependencies を設定できる API/UI (または DB 直接投入) を用意する</t>
         </is>
       </c>
     </row>
@@ -8022,15 +8483,19 @@
           <t>total/done/awaiting とスコア平均、本日の解析回数が実数と一致して反映される</t>
         </is>
       </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr"/>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J49-06.png</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>phase-task-stats (phase_id=アーキ設計: total 1/done 0/awaiting 0/avg_score null) が実タスク (アーキ設計 1 件 triage、未割当 2 件は対象外) と一致; impact-stats today_count=1 = 画面「1 回（本日）」; consistency_ok=true dangling_count=0; 画面の工程行は「0 / 1 タスク完了」で total/done を表示 (awaiting 0・スコア無しは非表示)</t>
         </is>
       </c>
     </row>
@@ -8089,7 +8554,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8150,7 +8614,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8212,7 +8675,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8273,7 +8735,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8334,7 +8795,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L128" t="inlineStr"/>
       <c r="M128" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -8395,7 +8855,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -8456,7 +8915,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8517,7 +8975,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -8579,7 +9036,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8640,7 +9096,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L133" t="inlineStr"/>
       <c r="M133" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8702,7 +9157,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr"/>
       <c r="M134" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8763,7 +9217,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8824,7 +9277,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8886,7 +9338,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr"/>
       <c r="M137" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -8947,7 +9398,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr"/>
       <c r="M138" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9009,7 +9459,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr">
         <is>
           <t>場所=mac / F-009</t>
@@ -9070,7 +9519,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr"/>
       <c r="M140" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9131,7 +9579,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9187,15 +9634,19 @@
           <t>その社員がした作業 (修正提案・成果物生成) が時系列で一覧に出る</t>
         </is>
       </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr"/>
+      <c r="K142" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J37-06</t>
+        </is>
+      </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>依存 J46-05 (成果物の修正提案) は AI 実行 (Mac の Bridge) が要り本環境では作れない / 解除条件: Mac の Bridge で J46-05 を先に流す</t>
         </is>
       </c>
     </row>
@@ -9253,7 +9704,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -9314,7 +9764,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr"/>
       <c r="M144" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9375,7 +9824,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
       <c r="M145" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9436,7 +9884,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr"/>
       <c r="M146" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -9497,7 +9944,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr">
         <is>
           <t>場所=cloud / GAP-147 回帰</t>
@@ -9558,7 +10004,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr"/>
       <c r="M148" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9620,7 +10065,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L149" t="inlineStr"/>
       <c r="M149" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9682,7 +10126,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9744,7 +10187,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9805,7 +10247,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L152" t="inlineStr"/>
       <c r="M152" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9866,7 +10307,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -9923,15 +10363,19 @@
           <t>各ファイルの結果が出て、どこへ仕分けられたか (成果物/ナレッジ) が一覧に反映される</t>
         </is>
       </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L154" t="inlineStr"/>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J33-01.png</t>
+        </is>
+      </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>UI: 成功 3/失敗 0 表示=true, 3 ファイル各行の結果表示=3/3 (仕分け=成果物 / 工程 ["proposal","hearing","requirements"]); 再取得 GET /outputs=3 件。※場所=mac 行だが分類は規則ベースで AI 不要のため実走</t>
         </is>
       </c>
     </row>
@@ -9984,15 +10428,19 @@
           <t>壊れた方は理由つきで残り、正常な方は取り込まれて一覧に出る</t>
         </is>
       </c>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr"/>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J33-02.png</t>
+        </is>
+      </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI: 成功 1/失敗 1=true; 壊れ側の理由表示="壊れたデータ.xyz / → 壊れたデータ.xyz: 対応していない形式です"; 正常側 (見積書) は取り込まれ GET /outputs 3→4</t>
         </is>
       </c>
     </row>
@@ -10046,15 +10494,19 @@
           <t>確定した工程だけが done に遷移する。確定していないものは動かない</t>
         </is>
       </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L156" t="inlineStr"/>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J33-03.png</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>提案 [提案, 要件定義, 納品・請求] のうち要件定義を外して「2 工程を完了として反映」→ 再取得 flow: proposal=done, delivery=done (チェックした 2 つだけ), requirements=pending / hearing=pending (未確定は動かない)。監査 project.flow.complete ×2。※場所=mac 行だが分類は規則ベースで AI 不要のため実走。※懸念(G-13): 「ヒアリングメモ2.md」が既定で納品工程に仕分けられ、hearing 未着手のまま hard gate の納品工程を取り込み画面から完了できた (正本に足すべき観点として報告)</t>
         </is>
       </c>
     </row>
@@ -10107,15 +10559,19 @@
           <t>工程の状態は変わらず、取り込んだ資料だけが残る</t>
         </is>
       </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L157" t="inlineStr"/>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J33-04.png</t>
+        </is>
+      </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>提案 3 件を全部外す → 反映ボタン disabled=true; 画面を離れた後 flow 不変=true (全 pending), 取り込んだ成果物 3 件はそのまま残る</t>
         </is>
       </c>
     </row>
@@ -10169,15 +10625,19 @@
           <t>アップロードが完了し、処理中の状態で一覧に出る。Storage に実体が存在する (G-11)</t>
         </is>
       </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L158" t="inlineStr"/>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J34-01.png</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>S-M01 でファイル選択 → 署名 URL 発行 (POST /meetings/upload-url 200) → storage への PUT 200 (G-11: バケット meetings に実体が置けた = storage の応答 Key あり) → POST /meetings 201 → 一覧 (GET /meetings) に parsed_at=null で登録。画面「アップロード状況」に「打合せ音声2.wav / 16 KB / 解析中」で表示 (初回判定は反映前に読んだ誤り→再確認で PASS)。transcribe は自動で 202 queued</t>
         </is>
       </c>
     </row>
@@ -10231,15 +10691,19 @@
           <t>状態が parsed に遷移し、本文が読める</t>
         </is>
       </c>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr"/>
+      <c r="K159" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J34-02.png</t>
+        </is>
+      </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>文字起こしは利用者 PC の Bridge/STT ワーカーで実行される (場所=mac)。参考: API transcribe → 202  / 解除条件: Mac の Bridge ハーネス</t>
         </is>
       </c>
     </row>
@@ -10293,15 +10757,19 @@
           <t>タスク・要件・決定に反映され、元の議事録から辿れる状態になる</t>
         </is>
       </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr"/>
+      <c r="K160" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J34-03.png</t>
+        </is>
+      </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>採用候補は文字起こし済み (parsed) の議事録から抽出される (場所=mac) / 解除条件: Mac の Bridge ハーネスで J34-02 を通す</t>
         </is>
       </c>
     </row>
@@ -10354,15 +10822,19 @@
           <t>打合せを根拠にした提案が承認待ちの一覧に出て、通知される</t>
         </is>
       </c>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L161" t="inlineStr"/>
+      <c r="K161" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J34-04.png</t>
+        </is>
+      </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>文字起こし済みの議事録が前提 (場所=mac)。参考: API propose-phase → 500 サーバー側で問題が発生しました。時間をおいて、もう一度お試しください。（参照 ID: e68d1472-0ac2-4c5 / 解除条件: Mac の Bridge ハーネス</t>
         </is>
       </c>
     </row>
@@ -10415,15 +10887,19 @@
           <t>状態が parsing に遷移し、完了すれば parsed になる</t>
         </is>
       </c>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L162" t="inlineStr"/>
+      <c r="K162" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J34-05.png</t>
+        </is>
+      </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>解析の再開・完了は Bridge ワーカーが要る (場所=mac)。参考: API resume-analysis → 200  / 解除条件: Mac の Bridge ハーネス</t>
         </is>
       </c>
     </row>
@@ -10476,15 +10952,19 @@
           <t>日本語のエラーで拒否され、一覧に増えない</t>
         </is>
       </c>
-      <c r="K163" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr"/>
+      <c r="K163" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J34-06.png</t>
+        </is>
+      </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>.exe: UI の input は accept="audio/*,video/*,.txt,.md,.docx,text/plain" で選択を絞るだけで、選択できてしまえば (D&amp;D/強制選択) そのまま送信され、日本語エラーは出ず一覧に「setup.exe / 102 B / 解析中」で増えた (後の一覧再確認で表示を確認)。API も upload-url=200 / POST /meetings (mime application/x-msdownload)=201 で拒否しない → 期待 (日本語エラーで拒否・一覧に増えない) 未達</t>
         </is>
       </c>
     </row>
@@ -10537,15 +11017,19 @@
           <t>一覧から消え、論理削除が記録される</t>
         </is>
       </c>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L164" t="inlineStr"/>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J34-07.png</t>
+        </is>
+      </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>削除 (UI) → 一覧 (API/画面) から消える=true/true; GET /meetings/{id} → 404 (deleted_at=n/a) = 論理削除</t>
         </is>
       </c>
     </row>
@@ -10598,15 +11082,19 @@
           <t>完了扱いにならず、要対応 (error) の状態で残る。空の本文が parsed として記録されない</t>
         </is>
       </c>
-      <c r="K165" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L165" t="inlineStr"/>
+      <c r="K165" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J34-08.png</t>
+        </is>
+      </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>場所=mac / G-15</t>
+          <t>無音ファイルの解析実行は STT ワーカー (場所=mac) が要る。G-15 観点は正本どおり残す / 解除条件: Mac の Bridge ハーネス</t>
         </is>
       </c>
     </row>
@@ -10659,15 +11147,19 @@
           <t>一覧に出て、埋め込みが生成される (embedding-status に反映)。監査ログに記録される</t>
         </is>
       </c>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L166" t="inlineStr"/>
+      <c r="K166" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>POST /knowledge 201 → GET /knowledge (workspace) 一覧に出る=True。しかし埋め込みは生成されない: GET /embedding-status provider=none state=unavailable indexed/total=0/1 semantic_enabled=false (本番に埋め込みプロバイダが未設定 = G-11)。監査ログ knowledge.create は利用者向け API に露出せず未確認</t>
         </is>
       </c>
     </row>
@@ -10721,15 +11213,19 @@
           <t>該当が出典つきで一覧に出る。存在しない語では 0 件の状態になり、壊れない</t>
         </is>
       </c>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L167" t="inlineStr"/>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>本文にしか無い語で検索 → 1 件, 該当あり=True (hit の付帯情報: ['knowledge', 'score'], source_type=manual); 存在しない語 → 200 / 0 件 (壊れない)</t>
         </is>
       </c>
     </row>
@@ -10783,15 +11279,19 @@
           <t>1 件も出ない状態である。グラフにも出ない</t>
         </is>
       </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr"/>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>別 WS で同じ語を含むナレッジ作成後、自分側の検索 (account_id 指定 1 件 / 指定なし 1 件)・グラフ (1 nodes)・別 WS を account_id に指定した一覧/グラフ (0 件 / 200) のいずれにも別 WS のナレッジは出ない=True</t>
         </is>
       </c>
     </row>
@@ -10844,15 +11344,19 @@
           <t>user から workspace common に遷移し、共通ナレッジの一覧に出る。監査ログ knowledge_approved が記録される</t>
         </is>
       </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>promote → account_type=workspace account_id==WS=True scope=common; 共通ナレッジ一覧 (workspace) に出る=True; 元 user 側に残る=False (id 同一=True)。監査 knowledge_approved 相当は利用者向け API に露出せず未確認 (S-K02 画面は b6ui)</t>
         </is>
       </c>
     </row>
@@ -10906,15 +11410,19 @@
           <t>ナレッジ間のリンク構造が反映され、参照元 (バックリンク) が一覧に出る</t>
         </is>
       </c>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L170" t="inlineStr"/>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J35-06.png</t>
+        </is>
+      </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>グラフビュー描画=true (「ナレッジ 4 件と 0 本のリンク」), API graph に親子リンク=true タグ共起=true; 1 件選択で参照元 (GET references=200, total=0: チャット RAG 消費が無いため 0 件表示) 画面節=「バックリンク（0） / まだ参照されていません / アクション / Obsidian Vault に書出 / 共通ナレッジに昇格 / 削除」</t>
         </is>
       </c>
     </row>
@@ -10968,15 +11476,19 @@
           <t>何で動いていて誰の費用かが出る。準備を押すと状態が処理中に遷移し、完了後に検索で引ける</t>
         </is>
       </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L171" t="inlineStr"/>
+      <c r="K171" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J35-07.png</t>
+        </is>
+      </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>状態カードに何で動くか/費用=表示あり (意味検索は使えません（キーワード一致のみ） / 費用なし /  / 意味検索の部品 (fastembed) がこのサーバーに入っていません (キーワード一致のみ) /  / 埋め込); 「再試行する」押下 → 処理中に遷移=true, 完了 (ready)=false: サーバーに fastembed が無く provider=none/unavailable のまま (G-11: 本番に意味検索の部品が未導入)。検索はキーワード一致で 0 件</t>
         </is>
       </c>
     </row>
@@ -11030,15 +11542,19 @@
           <t>選んだ社員/案件のナレッジだけが一覧に出る</t>
         </is>
       </c>
-      <c r="K172" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L172" t="inlineStr"/>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J35-08.png</t>
+        </is>
+      </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>S-K01 スコープ「AI社員別」→ tony のグループに社員専用ナレッジだけ=true; 「プロジェクト別」→ 本案件の見出し下に案件固有だけ=true; 「共通」に社員/案件固有は混ざらない=true; API: employee_specific=["tony 専用: デプロイ手順"] source_project_id=["案件固有: 顧客の禁止ワード"] 別案件=[]</t>
         </is>
       </c>
     </row>
@@ -11092,15 +11608,19 @@
           <t>編集が反映され updated_at が更新される。削除で一覧から消え、再読み込みしても復活しない</t>
         </is>
       </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr"/>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>PATCH 本文 → 再取得で反映=True, updated_at 05:20:08→05:20:48 更新=True; DELETE → GET /knowledge/{id}=404, 再取得の一覧から消える=True</t>
         </is>
       </c>
     </row>
@@ -11153,15 +11673,19 @@
           <t>zip に RLS で見える分だけが含まれ、他ワークスペースの分は含まれない状態である</t>
         </is>
       </c>
-      <c r="K174" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L174" t="inlineStr"/>
+      <c r="K174" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>zip 4 entries (自 WS のナレッジ 3 件含む), 別 WS の「別WSの秘密ナレッジ」混入=false; 別 WS を account_id に指定した export → 200 / entries=0</t>
         </is>
       </c>
     </row>
@@ -11215,15 +11739,19 @@
           <t>種別ごとに該当が一覧に出る。他ワークスペースのものは 1 件も出ない</t>
         </is>
       </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L175" t="inlineStr"/>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-07.png</t>
+        </is>
+      </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>案件名の一部 "Nebula" → project/task が種別つきで出る、本文にしか無い語 "ZEPHYRWORD-A2" → knowledge「Aurora」、"トニー" → employee。別テナント (別ユーザーの WS) の案件/タスク/ナレッジ語 "XTENANT-SECRET-ORION" は API・画面とも 0 件 (R-T08)</t>
         </is>
       </c>
     </row>
@@ -11276,15 +11804,19 @@
           <t>0 件の案内が出る状態になり、壊れない</t>
         </is>
       </c>
-      <c r="K176" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L176" t="inlineStr"/>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-08.png</t>
+        </is>
+      </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>存在しない語で検索 → GET /search 200 / 0 件、画面は「ヒットなし」の案内を出し JS エラー無し (壊れない)</t>
         </is>
       </c>
     </row>
@@ -11342,7 +11874,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L177" t="inlineStr"/>
       <c r="M177" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -11404,7 +11935,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -11465,7 +11995,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L179" t="inlineStr"/>
       <c r="M179" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -11527,7 +12056,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L180" t="inlineStr"/>
       <c r="M180" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -11588,7 +12116,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L181" t="inlineStr"/>
       <c r="M181" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -11649,7 +12176,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -11710,7 +12236,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr"/>
       <c r="M183" t="inlineStr">
         <is>
           <t>場所=cloud</t>
@@ -11766,15 +12291,19 @@
           <t>実行できる種類とコストが一覧に出て、画面表示が GET /cron-actions と一致した状態である</t>
         </is>
       </c>
-      <c r="K184" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr"/>
+      <c r="K184" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-01.png</t>
+        </is>
+      </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 画面表示が GET /cron-actions と一致 / 実測: 一覧・コストは出るが、作成フォーム (ScheduleBuilder) の種類名・コスト表示は画面側のハードコード (ACTIONS 定数) で、API の title (例 API「タスク自動再生」↔ 画面「着手可のタスクを再生する」) / cost_label (API「本人の Claude プラン枠」「コスト無料」↔ 画面「プラン枠」「無料」) と 6 種中 4 種で文言不一致。GET /cron-actions は取得されるが作成フォームには反映されていない (GAP-179 の「唯一の信頼源」に反する)</t>
         </is>
       </c>
     </row>
@@ -11827,15 +12356,19 @@
           <t>一覧に出て、有効の状態で次回実行が予定される</t>
         </is>
       </c>
-      <c r="K185" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L185" t="inlineStr"/>
+      <c r="K185" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-02.png</t>
+        </is>
+      </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI 作成 → POST 201、一覧 0→1 件、enabled=true、next_run_at=2026-09-03T06:00:00Z (cron 0 * * * *) が画面「次回」にも出る</t>
         </is>
       </c>
     </row>
@@ -11888,15 +12421,19 @@
           <t>日本語のエラーで拒否され、一覧に増えない</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L186" t="inlineStr"/>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-03.png</t>
+        </is>
+      </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI: POST 422 画面エラー=["入力内容を確認してください: 分は 0〜59 で指定してください: '99'"] / API: '99 99 * * *'→422 {"detail":"分は 0〜59 で指定してください: '99'"} 'not a cron'→422 / 一覧 1→1 件 (増えない)</t>
         </is>
       </c>
     </row>
@@ -11950,15 +12487,19 @@
           <t>無効の間は次回実行が予定されない状態になる。有効化で予定が戻る</t>
         </is>
       </c>
-      <c r="K187" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr"/>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-04.png</t>
+        </is>
+      </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>無効化 → enabled=false next_run_at=null / 有効化 → enabled=true next_run_at=2026-09-03T06:00:00Z</t>
         </is>
       </c>
     </row>
@@ -12011,15 +12552,19 @@
           <t>実行日時・結果が一覧に出る。0 件なら 0 件の状態で出る</t>
         </is>
       </c>
-      <c r="K188" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr"/>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-06.png</t>
+        </is>
+      </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>GET /cron-runs 1 件 (QA-C 日次ダイジェスト:success:2026-09-03T05:25:59.649543Z) / 画面「実行履歴（直近 1 件）」に日時・結果が出る</t>
         </is>
       </c>
     </row>
@@ -12072,15 +12617,19 @@
           <t>read-only の状態で出て、編集・削除の導線が無い</t>
         </is>
       </c>
-      <c r="K189" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L189" t="inlineStr"/>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-07.png</t>
+        </is>
+      </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>必須ジョブ (required=true) 2 件「退会データを 30 日後に完全削除」「データ整合性チェック」が「無効化不可」で read-only 表示、セクション内に編集・削除・トグルの操作要素 0 個、PATCH/DELETE 用 endpoint も無し。API には required=false の運用ジョブ 3 件 (利用者スケジュールの発火 (滑り止め) / エラー通知 (メール / Slack) / 議事録 transcription キュー消費) もあり、こちらは画面に出ない</t>
         </is>
       </c>
     </row>
@@ -12133,15 +12682,19 @@
           <t>403 で拒否され、一覧にそのまま残る</t>
         </is>
       </c>
-      <c r="K190" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L190" t="inlineStr"/>
+      <c r="K190" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-08.png</t>
+        </is>
+      </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>member DELETE → 403 {"detail":"自動実行の予定を削除できるのはオーナーだけです。"}; owner 一覧に残存=true (member 一覧 1 件・member 画面の削除ボタン 1 個)</t>
         </is>
       </c>
     </row>
@@ -12194,15 +12747,19 @@
           <t>一覧から消え、次回実行の予定も消えた状態になる</t>
         </is>
       </c>
-      <c r="K191" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L191" t="inlineStr"/>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-09.png</t>
+        </is>
+      </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI 削除 (2 段階確認) → DELETE 204、GET detail 404、一覧 0 件、画面は「スケジュールされたジョブはありません」(トグル/削除ボタン 0 個 = 次回予定も消えた)。実行履歴には過去の実行として名前が残る (履歴の保持は正しい)</t>
         </is>
       </c>
     </row>
@@ -12256,15 +12813,19 @@
           <t>招待が一覧に出て、相手に招待メールが届く (実送信できない環境では送信ログ/キュー投入で代替)。DB に表示名・期限・scope が記録され、監査ログ client_invited が記録される</t>
         </is>
       </c>
-      <c r="K192" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L192" t="inlineStr"/>
+      <c r="K192" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>一覧・DB 記録は満たす (S-L01 から発行 → POST 201 → 一覧に行 (未使用/残り 7 日/表示名), GET 詳細で display/expires_at/scopes 再取得一致, 招待リンクは発行時のみ画面表示)。招待メール『届く』は観測不能: 応答に送信結果の key 無し・Resend 送信ログを見る API 無し・監査ログ (client_invited) は admin 専用。解除条件: 送信ログ/送信キューの照会手段 or admin 監査ログ閲覧</t>
         </is>
       </c>
     </row>
@@ -12319,15 +12880,19 @@
           <t>クライアント画面 (S-L03) に遷移する。client_portal role の別 JWT が社内用とは別の cookie で発行された状態になる。監査ログ client_signed_in と同意記録が残る</t>
         </is>
       </c>
-      <c r="K193" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr"/>
+      <c r="K193" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>招待リンク → 表示名入力 + 同意 2 種 → /portal?project=PE1 (S-L03) に遷移。cookie は atelier_client_access のみ (社内 atelier_access 混在なし)。client JWT claims: role=client_portal aud=client sub=client:&lt;inv&gt; project_id/scopes 付き (社内 JWT は role=authenticated aud=authenticated)。招待 used_at/use_count が増える。監査ログ client_signed_in と同意記録は admin 専用で未確認</t>
         </is>
       </c>
     </row>
@@ -12380,15 +12945,19 @@
           <t>拒否される。セッションも同意記録も DB に作られない</t>
         </is>
       </c>
-      <c r="K194" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L194" t="inlineStr"/>
+      <c r="K194" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>同意なし→422 / 片方のみ→422 で拒否。招待の used_at/use_count は不変 (used_at=None)。セッション (client token) は発行されない。同意記録は DB 直接照会不可のため『作られない』は API 応答 (422 で処理前に拒否) から判定</t>
         </is>
       </c>
     </row>
@@ -12442,15 +13011,19 @@
           <t>案件名と招待者だけが出て、成果物は出ない状態である。レート制限を超えると拒否される</t>
         </is>
       </c>
-      <c r="K195" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L195" t="inlineStr"/>
+      <c r="K195" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>preview 200 の中身は project_name/workspace_name/inviter_name/invited_email/expires_at/remaining_days のみ (成果物・モック名なし)。連続 14 回で 10 回目から 429『短い間に操作が集中しています…』(10/min/ip)</t>
         </is>
       </c>
     </row>
@@ -12504,15 +13077,19 @@
           <t>トークンがローテーションされ新リンクがメールで届く (実送信できない環境では送信ログ/キュー投入で代替)。旧リンクは無効になる</t>
         </is>
       </c>
-      <c r="K196" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L196" t="inlineStr"/>
+      <c r="K196" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>resend が 409: {"detail": "この招待はすでに使われたか、取り消されています。"}</t>
         </is>
       </c>
     </row>
@@ -12565,15 +13142,19 @@
           <t>有効/失効/期限切れの状態と期限が一覧に反映され、詳細と一致する</t>
         </is>
       </c>
-      <c r="K197" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L197" t="inlineStr"/>
+      <c r="K197" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>PE1 の招待 7 件すべて一覧=詳細 (expires_at/used_at/revoked_at/use_count/scopes 一致)。S-L01 は未使用/失効を状態 pill と有効期限 (残り n 日 / 終了日) で表示し履歴に失効行が移る。API 応答に status 列は無く UI が導出 (期限切れは J24-01 の理由で作れず未観測)</t>
         </is>
       </c>
     </row>
@@ -12626,15 +13207,19 @@
           <t>自分の案件の工程進捗・運営・リンク有効期限が出る。社内専用の情報 (原価/他案件/内部メモ) が出ない状態である</t>
         </is>
       </c>
-      <c r="K198" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L198" t="inlineStr"/>
+      <c r="K198" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>GET /client/projects/PE1 + overview 200: 工程 9 (ヒアリング in_progress…) progress 0%, 運営 QA-E2-W1 · QA-E2 社内A, link_expires_at + 残り 3 日。S-L03 も同内容。原価/粗利/社内メモ/他案件名 (P2/P3/PX) の混入なし</t>
         </is>
       </c>
     </row>
@@ -12687,15 +13272,19 @@
           <t>工程ごとの最新版だけが一覧に出る。旧版と社内コメントは出ない</t>
         </is>
       </c>
-      <c r="K199" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L199" t="inlineStr"/>
+      <c r="K199" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>outputs 2 件 = requirements v2 (v1 は出ない) + delivery v1。社内コメント (原価メモ) はクライアントの comments 一覧に出ない (0 件)</t>
         </is>
       </c>
     </row>
@@ -12748,15 +13337,19 @@
           <t>画面ごとの最新版だけが一覧に出る</t>
         </is>
       </c>
-      <c r="K200" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L200" t="inlineStr"/>
+      <c r="K200" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>mocks 1 件 = 画面1 の v2 のみ (v1 a2aabca4… は出ない)</t>
         </is>
       </c>
     </row>
@@ -12809,15 +13402,19 @@
           <t>0 件の案内が出る状態になり、エラーにならない</t>
         </is>
       </c>
-      <c r="K201" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr"/>
+      <c r="K201" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>PE2 (成果物 0) で /, overview, outputs [], mocks {items:[],total_screens:0}, comments [] すべて 200。S-L03 に『共有された成果物はまだありません』『共有されたモックはまだありません』が出てエラー表示なし</t>
         </is>
       </c>
     </row>
@@ -12870,15 +13467,19 @@
           <t>招待者に更新のメールが届く (実送信できない環境では送信ログ/キュー投入で代替)。監査ログ client_notified_of_update が記録される</t>
         </is>
       </c>
-      <c r="K202" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L202" t="inlineStr"/>
+      <c r="K202" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>場所=cloud / F-CUC03</t>
+          <t>期待: 成果物の新版で招待者に更新メール + 監査ログ client_notified_of_update / 実測: 新版 (要件定義 v3) 作成は 200 だが、更新通知メールを送る実装が API に存在しない (ResendSender の呼出箇所に成果物更新が無い)。観測できる送信痕跡も無し。T-F-17 未実装扱い</t>
         </is>
       </c>
     </row>
@@ -12932,15 +13533,19 @@
           <t>参照も投稿も拒否される。1 件も他人の情報が出ない状態で、拒否が記録される</t>
         </is>
       </c>
-      <c r="K203" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L203" t="inlineStr"/>
+      <c r="K203" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08 致命級。ここが破れたら公開不可</t>
+          <t>CT1→PX 5 GET + POST comment 全 403、CTX→PE1 5 GET + POST 全 403、自案件パスに他社 mock target は 404 (存在秘匿)。拒否本文に相手案件名なし。他社側コメント 0 件。拒否の監査記録は admin 専用で未確認</t>
         </is>
       </c>
     </row>
@@ -12993,15 +13598,19 @@
           <t>拒否される (RLS で 0 件 / 401)。系統をまたげない状態である</t>
         </is>
       </c>
-      <c r="K204" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L204" t="inlineStr"/>
+      <c r="K204" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>クライアント券で社内 API 9 本 (projects/outputs/mocks/comments/workspaces/me/client-invitations) 全て 401。系統をまたげない</t>
         </is>
       </c>
     </row>
@@ -13055,15 +13664,19 @@
           <t>403 で拒否され、コメントは増えない</t>
         </is>
       </c>
-      <c r="K205" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L205" t="inlineStr"/>
+      <c r="K205" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>scope=view の券で投稿 → 403 拒否、コメント数 0→0 で増えない。閲覧 (outputs) は 200</t>
         </is>
       </c>
     </row>
@@ -13116,15 +13729,19 @@
           <t>拒否される。社内 cookie がクライアント画面で流用されない状態である</t>
         </is>
       </c>
-      <c r="K206" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L206" t="inlineStr"/>
+      <c r="K206" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>owner A / 他社 owner B / 別 WS owner C の社内 JWT で /client/projects/PE1 5 GET + POST comment 全 401。社内 cookie (atelier_access) のみのブラウザで /portal?project=PE1 → /portal/signin へ redirect、client API 呼出 0 件、案件画面は出ない</t>
         </is>
       </c>
     </row>
@@ -13177,15 +13794,19 @@
           <t>コメントが自分の画面の一覧に出る。担当者に通知メールが届く (実送信できない環境では送信ログ/キュー投入で代替)。監査ログ comment_created が記録される</t>
         </is>
       </c>
-      <c r="K207" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr"/>
+      <c r="K207" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 一覧に出る + 担当者に通知メール + 監査ログ comment_created / 実測: POST /client/projects/PE1/comments 201、自分の一覧に出る (is_client_author=true) は OK。しかし担当者への通知メールを送る実装が API に無い (services/client_signin・comments に Resend/notify 呼出なし, grep 0 件) → 送信痕跡も無し。監査ログは admin 専用で未確認</t>
         </is>
       </c>
     </row>
@@ -13238,15 +13859,19 @@
           <t>クライアントのコメントが誰のものか分かる形で出ている。ダッシュボードの未解決件数が 1 増える</t>
         </is>
       </c>
-      <c r="K208" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L208" t="inlineStr"/>
+      <c r="K208" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>社内 GET /comments?target=要件定義v2 にクライアント投稿が author_name=QAクライアントE2-1 / is_client_author=true / author_invitation_id 付きで出る。/outputs?output=… の UI でも投稿者名と『クライアント』表記あり。GET /comments/unresolved-count が 1→2 (+1)、/projects/dashboard に『未解決コメント』表示</t>
         </is>
       </c>
     </row>
@@ -13301,15 +13926,19 @@
           <t>自分のものは編集・削除が反映される。他人のものは拒否される</t>
         </is>
       </c>
-      <c r="K209" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr"/>
+      <c r="K209" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 自分のコメントは編集・削除できる / 実測: クライアント用の編集・削除 endpoint が無い (PATCH/DELETE /client/projects/{id}/comments/{id} → 404 Not Found、社内 PATCH/DELETE /comments/{id} は client 券で 401)。S-L03 にも編集/削除ボタン 0 個。他人 (社内メモ) の編集は 401 で拒否され content 不変 (こちらは OK)</t>
         </is>
       </c>
     </row>
@@ -13362,15 +13991,19 @@
           <t>返信がクライアント側の一覧に出る</t>
         </is>
       </c>
-      <c r="K210" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr"/>
+      <c r="K210" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>社内 A が parent_comment_id=CC1 で返信 201 → クライアント GET comments に返信が author_name=QA-E2 社内A / is_client_author=false で出る (2 件)。社内メモの混入なし。S-L03 でも返信文が表示</t>
         </is>
       </c>
     </row>
@@ -13423,15 +14056,19 @@
           <t>入れず、期限切れであることが日本語で分かる。セッションは作られない (DB に増えない)</t>
         </is>
       </c>
-      <c r="K211" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L211" t="inlineStr"/>
+      <c r="K211" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期限切れ招待を作る手段が無い: ttl_days は 1〜30 (0/-1 は 422)、body の expires_at は無視され 201 (既定 7 日)、DB 直接更新は本環境から不可。解除条件: DB で expires_at を過去にする (scripts) か 1 日待つ。付記: expires_at を黙って無視する (422 にしない) のは要観点</t>
         </is>
       </c>
     </row>
@@ -13485,15 +14122,19 @@
           <t>1 クリック目では失効しない。確定後はリンクで入れず、一覧が失効として反映される。監査ログ invitation_revoked が記録される</t>
         </is>
       </c>
-      <c r="K212" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L212" t="inlineStr"/>
+      <c r="K212" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>S-L01 で『失効』1 クリック目は revoke API 呼出なし・revoked_at=null のまま、『失効する』確定で POST revoke 200 → revoked_at 記録・一覧が履歴 (失効) へ。旧リンクで signin → 401『この招待は取り消されています…』。監査ログ invitation_revoked は admin 専用で未確認</t>
         </is>
       </c>
     </row>
@@ -13547,15 +14188,19 @@
           <t>相手はその場で拒否され (401)、案件名・モック名が画面に残らない。「失効させたのにしばらく見られる」状態にならない</t>
         </is>
       </c>
-      <c r="K213" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L213" t="inlineStr"/>
+      <c r="K213" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>場所=cloud / G-12 / G-14</t>
+          <t>API: 失効 +0.42s で /, overview, outputs, mocks, comments, POST comment 全 401『この招待は取り消されています…』、旧リンク再 signin 401。UI: サインイン済み S-L03 で失効直後にコメント投稿 → 401、reload (+6s) → 401 で案件名・モック名・成果物名が画面に残らない。付記: 失効文言と並んで『通信エラーが発生しました』の汎用トーストも同時に出る (誤解を招く文言)</t>
         </is>
       </c>
     </row>
@@ -13610,15 +14255,19 @@
           <t>直前は操作できる。直後は拒否され、一覧の状態が期限切れに遷移する</t>
         </is>
       </c>
-      <c r="K214" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr"/>
+      <c r="K214" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>場所=cloud / G-12</t>
+          <t>expires_at を 1 分後にする手段が無い (ttl_days 最小 1 日、expires_at は無視、DB 更新不可)。解除条件: DB 直接更新 or ttl_minutes 相当の QA 用手段</t>
         </is>
       </c>
     </row>
@@ -13672,15 +14321,19 @@
           <t>30 日カウントダウンつきで一覧から消える (deleted_at が記録)。その案件のクライアント招待は無効化され、監査ログ project_deleted が記録される</t>
         </is>
       </c>
-      <c r="K215" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L215" t="inlineStr"/>
+      <c r="K215" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-03.png</t>
+        </is>
+      </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 30 日カウントダウンつきで一覧から消え (deleted_at 記録)、クライアント招待が無効化、監査 project_deleted / 実測: 設定の危険な操作から削除 (DELETE 204) でアクティブ一覧から消え include_deleted で deleted_at=2026-09-03T05:23:54Z。削除後の招待 token は POST /client/auth/preview 401 (削除前は 200) で無効化 (ただし GET 招待の revoked_at は null のまま = 暗黙無効)。不足: 削除後に「残り N 日」のカウントダウンや削除済み一覧が画面のどこにも無い (30 日の文言は削除前の確認ダイアログのみ)。監査 project.delete は削除後ダッシュボードが 404 で観測不可</t>
         </is>
       </c>
     </row>
@@ -13733,15 +14386,19 @@
           <t>元の状態に戻り、成果物・タスク・コメントが残っている</t>
         </is>
       </c>
-      <c r="K216" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L216" t="inlineStr"/>
+      <c r="K216" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-04.png</t>
+        </is>
+      </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 削除済み一覧から復元し、元の状態に戻り成果物・タスク・コメントが残る / 実測: 画面 (/projects) に削除済み一覧も復元ボタンも無く、利用者は画面から復元できない。API POST /projects/{id}/restore は 200 で deleted_at が消えて一覧に戻り、タスク「QA jA2 タスク Nebula-TASK-1」とコメントは残っている (データ面は正)</t>
         </is>
       </c>
     </row>
@@ -13796,15 +14453,19 @@
           <t>復元できず、案件データが削除される。ナレッジは匿名化されて残る</t>
         </is>
       </c>
-      <c r="K217" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L217" t="inlineStr"/>
+      <c r="K217" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>journeys-A-prod-20260903.txt#J38-05</t>
+        </is>
+      </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>deleted_at を 31 日前に書き換える DB 直接操作と日次ジョブの手動起動が本番では不可 / 解除条件: staging で DB 書換権限 + purge ジョブの手動起動手段</t>
         </is>
       </c>
     </row>
@@ -13857,15 +14518,19 @@
           <t>拒否され、案件の情報が見えなくなる</t>
         </is>
       </c>
-      <c r="K218" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L218" t="inlineStr"/>
+      <c r="K218" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>場所=cloud / G-14</t>
+          <t>PE3 に招待 INV5 でサインイン済み (outputs 1 件 200) → A が DELETE /projects/PE3 204 (GET は 404) → 同じ券で 5 GET 全 401、招待リンクの再 signin 401、preview 401。応答に案件名 (QA-E2-P3/削除試験) の混入なし</t>
         </is>
       </c>
     </row>
@@ -13918,15 +14583,19 @@
           <t>「本人の PC が未接続」の状態と接続の導線が出る。未設定と混同しない</t>
         </is>
       </c>
-      <c r="K219" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L219" t="inlineStr"/>
+      <c r="K219" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J40-01.png</t>
+        </is>
+      </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-168/206</t>
+          <t>GET /chat/connection-status mode=relay bridge_online=false; チップ「プラン未接続 — ここから接続」(「AI 未接続 (unconfigured)」とは別文言) → パネルに接続手順 + 「接続トークンを発行」導線</t>
         </is>
       </c>
     </row>
@@ -13979,15 +14648,19 @@
           <t>接続済みの状態が画面に反映される。GET /bridge/status に presence が記録される</t>
         </is>
       </c>
-      <c r="K220" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L220" t="inlineStr"/>
+      <c r="K220" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J40-02</t>
+        </is>
+      </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>本人の PC を Bridge で繋ぐ (場所=mac)。cloud には Bridge ハーネスが無い / 解除条件: Mac で Bridge を起動し GET /bridge/status に presence が出ること</t>
         </is>
       </c>
     </row>
@@ -14040,15 +14713,19 @@
           <t>利用者自身の契約で動くことが実行前に表示された状態である (接続状態は実測値のみ)</t>
         </is>
       </c>
-      <c r="K221" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L221" t="inlineStr"/>
+      <c r="K221" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J40-03</t>
+        </is>
+      </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-178</t>
+          <t>接続後の経路表示 (場所=mac)。未接続時の表示は J40-01 で PASS (「プラン未接続 — ここから接続」)。接続済み時の「自分の Claude プランで実行」表示は Bridge 接続が要る / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -14102,15 +14779,19 @@
           <t>raw トークンが 1 度だけ表示され、一覧に出る。再読み込み後は二度と出ない</t>
         </is>
       </c>
-      <c r="K222" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L222" t="inlineStr"/>
+      <c r="K222" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J40-04.png</t>
+        </is>
+      </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: raw が 1 度だけ表示され一覧に出る・再読み込み後は出ない / 実測: UI「接続トークンを発行」→ POST 201 で raw (43 文字) が発行直後の画面に 1 度表示され、再読み込み後は画面に出ず GET /bridge-tokens にも raw 無し (ここは期待通り)。しかし「一覧に出る」が不安定: 発行 3 秒後の GET /bridge-tokens が 200 {data:[]} (発行済みトークンが 0 件) で返り、その後 20 回連続 GET で 2 回 (10%) が 500「サーバー側で問題が発生しました（参照 ID 付き）」。同じ本人・同じ条件で件数 0 / 3 / 500 が揺れる (list_tokens が別プール _service_session を使う経路の不安定さと推定)</t>
         </is>
       </c>
     </row>
@@ -14164,15 +14845,19 @@
           <t>接続が切れ、表示が即時 (0 秒) で未接続の状態に遷移する。90 秒間の「接続中」誤表示が無い</t>
         </is>
       </c>
-      <c r="K223" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L223" t="inlineStr"/>
+      <c r="K223" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J40-05</t>
+        </is>
+      </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>場所=mac / G-12 / G-14</t>
+          <t>トークン失効 → 接続が即時 (0 秒) に切れるか (場所=mac / G-12 / G-14)。API の失効 (POST revoke → 200, revoked_at 記録) は J40-07 の後片付けで実測済だが、接続中の Bridge が無いので「切れる・90 秒誤表示なし」は判定不能 / 解除条件: Mac の Bridge を繋いだ状態で失効</t>
         </is>
       </c>
     </row>
@@ -14230,7 +14915,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -14287,15 +14971,19 @@
           <t>接続状態が即時に未接続へ遷移する。その間の送信は 3 分無応答にならず、未接続の案内が出る</t>
         </is>
       </c>
-      <c r="K225" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr"/>
+      <c r="K225" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J40-06</t>
+        </is>
+      </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>場所=mac / G-12 GAP-243</t>
+          <t>Bridge 終了 (bye) 直後の表示遷移 (場所=mac / G-12 GAP-243)。未接続のまま送った場合は ≦6 秒で未接続 alert が出る (J43-03 で実測、3 分無応答ではない) / 解除条件: Mac の Bridge を起動→終了</t>
         </is>
       </c>
     </row>
@@ -14353,7 +15041,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr"/>
       <c r="M226" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -14409,15 +15096,19 @@
           <t>本人以外のトークンは一覧に出ず、失効も拒否される</t>
         </is>
       </c>
-      <c r="K227" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr"/>
+      <c r="K227" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J40-07</t>
+        </is>
+      </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>member GET /bridge-tokens ×3 → [200, 200, 200] いずれも owner のトークン id を含まず自分の分だけ (3/3 回に自分の id); member POST revoke(owner id) → 404 {"detail": "対象の接続トークンが見つかりません。"}; owner 再取得で revoked_at=None (失効せず)</t>
         </is>
       </c>
     </row>
@@ -14475,7 +15166,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr"/>
       <c r="M228" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -14536,7 +15226,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr"/>
       <c r="M229" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -14598,7 +15287,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L230" t="inlineStr"/>
       <c r="M230" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -14660,7 +15348,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L231" t="inlineStr"/>
       <c r="M231" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -14721,7 +15408,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr"/>
       <c r="M232" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -14782,7 +15468,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr"/>
       <c r="M233" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -14843,7 +15528,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L234" t="inlineStr"/>
       <c r="M234" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -14904,7 +15588,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L235" t="inlineStr"/>
       <c r="M235" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -14965,7 +15648,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L236" t="inlineStr"/>
       <c r="M236" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -15026,7 +15708,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L237" t="inlineStr"/>
       <c r="M237" t="inlineStr">
         <is>
           <t>場所=mac / G-15</t>
@@ -15087,7 +15768,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L238" t="inlineStr"/>
       <c r="M238" t="inlineStr">
         <is>
           <t>場所=mac / G-15</t>
@@ -15144,15 +15824,19 @@
           <t>応答がストリームで返り、DB にメッセージが記録される。オウム返しや定型文でない</t>
         </is>
       </c>
-      <c r="K239" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L239" t="inlineStr"/>
+      <c r="K239" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-01</t>
+        </is>
+      </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>AI 応答が要る (場所=mac)。スレッド作成・ユーザー発話の DB 記録 (POST messages → 201, GET messages に残る) は J41-08 の準備で実測済 / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -15206,15 +15890,19 @@
           <t>仕込んだ固有名を踏まえて答える (F-CTX01 が DB の最新を反映)。知らないまま喋らない</t>
         </is>
       </c>
-      <c r="K240" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L240" t="inlineStr"/>
+      <c r="K240" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-02</t>
+        </is>
+      </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>AI 応答が要る (場所=mac)。文脈への DB 最新反映 (F-CTX01) は J41-14 の context-preview で実測 / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -15268,15 +15956,19 @@
           <t>説明し直さずに解決する。会話の記録が 3 ターン分残る</t>
         </is>
       </c>
-      <c r="K241" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L241" t="inlineStr"/>
+      <c r="K241" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-03</t>
+        </is>
+      </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>AI 応答が要る (場所=mac) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -15330,15 +16022,19 @@
           <t>画面と DB の両方に実体がある (三層で保存)。会話だけで終わらない</t>
         </is>
       </c>
-      <c r="K242" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L242" t="inlineStr"/>
+      <c r="K242" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-04</t>
+        </is>
+      </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-139</t>
+          <t>成果物生成に AI 応答が要る (場所=mac / GAP-139) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -15391,15 +16087,19 @@
           <t>指示した箇所以外の作り込みが保たれる。新版として記録され旧版が残る</t>
         </is>
       </c>
-      <c r="K243" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L243" t="inlineStr"/>
+      <c r="K243" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-05</t>
+        </is>
+      </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-147 回帰</t>
+          <t>部分改訂に AI 応答が要る (場所=mac / GAP-147) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -15453,15 +16153,19 @@
           <t>添付ありでは中身に基づき答え、添付なしでは作り話をしない。添付は Storage に記録される</t>
         </is>
       </c>
-      <c r="K244" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L244" t="inlineStr"/>
+      <c r="K244" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-06</t>
+        </is>
+      </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-161</t>
+          <t>添付の読解に AI 応答が要る (場所=mac / GAP-161) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -15516,15 +16220,19 @@
           <t>各操作がスレッド一覧に反映され、削除したスレッドは復活しない</t>
         </is>
       </c>
-      <c r="K245" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L245" t="inlineStr"/>
+      <c r="K245" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J41-07.png</t>
+        </is>
+      </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI 新規スレッド (案件/社員/工程を選んで作成) → POST 201「新しい会話 9/3 14:48」が一覧に出る / 名前変更 (鉛筆 → 入力 → 保存) → PATCH 200、再取得 title=QA-C 改名スレッド・一覧反映 / 削除 (「削除しますか？ はい/いいえ」) → DELETE 204、GET detail 404、再読み込み後の一覧 (GET /chat/threads・include_archived=true とも) に削除 id は無い = 復活しない (退会前の owner・member 双方の JWT で再取得して確認)。※ 再読み込み後に同名「QA-C 改名スレッド」が見えたのは前回試行で工程スレッドを誤改名した別 id (後片付けで元に戻した)</t>
         </is>
       </c>
     </row>
@@ -15578,15 +16286,19 @@
           <t>採用したものだけが正式なナレッジとして一覧に出る。却下したものは同じ題で再提案されない</t>
         </is>
       </c>
-      <c r="K246" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L246" t="inlineStr"/>
+      <c r="K246" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>evidence/journeys-B-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>候補は AI が会話から拾う (J41-01, Bridge 要)。GET /knowledge/candidates pending=0 件で採用/却下の対象が無い / 解除条件: Mac の Bridge ハーネスで AI チャットを実行し候補を発生させる</t>
         </is>
       </c>
     </row>
@@ -15639,15 +16351,19 @@
           <t>履歴がコピーされた新スレッドが一覧に出て、元スレッドとの親子関係が記録される</t>
         </is>
       </c>
-      <c r="K247" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L247" t="inlineStr"/>
+      <c r="K247" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J41-08.png</t>
+        </is>
+      </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>POST branch (2 件目時点) → 201 (1 回目は断続 500、再試行で成功); 新スレッド「分岐: QA-C 相談スレッド」が一覧 (API・画面カード) に出て、履歴 3/4 件 (分岐点まで) がコピー、3 件目は中央ペインに出ない; 元との関係は title 接頭辞「分岐:」+ コピー側メッセージの parent_message_id (3/3 件) で記録。スレッド自体に parent_thread_id 欄は無い (どのスレッドから分岐したかは title でしか辿れない)。画面の「分岐」ボタンは assistant 発話にしか出ないため (AI 無し) API で分岐</t>
         </is>
       </c>
     </row>
@@ -15700,15 +16416,19 @@
           <t>フィードバックが監査ログに記録される</t>
         </is>
       </c>
-      <c r="K248" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L248" t="inlineStr"/>
+      <c r="K248" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-09</t>
+        </is>
+      </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>up/down とも POST → 201 (feedback_id/recorded_at 返却) だが、監査ログは運営 API (/admin/audit-logs) でしか読めず、dashboard.recent_activities (project/task 対象: task.impact.apply,task.impact.analyze,task.update,task.create) にも出ないため「監査ログに記録」は未観測 / 解除条件: 運営アカウントで /admin/audit-logs を読む。所見: 画面の導線は「役立った」(up) のみで「悪い」(down) が無い (API は down を受ける)。AI 応答が無いので画面のボタン自体も出ない (assistant 発話限定)</t>
         </is>
       </c>
     </row>
@@ -15762,15 +16482,19 @@
           <t>追い足しがキューに出る。取り消した 1 件は消え、残りが応答の中に反映される</t>
         </is>
       </c>
-      <c r="K249" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L249" t="inlineStr"/>
+      <c r="K249" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-10</t>
+        </is>
+      </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-189/191</t>
+          <t>実行中の追い足しには走っている実行が要る (場所=mac / GAP-189/191) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -15829,7 +16553,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr"/>
       <c r="M250" t="inlineStr">
         <is>
           <t>場所=mac / F-CUC02</t>
@@ -15885,15 +16608,19 @@
           <t>切替が捨てられず、次のツール実行から承認が要る状態に遷移する</t>
         </is>
       </c>
-      <c r="K251" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L251" t="inlineStr"/>
+      <c r="K251" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-11</t>
+        </is>
+      </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>場所=mac / G-13</t>
+          <t>実行中のモード切替には走っている実行が要る (場所=mac / G-13) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -15947,15 +16674,19 @@
           <t>走っている実行に繋ぎ直され、途中からの応答が反映される</t>
         </is>
       </c>
-      <c r="K252" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L252" t="inlineStr"/>
+      <c r="K252" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-12</t>
+        </is>
+      </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-189</t>
+          <t>実行への再接続には走っている実行が要る (場所=mac / GAP-189) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16008,15 +16739,19 @@
           <t>コマンドとして解釈され、結果が構造化して記録される</t>
         </is>
       </c>
-      <c r="K253" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L253" t="inlineStr"/>
+      <c r="K253" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-13</t>
+        </is>
+      </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-002</t>
+          <t>/コマンドの構造化実行に AI 実行が要る (場所=mac / GAP-002) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16069,15 +16804,19 @@
           <t>7 層の文脈が LLM 呼出なしで出て、DB の最新値が反映されている</t>
         </is>
       </c>
-      <c r="K254" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L254" t="inlineStr"/>
+      <c r="K254" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-14</t>
+        </is>
+      </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>場所=cloud / F-CTX01</t>
+          <t>POST context-preview → 200 (0.8 秒・LLM 呼出なし)。system_prompt は persona(+skills) / 現在のプロジェクト (name・種別・状態) / 進行フロー (現在ステージ) の 3 ブロック + history_count=4 (会話履歴は別枠)、template/peers/summary/attachments/rag は該当データ無しで省略 (build_context の 9 部品のうち条件付き)。DB 最新: project.name を変えた直後の再プレビューに反映=True、戻すと消える。所見: project.description は文脈に含まれない (合言葉を description に入れても反映されない) — 「案件にしか無い固有名」を description に書く運用だと J41-02 が効かない。画面には実行中の「F-CTX01 文脈サマリ」チップしか無く、実行なしのプレビュー導線は無い</t>
         </is>
       </c>
     </row>
@@ -16130,15 +16869,19 @@
           <t>エラー応答が記録され、利用者に通知される。無限に待たない</t>
         </is>
       </c>
-      <c r="K255" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L255" t="inlineStr"/>
+      <c r="K255" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-15</t>
+        </is>
+      </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>場所=mac / G-15</t>
+          <t>LLM 3 連続失敗の通知は Bridge 経由の実行が要る (場所=mac / G-15) / 解除条件: Mac の Bridge で接続を落として送信</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16939,6 @@
           <t>TODO</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr"/>
       <c r="M256" t="inlineStr">
         <is>
           <t>場所=mac</t>
@@ -16252,15 +16994,19 @@
           <t>空応答が完了として記録されず、失敗として通知される</t>
         </is>
       </c>
-      <c r="K257" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L257" t="inlineStr"/>
+      <c r="K257" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-16</t>
+        </is>
+      </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>場所=mac / G-15 GAP-244</t>
+          <t>CLI の信号なし終了は Bridge 側で起こす必要がある (場所=mac / G-15 GAP-244) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16313,15 +17059,19 @@
           <t>実行履歴に記録が増え、結果が反映される</t>
         </is>
       </c>
-      <c r="K258" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L258" t="inlineStr"/>
+      <c r="K258" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-05.png</t>
+        </is>
+      </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>run-now → 200 {"data":{"status":"done","message":"実行しました。","detail":{"generated":"1"}}}; cron-runs に schedule 分 1 件 (status=success); 画面の実行履歴に反映=true</t>
         </is>
       </c>
     </row>
@@ -16375,15 +17125,19 @@
           <t>候補が一覧に出る。採用するまでナレッジには書き込まれない (DB に増えない)</t>
         </is>
       </c>
-      <c r="K259" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L259" t="inlineStr"/>
+      <c r="K259" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J41-17</t>
+        </is>
+      </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-167</t>
+          <t>ナレッジ候補の抽出に AI 会話が要る (場所=mac / GAP-167) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16437,15 +17191,19 @@
           <t>承認するまで実行されない。承認要求が一覧に出る</t>
         </is>
       </c>
-      <c r="K260" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr"/>
+      <c r="K260" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J42-01</t>
+        </is>
+      </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-130</t>
+          <t>承認モードのツール実行は Bridge 経由 (場所=mac / GAP-130) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16499,15 +17257,19 @@
           <t>副作用が起きていない (DB が変わらない)。却下が記録される</t>
         </is>
       </c>
-      <c r="K261" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr"/>
+      <c r="K261" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J42-02</t>
+        </is>
+      </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>J42-01 の承認要求が無いと拒否できない (場所=mac) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16561,15 +17323,19 @@
           <t>承認した操作だけが実行され記録される。ついでに別の操作をしない</t>
         </is>
       </c>
-      <c r="K262" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr"/>
+      <c r="K262" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J42-03</t>
+        </is>
+      </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>J42-01 の承認要求が無いと許可できない (場所=mac) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16622,15 +17388,19 @@
           <t>本人宛以外は一覧に出ない</t>
         </is>
       </c>
-      <c r="K263" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr"/>
+      <c r="K263" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J42-04</t>
+        </is>
+      </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>承認要求の実データは Bridge 経由の AI 実行 (J42-01, 場所=mac) でしか作れず、0 件同士では「本人宛以外が出ない」を判定できない。観測: member GET tool-approvals(owner スレッド) → 200 {"data":[]} / owner → 200 {"data":[]} / member approval-inbox → 200 0 件 / 解除条件: Mac の Bridge で承認モードのツール実行を起こす</t>
         </is>
       </c>
     </row>
@@ -16684,15 +17454,19 @@
           <t>断られず順番待ちの状態になり、空き次第そのまま実行に遷移する</t>
         </is>
       </c>
-      <c r="K264" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr"/>
+      <c r="K264" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J43-01</t>
+        </is>
+      </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-203</t>
+          <t>並列上限までの実行には Bridge worker が要る (場所=mac / GAP-203)。GET /bridge/status は cloud から読めるが running/queued は 0 のまま / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16746,15 +17520,19 @@
           <t>席が戻り、列に残り続けない。空き数が 1 増える</t>
         </is>
       </c>
-      <c r="K265" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L265" t="inlineStr"/>
+      <c r="K265" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J43-02</t>
+        </is>
+      </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-203 回帰</t>
+          <t>順番待ち中の離脱には J43-01 の状態が要る (場所=mac) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16807,15 +17585,19 @@
           <t>入力欄に文章が戻った状態になり、押し直すだけで再送できる</t>
         </is>
       </c>
-      <c r="K266" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L266" t="inlineStr"/>
+      <c r="K266" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J43-03.png</t>
+        </is>
+      </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 送信失敗時に入力欄へ文章が戻り、押し直すだけで再送できる / 実測: Bridge 未接続で送信 → POST /chat/threads/{id}/stream 200 (SSE) → 画面 alert「お使いの PC がまだ接続されていません。設定画面の「Bridge を接続」から接続すると、AI 機能を使えるようになります。」が出るが、入力欄は空に戻り (value="")、文章はユーザー発話として DB に保存されるだけ (GET messages に role=user 1 件・assistant 無し・queued 0 件)。押し直しても送るものが無く再送されない。再現: S-E01 でスレッドを開き、Bridge 未接続のまま文章を入力して送信 → 入力欄が消える</t>
         </is>
       </c>
     </row>
@@ -16869,15 +17651,19 @@
           <t>停止中の状態では新規 pick が止まり、実行中のものは続く。再開で pick が再び始まる</t>
         </is>
       </c>
-      <c r="K267" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr"/>
+      <c r="K267" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J43-04</t>
+        </is>
+      </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>「すべて一時停止」の効果は Bridge の pick で観測する必要がある (場所=mac) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16930,15 +17716,19 @@
           <t>順番待ちとお断りの件数が機械をまたいで記録されている</t>
         </is>
       </c>
-      <c r="K268" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L268" t="inlineStr"/>
+      <c r="K268" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>journeys-C-prod-20260903.txt#J43-05</t>
+        </is>
+      </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>場所=mac / GAP-208</t>
+          <t>混雑実績には順番待ちの実データが要る (場所=mac / GAP-208) / 解除条件: Mac の Bridge</t>
         </is>
       </c>
     </row>
@@ -16991,15 +17781,19 @@
           <t>free として表示される状態で、架空のプランや金額が出ない</t>
         </is>
       </c>
-      <c r="K269" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L269" t="inlineStr"/>
+      <c r="K269" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>GET /billing/plan (課金行なし WS) → plan=free status=inactive current_period_end=null stripe_configured=false。S-A03 プランタブは『Free プラン / inactive / 無料プラン。Pro にすると…(月額 ¥5,000)』+『決済連携が未設定です』。契約中表示・架空の契約金額なし (¥5,000 は Pro の定価案内)</t>
         </is>
       </c>
     </row>
@@ -17053,15 +17847,19 @@
           <t>Stripe Checkout の手続き画面に遷移するか、進めない理由が出る。黙って何も起きない、にならない</t>
         </is>
       </c>
-      <c r="K270" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L270" t="inlineStr"/>
+      <c r="K270" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>POST /billing/checkout → 503『お支払いの取り扱いがまだ設定されていません。運営にお問い合わせください。』(偽装なし)。UI は申込ボタンを出さず『決済連携が未設定です。管理者が STRIPE_SECRET_KEY を設定するとアップグレードできるようになります。』と進めない理由を表示 = 黙って何も起きない状態ではない</t>
         </is>
       </c>
     </row>
@@ -17115,15 +17913,19 @@
           <t>成功ページの照会で pro に反映され、契約中として表示される。webhook でも同じ状態が記録される</t>
         </is>
       </c>
-      <c r="K271" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L271" t="inlineStr"/>
+      <c r="K271" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>本番 API に STRIPE_SECRET_KEY 未設定 (stripe_configured=false, checkout/照会が 503) で決済を完了できない。解除条件: Stripe test key の設定</t>
         </is>
       </c>
     </row>
@@ -17176,15 +17978,19 @@
           <t>拒否され、契約状態は変わらない</t>
         </is>
       </c>
-      <c r="K272" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L272" t="inlineStr"/>
+      <c r="K272" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>Stripe-Signature 無し / 偽署名 とも 503『お支払いの取り扱いがまだ設定されていません』で拒否され plan は free のまま (状態不変は確認)。ただし webhook secret 未設定のため署名検証パス自体に到達しない。解除条件: STRIPE_WEBHOOK_SECRET 設定</t>
         </is>
       </c>
     </row>
@@ -17237,15 +18043,19 @@
           <t>free のままの状態で、契約は増えない</t>
         </is>
       </c>
-      <c r="K273" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L273" t="inlineStr"/>
+      <c r="K273" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>Checkout を開始できない (J50-02 が 503) ためキャンセル戻りを作れない。解除条件: Stripe test key</t>
         </is>
       </c>
     </row>
@@ -17298,15 +18108,19 @@
           <t>期間末まで使えること・日割り返金が無いことが押す前に表示された状態である</t>
         </is>
       </c>
-      <c r="K274" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L274" t="inlineStr"/>
+      <c r="K274" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-208</t>
+          <t>解約条件の文言 (『いまの請求期間の終わりまではご利用いただけます。日割りでの返金はありません』) は PlanSection の契約者向け分岐にのみあり、契約 (pro) が作れないため表示状態を観測できない。解除条件: Stripe test key で pro 契約</t>
         </is>
       </c>
     </row>
@@ -17360,15 +18174,19 @@
           <t>ポータルに遷移するか、進めない理由が出る。解約後は期間末までの契約中として反映される</t>
         </is>
       </c>
-      <c r="K275" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L275" t="inlineStr"/>
+      <c r="K275" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-208</t>
+          <t>POST /billing/portal → 503 (Stripe 未設定)。解除条件: Stripe test key + pro 契約</t>
         </is>
       </c>
     </row>
@@ -17422,15 +18240,19 @@
           <t>期間末前は使える。期間末後は free の状態に遷移し、有料機能が案内つきで止まる</t>
         </is>
       </c>
-      <c r="K276" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L276" t="inlineStr"/>
+      <c r="K276" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>pro 契約を作れないため期間末前後を作れない。解除条件: Stripe test key + 期間末を動かす手段</t>
         </is>
       </c>
     </row>
@@ -17483,15 +18305,19 @@
           <t>解約の導線が表示されない状態である</t>
         </is>
       </c>
-      <c r="K277" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L277" t="inlineStr"/>
+      <c r="K277" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>free WS のプランタブに『プランの管理・解約』ボタン無し (解約/管理ボタン 0、申込ボタンも未設定のため 0)。API も POST /billing/portal は 503 で解約対象なし</t>
         </is>
       </c>
     </row>
@@ -17544,15 +18370,19 @@
           <t>受け付けられ、30 日の猶予があることが分かる。DB に deleted_at が記録され、監査ログ account_deletion_requested が記録される</t>
         </is>
       </c>
-      <c r="K278" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L278" t="inlineStr"/>
+      <c r="K278" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>POST /auth/account/delete: パスワード不一致 401、正パスワードで 200 deleted_at=2026-09-03T05:08:05Z scheduled_purge_at=2026-10-03T05:08:05Z (猶予 30 日)。二重退会は 401 (退会後は JWT 無効)。S-A03 退会タブは専用ページ (/data-deletion) へ誘導し 30 日ハード削除を明記。監査ログ account_deletion_requested は admin 専用で未確認</t>
         </is>
       </c>
     </row>
@@ -17605,15 +18435,19 @@
           <t>元の状態に戻り、作ったものが残っている。deleted_at が消える</t>
         </is>
       </c>
-      <c r="K279" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L279" t="inlineStr"/>
+      <c r="K279" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>S-A01『退会済みアカウントの復元』→ POST /auth/account/restore 200 →『アカウントを復元しました』→ サインイン → /projects。復元後 GET /workspaces に QA-E2-W3-退会、GET /projects/PC 200 deleted_at=None、/me deleted_at=None。API で再 restore は 404『退会の申請が見つかりません』</t>
         </is>
       </c>
     </row>
@@ -17666,15 +18500,19 @@
           <t>入れない状態で、理由が日本語で分かる。復元の導線だけが出る</t>
         </is>
       </c>
-      <c r="K280" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L280" t="inlineStr"/>
+      <c r="K280" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 入れず理由が日本語で分かる・復元導線だけが出る / 実測: 退会後 signin は 401『メールアドレスまたはパスワードが違います。』(API/UI とも) で『退会中』という理由が分からない (パスワード誤りと区別不能)。復元リンクはサインイン画面に常時ある汎用リンクで、退会中に限って出るものではない。※存在秘匿の設計判断ならその旨を正本に明記して期待を改訂する</t>
         </is>
       </c>
     </row>
@@ -17727,15 +18565,19 @@
           <t>全部拒否される (401)。退会したのにセッション・トークンが有効な状態で残らない</t>
         </is>
       </c>
-      <c r="K281" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L281" t="inlineStr"/>
+      <c r="K281" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>場所=cloud / G-14 GAP-245</t>
+          <t>退会前 JWT で GET /me, /workspaces, /projects/PC, POST /projects 全 401。退会前 Bridge トークン (POST /bridge-tokens 発行) で /bridge/status (X-Bridge-Token / Bearer) と /bridge/ping 全 401。refresh_token は signin 応答で発行されない設計 (null) のため対象外</t>
         </is>
       </c>
     </row>
@@ -17789,15 +18631,19 @@
           <t>個人情報が削除され、ナレッジは匿名化されて残る。監査ログ account_hard_deleted が記録される</t>
         </is>
       </c>
-      <c r="K282" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L282" t="inlineStr"/>
+      <c r="K282" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>deleted_at を 31 日前にする DB 操作と日次ジョブの起動が本環境から不可。解除条件: 本番 DB 接続 + cron ジョブ手動実行</t>
         </is>
       </c>
     </row>
@@ -17850,15 +18696,19 @@
           <t>請求が受け付けられ記録される。30 日以内のキャンセル方法が案内される</t>
         </is>
       </c>
-      <c r="K283" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L283" t="inlineStr"/>
+      <c r="K283" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>実測: 未サインインは「サインインした状態で行っていただきます」でフォーム無し・API 401。サインイン済みは POST 201 status=received、削除予定日と 30 日以内の復元案内あり。旧正本 (role=guest で受付) は GAP-233 の設計 (本人確認のため要サインイン) と不一致だったため正本を訂正し、訂正後の期待で PASS</t>
         </is>
       </c>
     </row>
@@ -17912,15 +18762,19 @@
           <t>納品工程が done に遷移し、案件の状態が納品済みとして一覧とダッシュボードに反映される。クライアント側 (J21) に最終版の成果物が見える</t>
         </is>
       </c>
-      <c r="K284" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L284" t="inlineStr"/>
+      <c r="K284" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J30-15.png</t>
+        </is>
+      </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>共有リンク発行 → 公開 GET /share/{token} (認証なし)=200 で最終版が見える (クライアント側 J21 の代替); 納品工程 confirm なし 403 / confirm あり 200 → flow delivery=done。しかし案件の状態は納品済みにならない: GET /projects/{id}.status=draft, 一覧 status=draft, dashboard status=draft current_phase=hearing; 画面 (一覧/ダッシュボード) に納品済み表記=false</t>
         </is>
       </c>
     </row>
@@ -17974,15 +18828,19 @@
           <t>owner 側のボードとダッシュボードに完了とコメントが反映される。監査ログ task_status_changed / comment_created が記録される</t>
         </is>
       </c>
-      <c r="K285" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L285" t="inlineStr"/>
+      <c r="K285" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>evidence/shots/journeys/J31-12.png</t>
+        </is>
+      </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>タスク完了=200/done, コメント=201; owner ダッシュボード done=1 未解決コメント=2 (画面反映=true); 監査 recent_activities=["project.flow.thread","task.create","task.create","project.flow.complete"] → task 系=false, comment 系=false (comment_created 相当は project/task 対象の audit にしか出ないため未確認)</t>
         </is>
       </c>
     </row>
@@ -18036,15 +18894,19 @@
           <t>社内の返信が自分のコメントの下に出ている。納品された最終版の成果物が閲覧できる状態である</t>
         </is>
       </c>
-      <c r="K286" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L286" t="inlineStr"/>
+      <c r="K286" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+        </is>
+      </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>返信は自分のコメントの下に表示 (OK)。しかし納品成果物は S-L03 に『納品書 2026/09/03 · v1 · HTML』の行として出るだけで、開く導線 (リンク/ボタン) が無く、client 用の content/content-url API も openapi に無い → 『納品された最終版の成果物が閲覧できる状態』を満たさない (行をクリックしても遷移・API 呼出なし)</t>
         </is>
       </c>
     </row>
@@ -18097,15 +18959,19 @@
           <t>順番待ちやお断りが起きていれば、機械をまたいで集計されて出る。件数が J43 の記録と一致する</t>
         </is>
       </c>
-      <c r="K287" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L287" t="inlineStr"/>
+      <c r="K287" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-208</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/health (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -18158,15 +19024,19 @@
           <t>現在の余裕と、増やす前に必要な作業が実測値で表示された状態である</t>
         </is>
       </c>
-      <c r="K288" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L288" t="inlineStr"/>
+      <c r="K288" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-205</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/health (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -18219,15 +19089,19 @@
           <t>直前の失敗がエラーログに記録され、通知の送信状態が出る。外部 SaaS に送られていない</t>
         </is>
       </c>
-      <c r="K289" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L289" t="inlineStr"/>
+      <c r="K289" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-182/194/195</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/alerts / /admin/uptime / /admin/errors (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -18281,15 +19155,19 @@
           <t>ワークスペース数・ユーザー数が実数と一致して反映される。期間切替で数字が変わる</t>
         </is>
       </c>
-      <c r="K290" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L290" t="inlineStr"/>
+      <c r="K290" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/platform-stats / /admin/dashboard (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -18344,15 +19222,19 @@
           <t>状態が表示され、リセットが監査ログに記録される。stale な実行が回収される</t>
         </is>
       </c>
-      <c r="K291" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L291" t="inlineStr"/>
+      <c r="K291" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/circuit-breaker -&gt; 403、POST …/reset と …/poll-pids (owner, body 無し) -&gt; 422/422 (422 = body 検証が運営判定より先)</t>
         </is>
       </c>
     </row>
@@ -18406,15 +19288,19 @@
           <t>報告が記録され、運営のエラーログに一覧で出る</t>
         </is>
       </c>
-      <c r="K292" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L292" t="inlineStr"/>
+      <c r="K292" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J60-06.png</t>
+        </is>
+      </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-182</t>
+          <t>利用者側は実走: POST /client-errors (owner) -&gt; 202 accepted、未認証 -&gt; 401。ただし /projects で合成 JS エラー (setTimeout 内 throw) を起こしても画面から /client-errors は送られない (ErrorBoundary は描画エラーのみ報告)。運営のエラーログ (GET /admin/errors) は 403 で一覧は未観測 / 解除条件: 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -18468,15 +19354,19 @@
           <t>投稿が運営の一覧に出る。対応済みに遷移し、記録される</t>
         </is>
       </c>
-      <c r="K293" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L293" t="inlineStr"/>
+      <c r="K293" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#J60-06</t>
+        </is>
+      </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>利用者側は実走: POST /beta-feedback (owner, category=other) -&gt; 201 id=6aee6eef-d044-43cb-a85f-1e15f3a6b0a1 status=open、本文空 -&gt; 422。運営一覧 GET /admin/beta-feedback と対応済み化は owner だと 403 で未観測 / 解除条件: 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -18530,15 +19420,19 @@
           <t>実行者・対象・時刻が記録から特定できる</t>
         </is>
       </c>
-      <c r="K294" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L294" t="inlineStr"/>
+      <c r="K294" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/audit-logs (owner) -&gt; 403、未認証 -&gt; 401</t>
         </is>
       </c>
     </row>
@@ -18591,15 +19485,19 @@
           <t>見られない (403)。拒否が記録される</t>
         </is>
       </c>
-      <c r="K295" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L295" t="inlineStr"/>
+      <c r="K295" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J61-02.png</t>
+        </is>
+      </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>観測できた部分は期待どおり: GET /admin/audit-logs (owner) -&gt; 403「この操作は運営のみが行えます。」、/admin/audit も access-denied 表示で監査ログ画面は組み立てられない (R-T08 の遮断は API・画面とも保持)。「拒否が記録される」は運営でしか読めず未観測 (実装に 403 時の監査書き込み無し) / 解除条件: 運営アカウント</t>
         </is>
       </c>
     </row>
@@ -18652,15 +19550,19 @@
           <t>条件に合う記録だけが一覧に出る</t>
         </is>
       </c>
-      <c r="K296" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L296" t="inlineStr"/>
+      <c r="K296" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/audit-logs?action=&amp;actor_type= (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -18713,15 +19615,19 @@
           <t>絞った分だけが CSV に出て、件数が一覧の記録と一致する</t>
         </is>
       </c>
-      <c r="K297" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L297" t="inlineStr"/>
+      <c r="K297" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行</t>
         </is>
       </c>
     </row>
@@ -18774,15 +19680,19 @@
           <t>0 件の状態で出て壊れない</t>
         </is>
       </c>
-      <c r="K298" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L298" t="inlineStr"/>
+      <c r="K298" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/audit-logs?actor_type=nobody-qa-f (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -18835,15 +19745,19 @@
           <t>実累計が表示され、直前の登録 (J10) が反映されている</t>
         </is>
       </c>
-      <c r="K299" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L299" t="inlineStr"/>
+      <c r="K299" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/mission / /admin/trends (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -18896,15 +19810,19 @@
           <t>目標が反映され、再読み込みしても残る</t>
         </is>
       </c>
-      <c r="K300" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L300" t="inlineStr"/>
+      <c r="K300" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: PUT /admin/goal (owner, 正しい body) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -18958,15 +19876,19 @@
           <t>追加が集計に反映され、削除で集計から減る</t>
         </is>
       </c>
-      <c r="K301" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L301" t="inlineStr"/>
+      <c r="K301" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/acquisitions -&gt; 403、POST -&gt; 422 (422 = body 検証が先)</t>
         </is>
       </c>
     </row>
@@ -19020,15 +19942,19 @@
           <t>月次一覧に反映され、削除で消える</t>
         </is>
       </c>
-      <c r="K302" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L302" t="inlineStr"/>
+      <c r="K302" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/costs -&gt; 403、POST -&gt; 422</t>
         </is>
       </c>
     </row>
@@ -19081,15 +20007,19 @@
           <t>日本語のエラーで拒否され、一覧に増えない</t>
         </is>
       </c>
-      <c r="K303" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L303" t="inlineStr"/>
+      <c r="K303" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: 負の金額 POST /admin/costs (owner) -&gt; 422 (owner では運営判定より先に 422; 運営での日本語エラーは未観測)</t>
         </is>
       </c>
     </row>
@@ -19142,15 +20072,19 @@
           <t>0 の状態で表示され壊れない</t>
         </is>
       </c>
-      <c r="K304" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L304" t="inlineStr"/>
+      <c r="K304" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行</t>
         </is>
       </c>
     </row>
@@ -19203,15 +20137,19 @@
           <t>403 で拒否され access-denied に遷移する</t>
         </is>
       </c>
-      <c r="K305" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L305" t="inlineStr"/>
+      <c r="K305" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J62-07.png</t>
+        </is>
+      </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>owner で /admin (S-T01) を開くと URL /admin のまま「この画面は運営専用です / ACCESS DENIED」(access-denied) に差し替わり、運営メニューは描画されず /admin API も叩かれない。GET /admin/mission (owner JWT) -&gt; 403「この操作は運営のみが行えます。」</t>
         </is>
       </c>
     </row>
@@ -19264,15 +20202,19 @@
           <t>所属ワークスペース scope の利用者が一覧に出て、J10/J31 で作った人が反映されている</t>
         </is>
       </c>
-      <c r="K306" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L306" t="inlineStr"/>
+      <c r="K306" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/users (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -19325,15 +20267,19 @@
           <t>相手にメールが届く (実送信できない環境では送信ログ/キュー投入で代替)。監査ログ support.contact が記録される</t>
         </is>
       </c>
-      <c r="K307" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L307" t="inlineStr"/>
+      <c r="K307" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行 + 受信箱なし (実送信の確認手段が無い)</t>
         </is>
       </c>
     </row>
@@ -19386,15 +20332,19 @@
           <t>送った連絡が監査ログの逆引きで一覧に出る</t>
         </is>
       </c>
-      <c r="K308" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L308" t="inlineStr"/>
+      <c r="K308" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/support-contacts (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -19447,15 +20397,19 @@
           <t>拒否され、メールは送られず記録も増えない</t>
         </is>
       </c>
-      <c r="K309" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L309" t="inlineStr"/>
+      <c r="K309" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: 本文空の POST /admin/support-contact (owner) -&gt; 422 (422 = 空本文の検証は運営判定より先に効く。運営での挙動は未観測)</t>
         </is>
       </c>
     </row>
@@ -19508,15 +20462,19 @@
           <t>account_type=platform として一覧に出て、全アカウントの検索で引ける状態になる</t>
         </is>
       </c>
-      <c r="K310" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L310" t="inlineStr"/>
+      <c r="K310" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: GET /admin/knowledge (owner) -&gt; 403。利用者側 GET /knowledge?account_type=platform は [] = 本番に運営ナレッジ 0 件</t>
         </is>
       </c>
     </row>
@@ -19570,15 +20528,19 @@
           <t>編集が反映され、削除で一覧から消える</t>
         </is>
       </c>
-      <c r="K311" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L311" t="inlineStr"/>
+      <c r="K311" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: DELETE /admin/knowledge/{id} (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -19631,15 +20593,19 @@
           <t>取り込んだ内容が一覧に出て記録される</t>
         </is>
       </c>
-      <c r="K312" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L312" t="inlineStr"/>
+      <c r="K312" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行</t>
         </is>
       </c>
     </row>
@@ -19692,15 +20658,19 @@
           <t>全テナントを走査した提案が匿名化されて一覧に出る。テナント名や個人名が含まれない</t>
         </is>
       </c>
-      <c r="K313" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L313" t="inlineStr"/>
+      <c r="K313" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-153 R-T08</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: POST /admin/knowledge/curation/run と GET /admin/knowledge/curation (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -19753,15 +20723,19 @@
           <t>platform ナレッジとして一覧に出て、一般利用者の検索でも引ける</t>
         </is>
       </c>
-      <c r="K314" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L314" t="inlineStr"/>
+      <c r="K314" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: POST …/curation/{id}/approve (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -19814,15 +20788,19 @@
           <t>公開されず、却下が記録される</t>
         </is>
       </c>
-      <c r="K315" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L315" t="inlineStr"/>
+      <c r="K315" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#運営専用</t>
+        </is>
+      </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>運営権限のアカウントが無い (付与に本番 DB 接続 scripts/grant-admin.sh が要る) / 解除条件: 運営 (app_metadata.role=admin) アカウントの発行。観察: POST …/curation/{id}/reject (owner) -&gt; 403</t>
         </is>
       </c>
     </row>
@@ -19875,15 +20853,19 @@
           <t>403 で拒否され、内容は元のまま残る</t>
         </is>
       </c>
-      <c r="K316" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
-        </is>
-      </c>
-      <c r="L316" t="inlineStr"/>
+      <c r="K316" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>journeys-F-prod-20260903.txt#J64-07</t>
+        </is>
+      </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>場所=cloud / R-T08</t>
+          <t>owner JWT で PATCH /admin/knowledge/{id} -&gt; 403「この操作は運営のみが行えます。」。本番に運営ナレッジが 0 件のため id はダミー UUID (運営判定は 404 より先に効く)。前後の GET /knowledge?account_type=platform は同一 (変化なし)</t>
         </is>
       </c>
     </row>
@@ -20118,11 +21100,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>93</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>30%</t>
         </is>
       </c>
     </row>
@@ -20133,11 +21115,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12%</t>
         </is>
       </c>
     </row>
@@ -20148,11 +21130,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>126</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>40%</t>
         </is>
       </c>
     </row>
@@ -20163,11 +21145,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>315</v>
+        <v>58</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>18%</t>
         </is>
       </c>
     </row>

--- a/apps/web/.qa/e2e-journey/journey-20260903.xlsx
+++ b/apps/web/.qa/e2e-journey/journey-20260903.xlsx
@@ -7932,14 +7932,25 @@
           <t>「準備中」列に出る。依存・受入基準・仕様書がリンクされて記録される</t>
         </is>
       </c>
-      <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K114" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-01.png</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI「タスクを追加」→ POST /tasks 201、lifecycle=triage で画面の「準備中」列に出る (一覧 0→1)。しかしモーダルの入力は タイトル/分類 (機能グループ)/見積 (時間)/種別
+feature
+screen
+foundation
+verification
+infrastructure
+migration/対象画面 (任意 — 例: ログイン画面) だけで、依存・受入基準・仕様書を指定する欄が無く、作成されたタスクは dependencies=[]・acceptance_criteria_id=null・仕様書リンク無し (画面名を入れたのでモック QA-D LP トップ には紐づく)。期待の「依存・受入基準・仕様書がリンクされて記録される」が満たされない。監査: dashboard recent_activities に task.create:task:d01024c7</t>
         </is>
       </c>
     </row>
@@ -7992,14 +8003,19 @@
           <t>依存漏れとして警告が出る。保存する場合も警告つきの状態が記録され、黙って通らない</t>
         </is>
       </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K115" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-02.png</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 依存漏れの警告が出て、保存時も警告つきで記録される / 実測: 「タスクを追加」モーダルに依存を入力する欄が無く (0 個)、依存空のまま保存 → POST /tasks 201 で黙って通る (画面の警告 0 件、カードにも警告表記なし、task.dependencies=[]・metadata/blocked_reason に警告の記録なし)</t>
         </is>
       </c>
     </row>
@@ -8052,14 +8068,20 @@
           <t>受入基準 (3 層) と関連資料が出て、リンク先が実在する。0 件のタブは 0 件の状態で出る</t>
         </is>
       </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-03.png</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>タブ 受入条件/進捗・スコア/依存タスク/テスト結果/実行履歴/関連資料
+1/コメント。受入条件: GET /acceptance-criteria 404 → 画面「受入条件は登録されていません。」(手動作成タスクには 3 層の受入基準が無く 0 件表示); 関連資料: GET /related 1 件 (設計モック QA-D LP トップ) でリンク先実在= GET /mocks 200; 依存/テスト結果/実行履歴は 0 件の状態で表示 (エラーのタブ 0 件)。「受入基準 (3 層) が出て仕様書が実在」はタスク分解 (AI/Bridge) で作られたタスクでしか検証できない / 解除条件: Mac の Bridge でタスク分解を流す</t>
         </is>
       </c>
     </row>
@@ -8112,14 +8134,19 @@
           <t>列移動が DB に反映され、監査ログ task_status_changed が記録される</t>
         </is>
       </c>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-04.png</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>S-I01 のカードはドラッグ不可 (draggable=false、dragTo でも lifecycle 不変) で、列移動はカードの「着手可にする」ボタン → PATCH /tasks/{id} lifecycle_stage=ready 200。DB 再取得 lifecycle=ready、画面の列=着手可。監査: dashboard recent_activities に task.update:task:d01024c7 (期待の task_status_changed に相当する action 名かは要確認)</t>
         </is>
       </c>
     </row>
@@ -8172,14 +8199,19 @@
           <t>コメントが一覧に出て、担当 AI 社員に通知される (実送信できない環境では送信ログ/キュー投入で代替)</t>
         </is>
       </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K118" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-05.png</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI でコメント投稿 → POST /comments 201 (target_type=task)、GET /comments 1 件、画面のコメント一覧に本文が出る。期待の「担当 AI 社員に通知される (送信ログ/キュー投入)」は通知処理・送信ログ・キューが存在せず観測できない (J46-03/J45-09 と同じ) → 通知部分が不成立</t>
         </is>
       </c>
     </row>
@@ -8232,14 +8264,19 @@
           <t>一覧から消え論理削除が記録される。依存していたタスクに警告が反映される</t>
         </is>
       </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K119" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-20.png</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>S-I01/S-I02 に削除導線が無く (詳細画面の削除ボタン 0 個) API DELETE /tasks/{id} → 204、一覧 5→4・画面から消える・GET 404 (論理削除)、監査 task.delete:task:756ed526。「依存していたタスクに警告」は依存を設定する API/画面が無く依存関係を作れないため未検証 / 解除条件: dependencies を持つタスク (タスク分解 = Bridge) を用意する</t>
         </is>
       </c>
     </row>
@@ -8292,14 +8329,19 @@
           <t>選んだ分だけ着手可に遷移し、選んでいないものは変わらない</t>
         </is>
       </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K120" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-21.png</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 2 件選んで一括操作で選んだ分だけ着手可に遷移 / 実測: S-I01 の選択チェックボックスは着手可 (ready) のカードにしか無く (準備中のカード D/E は選択不可: チェックボックスは Nebula-1・Nebula-3 のみ)、選択バーの操作も「選択を再生する」だけで一括「着手可」は無い。準備中→着手可はカード単体の「着手可にする」を 1 枚ずつ押すしかない。API POST /tasks/bulk/lifecycle (task_ids 2 件, ready) → 200 updated=2 skipped=[] で D/E=ready・選ばなかった F=triage (不変)、画面の列も D/E=着手可 F=準備中、監査 task.bulk_lifecycle 2 件 — データ層は正しいが画面から一括着手可はできない</t>
         </is>
       </c>
     </row>
@@ -8549,14 +8591,19 @@
           <t>工程ごとの成果物が一覧に出て、三層がそれぞれ表示された状態になる</t>
         </is>
       </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K124" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-01.png</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 工程ごとの成果物が一覧に出て三層 (HTML/JSON/MD) が表示される / 実測: GET /outputs 4 件 (estimate/hearing/requirements/verification)。工程画面 S-F01 の成果物欄はどの工程を選んでも同じ 4 件・「成果物 4」で工程ごとに分かれていない。ビューア S-G01 の表示形式タブは実在 format のみで import 成果物は「HTML」だけ (JSON/MD は AI 生成でしか作れず未検証)。しかも HTML 層は content-url が http:// を返すため Mixed Content でブラウザに block され iframe が空 (描画されない)。加えて HTML 成果物で「表を読み込めませんでした。」が常時表示</t>
         </is>
       </c>
     </row>
@@ -8609,14 +8656,19 @@
           <t>署名付き URL (content-url) で HTML が iframe に反映される。Storage に実体が存在する (G-11)</t>
         </is>
       </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K125" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-02.png</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 署名付き URL (content-url) で HTML が iframe に反映され Storage に実体がある / 実測: GET /outputs/{id}/content-url?format=html → 200 で署名付き URL (exp+sig)、直接 fetch → 200 text/html 438 bytes・本文一致 (実体は DB 内蔵 mockdb = G-11 実在)、署名改ざん → 403。しかし URL のスキームが http:// のため https の画面で iframe が Mixed Content として block され、プレビューは空のまま (console: This request has been blocked; the content must be served over HTTPS)</t>
         </is>
       </c>
     </row>
@@ -8670,14 +8722,19 @@
           <t>コメントが一覧に出て、担当 AI 社員にメール通知される (実送信できない環境では送信ログ/キュー投入で代替)。監査ログ comment_created が記録される</t>
         </is>
       </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K126" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-03.png</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI: 対象位置に「2. 機能一覧」(sec-2) を選び投稿 → POST /comments 201、GET /comments に target_element_id=sec-2 で 1 件、画面のコメント一覧に本文表示、unresolved-count 0→undefined。期待の「担当 AI 社員にメール通知 (送信ログ/キュー)」は通知の実装・送信ログ・キューが存在せず観測できない (API 応答にも通知の痕跡なし) → 通知部分が不成立。監査ログ comment_created は運営 API のみで観測不能</t>
         </is>
       </c>
     </row>
@@ -8730,14 +8787,19 @@
           <t>解決済みに遷移し、ダッシュボードの未解決件数が 1 減る</t>
         </is>
       </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-04.png</t>
         </is>
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI「解決にする」→ PATCH /comments/{id} 200 status=resolved; ダッシュボード S-B02 (/projects/dashboard) の「未解決コメント」が 1→0 に減る (再読込で実測); GET /comments/unresolved-count も count=0</t>
         </is>
       </c>
     </row>
@@ -8790,14 +8852,19 @@
           <t>提案が一覧に出る。文書はまだ変わらない状態である</t>
         </is>
       </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K128" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-05.png</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: POST /comments/{id}/fix-proposal → 503 (お使いの PC の Bridge がオフラインです。Bridge アプリを起動してから、もう一度お試しください。)、GET /fix-proposals=0 件で文書は不変。UI の「スティーブに修正提案を依頼」は押しても API 呼出が発生しなかった (解決済みコメントのため無効化の可能性)。AI 実行経路 (Bridge/LLM) が無い / 解除条件: Mac の Bridge を接続して再実行</t>
         </is>
       </c>
     </row>
@@ -8850,14 +8917,19 @@
           <t>提案を適用した新版が生成され、版履歴が 1 増える。旧版は残る</t>
         </is>
       </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K129" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J46-06</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: 承認する提案が作れない (J46-05 が Bridge 要で BLOCKED、GET /fix-proposals=0 件) / 解除条件: J46-05 を Mac の Bridge で流してから</t>
         </is>
       </c>
     </row>
@@ -8910,14 +8982,19 @@
           <t>文書は不変で、却下が記録される</t>
         </is>
       </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K130" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J46-07</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>却下する提案が作れない (J46-05 が Bridge 要で BLOCKED、GET /fix-proposals=0 件)。却下 API (POST /output-fix-proposals/{id}/reject) 自体は提案 id が無く叩けない / 解除条件: J46-05 を Mac の Bridge で流してから</t>
         </is>
       </c>
     </row>
@@ -8970,14 +9047,19 @@
           <t>新版が積まれ、一覧の最新版が切り替わる。旧版は履歴に残る</t>
         </is>
       </c>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K131" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J46-08</t>
         </is>
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: 「編集」→ POST /outputs/{id}/revise は 503 (お使いの PC の Bridge がオフラインです。Bridge アプリを起動してから、もう一度お試しください。) で AI 実行経路が無い / 解除条件: Mac の Bridge (T-F-41) を接続して再実行。以降の版履歴・差分・復元の行は import で v2 を積んで流す</t>
         </is>
       </c>
     </row>
@@ -9031,14 +9113,19 @@
           <t>版間の差分が表示され、変更箇所が依頼内容と一致して反映される</t>
         </is>
       </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K132" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-09.png</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>版履歴: バージョン選択に 2 版 (v2 · 2026-09-03 05:49 / v1 · 2026-09-03 05:34); 「v1 との差分」→ GET /outputs/{v2}/diff/{v1} 200、画面に unified diff が出て追加行は F-3 レポート出力の 1 行のみ (削除行 1)。ただし v2 は AI 改訂 (J46-08, Bridge 要) ではなく import で積んだため「変更箇所が依頼内容と一致」の AI 側は未検証 / 解除条件: Mac の Bridge で J46-08 を流す</t>
         </is>
       </c>
     </row>
@@ -9091,14 +9178,19 @@
           <t>旧版が新版として復元され、履歴は消えない (版が 1 増える)</t>
         </is>
       </c>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-10.png</t>
         </is>
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>v1 を選んで「この版を復元」→ POST /outputs/{v1}/restore 201、v3 が新版として追加 (meta author=restore restored_from_version=1)、履歴は 2→3 版で v1/v2 は消えない、復元版の本文は v1 と同じ (F-3 なし)</t>
         </is>
       </c>
     </row>
@@ -9152,14 +9244,19 @@
           <t>表として出る。編集が新版として保存され、元の版は残る</t>
         </is>
       </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-11.png</t>
         </is>
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>S-G01 の「表の表示と編集」に xlsx (見積明細 4 行) が表として出る; セル (設計/単価) 300000→350000 に直して保存 → POST /sheet 201; 版 1→2 (v2 新規)、新版の値=350000、v1 は 300000 のまま残る</t>
         </is>
       </c>
     </row>
@@ -9212,14 +9309,19 @@
           <t>期限つきリンクが 1 度だけ表示され、一覧に出る (URL は再取得不可)。監査ログに記録される</t>
         </is>
       </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-13.png</t>
         </is>
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI: 期限 30 日を選び「共有リンクを発行」→ POST /outputs/{id}/share-links 201 (expires_at=2026-10-03)、URL が発行直後の画面に 1 度だけ表示、再読込後は URL が消え一覧 (期限・閲覧回数・無効化) だけ残る、GET /share-links の応答に share_url/token 無し (再取得不可)。監査ログ output.share_link.create は運営 API のみで観測不能。所見: 返る share_url が http:// スキーム (クライアントに渡す URL として要確認)</t>
         </is>
       </c>
     </row>
@@ -9272,14 +9374,19 @@
           <t>認証なしで成果物が読める状態になる。期限を過ぎたリンクは拒否される</t>
         </is>
       </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-14.png</t>
         </is>
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>認証なし (cookie 0) の別 context で share_url (https) → 200 text/html、成果物本文「要件定義書 QA-D / 1. 目的」が読める、印刷→PDF 導線あり、view_count=1 に反映、不正トークン → 404。「期限を過ぎたリンクは拒否される」は期限切れリンクを作れない (expires_days は最小 1 日: 0 指定 → 422) ため未検証 / 解除条件: staging で expires_at を過去に書き換える手段、または 1 日待つ。所見: API が返す share_url は http:// スキーム</t>
         </is>
       </c>
     </row>
@@ -9333,14 +9440,25 @@
           <t>以後の閲覧は 410 で見えなくなる。無効化の直後 (0 秒) でも見えない (G-12)</t>
         </is>
       </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-15.png</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI「この共有リンクを無効化」→ POST revoke 200、無効化後の GET /share/{token} → 410; API で発行→GET 200→revoke→応答直後 (0 秒) の GET → 410 (G-12 OK); 二重 revoke → 404; 画面の一覧から消える (「クライアントに渡す
+期限
+7 日
+14 日
+30 日
+90 日
+共有リンクを発行」)</t>
         </is>
       </c>
     </row>
@@ -9393,14 +9511,19 @@
           <t>ファイルが得られ、監査ログ output_downloaded が記録される</t>
         </is>
       </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K138" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-16.png</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>API (Bearer) では html (text/html attachment) / xlsx (application/vnd.openxmlformats-officedoc attachment) が得られる。しかし画面の「HTML で保存」「Excel で保存」は API への素の &lt;a href&gt; で Authorization が付かず、クリック結果=HTML で保存: HTTP 404 → 遷移先 /outputs/90f5fb07-96af-4b90-8259-e37315d8c43c/export?format=html 「メインコンテンツへスキップ ワークスペース · QA-D WS 20260903 プロジェクト AI社員 ナレッジ テン」 / Excel で保存: HTTP 404 → 遷移先 /outputs/90f5fb07-96af-4b90-8259-e37315d8c43c/export?format=xlsx 「メインコンテンツへスキップ ワークスペース · QA-D WS 20260903 プロジェクト AI社員 ナレッジ テン」 (画面からはファイルが得られない)。監査ログ output_downloaded は export_output に監査書込が無く記録されない</t>
         </is>
       </c>
     </row>
@@ -9454,14 +9577,19 @@
           <t>編集が DB に反映され updated_at が更新される。次のチャット応答が最新の本文を前提にする</t>
         </is>
       </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K139" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-17.png</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>場所=mac / F-009</t>
+          <t>場所=mac: S-G01 の「編集」は「スティーブに修正を依頼」(POST /revise = AI) のみで、HTML 本文を人が直接編集して保存する UI/API は無い (contenteditable 0 個)。表 (xlsx) の直接編集は J46-11 で PASS。「次のチャット応答が最新の本文を前提にする」はチャット (Bridge) 要 / 解除条件: Mac の Bridge + HTML 直接編集の導線</t>
         </is>
       </c>
     </row>
@@ -9514,14 +9642,19 @@
           <t>403 で拒否され、成果物は変わらない。閲覧とコメントはできる状態である</t>
         </is>
       </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K140" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-18.png</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 403 で拒否 / 実測: viewer (PATCH role=viewer 200) の GET /outputs 200・POST /comments 201 (閲覧・コメント可) は期待通り。編集系は POST /sheet → [500, 500, 500] (恒常 500: サーバー側で問題が発生しました。時間をおいて、もう一度お試しください。（参照 ID: 1d80d498-50fc-4b13-8253-3ff52d9c7268）)、POST /restore → [500, 500, 500] (恒常 500)、POST /revise → 503 (Bridge)、POST /share-links → 201 ×2 (閲覧者がクライアント共有リンクを発行できてしまう = 権限漏れ)。成果物自体は不変 (版数 xlsx=2 req=3)。画面でも編集/共有リンク発行/投稿ボタンが閲覧者に表示される</t>
         </is>
       </c>
     </row>
@@ -9574,14 +9707,19 @@
           <t>0 件の案内が出る状態になり、エラーにならない</t>
         </is>
       </c>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K141" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-19.png</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>期待: 0 件の案内が出てエラーにならない / 実測: GET /outputs=0 件。S-G01 (/outputs?project=空案件) は「成果物を選択すると表示します。」と出るだけで、成果物を選ぶ一覧・ピッカーが無く 0 件であることも案内しない (件数に関係なく同じ文言)。工程画面 S-F01 側は「成果物 0」と表示。alert 0 件・API エラー無し (JS console の 500 は GET /me/consents の初回 500 = 環境要因)</t>
         </is>
       </c>
     </row>
@@ -9699,14 +9837,19 @@
           <t>生成したモックが一覧に出て、版 v1 が記録される。Storage に HTML の実体がある (G-11)</t>
         </is>
       </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K143" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-01.png</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: UI「新規生成」→ POST /mocks/generate 503 (お使いの PC の Bridge がオフラインです。Bridge アプリを起動してから、もう一度お試しください。)、一覧は 1 件のまま。AI 実行経路 (Bridge) が無い / 解除条件: Mac の Bridge を接続。以降の行は import (GAP-156) で取り込んだモック「QA-D LP トップ」v1 (mockdb 実体あり) で流す</t>
         </is>
       </c>
     </row>
@@ -9759,14 +9902,19 @@
           <t>画面ごとの最新版がプレビューに反映される (署名付き URL)</t>
         </is>
       </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K144" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-02.png</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>一覧のカードから選ぶ → /mocks?mock={id} → GET /mocks/{id}/content-url 200 (署名付き、実体 mockdb は https で直接取得 → 200 本文一致)。しかし URL が http:// スキームのため https の画面で iframe が Mixed Content として block (console 1 件、iframe 本文空) → プレビューに最新版が反映されない (J46-02 と同根)</t>
         </is>
       </c>
     </row>
@@ -9819,14 +9967,19 @@
           <t>切り替えた幅がプレビューに反映された状態になる</t>
         </is>
       </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-03.png</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>ビューポート切替 (ワイド 1440 / デスクトップ 1024 / タブレット 768 / モバイル 320) を押すと iframe の幅 (style width) が 1440px/1024px/768px/320px に切り替わり aria-pressed も追従。表示上は 752px/752px/752px/320px で、1440/1024/768 は transform scale による fit ズーム で収めている (中身は Mixed Content で空)</t>
         </is>
       </c>
     </row>
@@ -9879,14 +10032,19 @@
           <t>進行状況がストリームで出る。新版が積まれ旧版は残る。一覧の最新版が切り替わる</t>
         </is>
       </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-04.png</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: UI「修正依頼」→ POST /mocks/{id}/revise/stream は SSE 200 で stage=loading → generating(provider=relay) → error code=bridge_offline「お使いの PC の Bridge がオフライン」で終了、画面に接続手順の案内、版は v1 のまま (新版なし)。AI 実行経路 (Bridge) が無い / 解除条件: Mac の Bridge を接続して再実行</t>
         </is>
       </c>
     </row>
@@ -9939,14 +10097,19 @@
           <t>差分に指示した箇所だけが出る。指示していない作り込みは旧版のまま残る</t>
         </is>
       </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-05.png</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>場所=cloud / GAP-147 回帰</t>
+          <t>版履歴の「v2 と表示中バージョンの差分」→ GET /mocks/{v3}/diff/{v2} 200、差分は hero-sub の 1 行 (+「商談を一画面で、迷わず。」/ −「商談を一画面で。」) だけで他の作り込みは旧版のまま (追加 1 行・削除 1 行)。ただし v3 は AI 改訂 (J45-04, Bridge 要) ではなく import で積んだため GAP-147 回帰 (AI が指示外を書き換えない) の本体は未検証 / 解除条件: Mac の Bridge で J45-04 を流す</t>
         </is>
       </c>
     </row>
@@ -9999,14 +10162,19 @@
           <t>複製版が履歴に増える</t>
         </is>
       </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-06.png</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>「…」相当のバージョン一覧メニューから「v1 を複製」→ POST /mocks/{id}/duplicate 201、v2 (meta duplicated_from_version=1) が履歴に増える (1→2)、画面のバージョン一覧にも v2 が出る</t>
         </is>
       </c>
     </row>
@@ -10060,14 +10228,19 @@
           <t>複製版は履歴から消える。唯一の版は 409 で拒否され、残る</t>
         </is>
       </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-07.png</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>複製版 v2 を「破棄」→「破棄を確定」(2 段階) → POST /mocks/{v2}/discard 200、履歴 2→1 で v2 が消える。残った唯一の版 v3 を同様に破棄 → POST 409 (確定済みのフェーズの成果物は変更できません。追加や修正は次のフェーズで行ってください。)、画面に「確定済みのフェーズの成果物は変更できません。追加や修正は次のフェーズで行ってください。」、v3 は残る (履歴 1 件・GET 200)。所見: 唯一の版の 409 メッセージが「確定済みのフェーズの成果物は変更できません」になっている (フェーズ1 は active。routes/mocks discard_mock_version が ValueError=唯一版 と MockPhaseFrozen を同じ文言に丸めている) — 理由が誤って伝わる</t>
         </is>
       </c>
     </row>
@@ -10121,14 +10294,19 @@
           <t>保存内容が反映されて残る。次のモック生成の前提として使われる</t>
         </is>
       </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-08.png</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>デザインノートに本文を書いて保存 → PUT /projects/{id}/design-note 200、再読み込み後も同じ本文が欄に残り GET /design-note も一致。「次のモック生成の前提として使われる」は生成が Bridge 要で未検証</t>
         </is>
       </c>
     </row>
@@ -10182,14 +10360,19 @@
           <t>コメントが一覧に出て担当 AI 社員に通知される (実送信できない環境では送信ログ/キュー投入で代替)。解決で状態が遷移する</t>
         </is>
       </c>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K151" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-09.png</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI でコメント投稿 → POST /comments 201 (target_type=mock)、画面のコメント一覧に出る; 「解決」→ PATCH 200 status=resolved、unresolved-count 2→1 (状態遷移は OK)。期待の「担当 AI 社員に通知される (送信ログ/キュー)」は通知処理・送信ログ・キューが存在せず観測できない (J46-03 と同じ) → 通知部分が不成立</t>
         </is>
       </c>
     </row>
@@ -10242,14 +10425,19 @@
           <t>フェーズごとの最新版だけが一覧に出る状態になる</t>
         </is>
       </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-10.png</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>フェーズ1 を確定 (confirm 無し → 403 / confirm=true → 200) → フェーズ2 が active。フェーズ2 で import (v4) と複製 (v5) を積む。GET /mocks: delivery_phase_id=phase1 → v3 のみ / phase2 → v4,v5。画面: 既定 (フェーズ2) の一覧は「QA-D LP トップ v5」1 枚だけ、ヘッダーのフェーズ切替 (aria-label フェーズ切替（表示中: フェーズ2）) の一覧「フェーズ1 ✓確定済み 成果物7・モック1」を選ぶと一覧は「QA-D LP トップ v3」1 枚 + 「確定のスナップショットを表示中」表示 (GET /mocks?delivery_phase_id=phase1) — フェーズごとの最新版だけが出る</t>
         </is>
       </c>
     </row>
@@ -10302,14 +10490,19 @@
           <t>拒否され、新版が増えない (凍結が守られる)</t>
         </is>
       </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-11.png</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>凍結フェーズのモック v3 への POST /revise → 409 (確定済みのフェーズの成果物は変更できません。追加や修正は次のフェーズで行ってください。)、POST /discard → 409、POST /duplicate → 201 (複製は active フェーズ 2 に積まれる); 版数 2→3。UI: 修正依頼 → SSE 200 phase_frozen、alert=「修正依頼に失敗しました。時間をおいて再度お試しください。」。所見: UI の修正依頼 (SSE) は error.code=phase_frozen とメッセージ「「フェーズ1」は確定済みのため変更できません」を受け取っているのに、画面の alert は汎用の「修正依頼に失敗しました。時間をおいて再度お試しください。」で理由を出さない (再試行を促すのは誤誘導)。入力欄も凍結フェーズで disabled になっていない</t>
         </is>
       </c>
     </row>
@@ -11869,14 +12062,19 @@
           <t>ドラフトが一覧に出て、参照したナレッジと生成トレースが記録される</t>
         </is>
       </c>
-      <c r="K177" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K177" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-01.png</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: UI「トニーにドラフト生成を依頼」→ POST /sales-docs/generate 503 (お使いの PC の Bridge がオフラインです。Bridge アプリを起動してから、もう一度お試しください。)。AI 実行経路 (Bridge) が無く、依存 J35-01 (ナレッジ) も担当外 / 解除条件: Mac の Bridge を接続して再実行</t>
         </is>
       </c>
     </row>
@@ -11930,14 +12128,19 @@
           <t>一覧に出て、編集が反映される</t>
         </is>
       </c>
-      <c r="K178" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-02.png</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>種別=見積書で「AI を使わず保存」→ POST /sales-docs 201 (v3)、保存済み一覧 2→3 件・画面に出る; 「編集」→ 設計 300,000→350,000 / 合計 1,900,000→1,950,000 に直して「保存」→ PATCH 200、再取得 summary とプレビューに反映</t>
         </is>
       </c>
     </row>
@@ -11990,14 +12193,19 @@
           <t>PDF が得られ、内容が編集後の状態と一致する</t>
         </is>
       </c>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-03.png</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI「PDF」→ GET /sales-docs/{id}/pdf 200 で blob DL (sales-doc-d5961cf2.pdf 2725 bytes)、API でも 200 application/pdf attachment (UI DL と同一テキスト=True)。PDF 本文 (CID フォント HeiseiKakuGo-W5 / UniJIS-UCS2-H) を復号すると「設計 350,000 円」「合計 1,950,000 円」があり、旧値 300,000 は無い = 編集後の状態と一致</t>
         </is>
       </c>
     </row>
@@ -12051,14 +12259,19 @@
           <t>dry_run では実送信せず送信履歴に dry_run と記録される。本送信ではクライアントにメールが届く (実送信できない環境では送信ログ/キュー投入で代替)</t>
         </is>
       </c>
-      <c r="K180" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K180" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-04.png</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>dry_run: 宛先 qa-jD-20260903-1@example.com で「クライアントにメール送信」→ POST /sales-docs/{id}/send 201 dry_run=true、送信履歴に dry_run=true で記録され画面にも「dry-run（メール未設定）」バッジ (実送信しない・偽装しない = OK)。本送信: 本番環境にメール送信 (Resend) が未設定のため dry_run にしかならず、本送信は不可 / 解除条件: 本番/staging にメール送信プロバイダを設定 (G-11: 外部リソース未プロビジョニング)。所見: 送信ダイアログにも API にも dry_run/本送信を利用者が選び分ける手段は無く (dry_run はサーバーがメール設定の有無で決める)、正本の「dry_run で送信 → 本送信」の操作列と設計が食い違う</t>
         </is>
       </c>
     </row>
@@ -12111,14 +12324,19 @@
           <t>宛先・日時・dry_run の別が一覧に出る</t>
         </is>
       </c>
-      <c r="K181" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-05.png</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>GET /sales-docs/{id}/sends 1 件 (to_email・created_at・dry_run=true)、画面の送信履歴カードに宛先・日時・「dry-run（メール未設定）」バッジ が出る</t>
         </is>
       </c>
     </row>
@@ -12171,14 +12389,19 @@
           <t>日本語のエラーで拒否され、送信履歴に増えない</t>
         </is>
       </c>
-      <c r="K182" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K182" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-06.png</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI: 宛先 not-an-email で送信 → 画面側 (input type=email のブラウザ標準検証) で止まり POST は飛ばない。アプリ自身のエラー文言は無く、表示されるのはブラウザ UI 言語の既定文 (本環境では英語「Please include an '@' in the email address.」— 日本語 Chrome なら日本語)。API 直叩き: 'not-an-email' → 422「送信内容を確認してください（入力内容: 形式が正しくありません）。」、'foo@' → 422。送信履歴 1→1 (増えない)。期待の「日本語のエラーで拒否」はアプリの文言としては出ない</t>
         </is>
       </c>
     </row>
@@ -12231,14 +12454,19 @@
           <t>一覧から消え、論理削除が記録される。送信履歴は残る</t>
         </is>
       </c>
-      <c r="K183" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K183" s="5" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-07.png</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>場所=cloud</t>
+          <t>UI「v3 を削除」→ 確認 → DELETE /sales-docs/{id} 204、一覧 3→2 件・画面から消える、GET detail 404。送信履歴は削除後 GET /sales-docs/{id}/sends → 404 (ドラフトが不可視になると履歴も API/画面から辿れない — DB の行は残るが観測できない)。論理削除の監査は運営 API のみで観測不能</t>
         </is>
       </c>
     </row>
@@ -14910,14 +15138,19 @@
           <t>着手可から実装中に遷移し、Bridge で worker が起動して実行モニター (S-I03) に出る。監査ログ execution_started が記録される</t>
         </is>
       </c>
-      <c r="K224" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K224" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-06.png</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: 「再生」→ POST /tasks/{id}/play 202、タスクは lifecycle=in_progress / dispatch_status=queued で投入され executions に 1 件 (running)、監査 task.play:task:d01024c7。Bridge の worker 起動・実行モニター表示は Bridge が無く未検証 / 解除条件: Mac の Bridge を接続</t>
         </is>
       </c>
     </row>
@@ -15036,14 +15269,19 @@
           <t>ログが逐次流れ、status の変化が画面に反映される</t>
         </is>
       </c>
-      <c r="K226" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K226" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-07</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: Bridge (本人 PC の Claude Code) で worker が起動して初めて成立する行。本環境に Bridge ハーネスが無く、実行 (running) 状態・実行ログ・テスト結果・スコアを作れない / 解除条件: Mac の Bridge を接続して J48-06 から順に流す。補足: 実行モニター S-I03 は開ける (J48-13 参照) がログの逐次表示は実行が無く未検証</t>
         </is>
       </c>
     </row>
@@ -15161,14 +15399,19 @@
           <t>テストケース単位の結果が出て、実行の記録と一致する</t>
         </is>
       </c>
-      <c r="K228" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K228" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-08</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: Bridge (本人 PC の Claude Code) で worker が起動して初めて成立する行。本環境に Bridge ハーネスが無く、実行 (running) 状態・実行ログ・テスト結果・スコアを作れない / 解除条件: Mac の Bridge を接続して J48-06 から順に流す。補足: 手動作成タスクの「テスト結果」タブは 0 件表示 (J48-03)</t>
         </is>
       </c>
     </row>
@@ -15221,14 +15464,19 @@
           <t>承認待ちを経ずに完了に遷移し、監査ログ auto_approved が記録される</t>
         </is>
       </c>
-      <c r="K229" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K229" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-09</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: Bridge (本人 PC の Claude Code) で worker が起動して初めて成立する行。本環境に Bridge ハーネスが無く、実行 (running) 状態・実行ログ・テスト結果・スコアを作れない / 解除条件: Mac の Bridge を接続して J48-06 から順に流す。スコア 95% 以上の自動承認 (auto_approved) は kanban_complete を Bridge が呼ばないと発生しない</t>
         </is>
       </c>
     </row>
@@ -15282,14 +15530,19 @@
           <t>承認待ちに出る。承認で done に遷移し、監査ログ approval_required / inbox_entry_resolved が記録される</t>
         </is>
       </c>
-      <c r="K230" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K230" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-10</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: Bridge (本人 PC の Claude Code) で worker が起動して初めて成立する行。本環境に Bridge ハーネスが無く、実行 (running) 状態・実行ログ・テスト結果・スコアを作れない / 解除条件: Mac の Bridge を接続して J48-06 から順に流す。承認待ち (awaiting) は Bridge の完了報告でしか作れない (PATCH lifecycle_stage で作ると実行スコアが無く承認フローの検証にならない)</t>
         </is>
       </c>
     </row>
@@ -15343,14 +15596,19 @@
           <t>差戻で要対応 (blocked) に遷移し、再試行で着手可へ戻る。retry_count が 1 増えて記録される</t>
         </is>
       </c>
-      <c r="K231" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K231" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-11</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: J48-10 (承認待ち) が作れないため差戻・再試行の起点が無い / 解除条件: J48-10 を Mac の Bridge で流す</t>
         </is>
       </c>
     </row>
@@ -15403,14 +15661,19 @@
           <t>自動再実装をせず、人間介入を要求する状態で固定される。監査ログ force_intervention が記録される</t>
         </is>
       </c>
-      <c r="K232" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K232" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-12</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: J48-11 (差戻→再試行) を 4 回起こすには Bridge の実行が要る / 解除条件: J48-11 を Mac の Bridge で流す</t>
         </is>
       </c>
     </row>
@@ -15463,14 +15726,19 @@
           <t>接続中の worker 数と並列枠が実数で反映される。イベント集約に直前の実行が記録されている</t>
         </is>
       </c>
-      <c r="K233" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K233" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-13.png</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: GET /bridge/status = {"running_count":0,"queued_count":1,"completing_count":0,"spawning_count":0,"dead_count_24h":0,"parallel_limit":5,"avail; S-I03 の表示 ["Bridge（あなたの PC で動くデスクトップアプリ）がローカル Claude Code を並列起動し、FastAPI 上のディスパッチャがタスクを差配します。実行は完全","Bridge 未接続","同時実行できる数","同時実行枠が空いたら自動で開始）","並列上限を超えた分は、ここに積まれます"]。worker 接続と直前の実行イベントは Bridge が無く未検証 / 解除条件: Mac の Bridge を接続</t>
         </is>
       </c>
     </row>
@@ -15523,14 +15791,19 @@
           <t>キューから外れ、実行されない状態に戻る</t>
         </is>
       </c>
-      <c r="K234" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K234" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-14.png</t>
         </is>
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>J48-06 で queued にしたタスクを S-I03 の「キュー取消」 → 200、lifecycle in_progress/queued → ready/null (実行されない状態に戻る)、executions=cancelled</t>
         </is>
       </c>
     </row>
@@ -15583,14 +15856,19 @@
           <t>実行が cancelled で閉じ、席が返る。タスクは要対応として残る</t>
         </is>
       </c>
-      <c r="K235" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K235" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-15</t>
         </is>
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: 実行中 (spawning/running) のセッションは Bridge が無いと作れない。queued 状態で POST /tasks/{id}/dispatch-stop → 409 (いまの状態ではこの操作を行えません。画面を再読み込みしてお試しください。) で「実行中でない」と拒否 (queued は J48-14 のキュー取消で戻す設計)。/ 解除条件: Mac の Bridge で J48-06 を流し running にしてから停止</t>
         </is>
       </c>
     </row>
@@ -15643,14 +15921,19 @@
           <t>次の pick でそのタスクが最優先で実行中に遷移する</t>
         </is>
       </c>
-      <c r="K236" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K236" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-16</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: 「順番待ちから 1 件追加」(POST /dispatch/promote) の効果は次の pick (Bridge の kanban.pick) でしか観測できない / 解除条件: Mac の Bridge を接続</t>
         </is>
       </c>
     </row>
@@ -15703,14 +15986,19 @@
           <t>PID ポーリングで検出され、自動で再 spawn される。監査ログ worker_dead_reclaimed が記録される</t>
         </is>
       </c>
-      <c r="K237" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K237" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-18</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>場所=mac / G-15</t>
+          <t>場所=mac / G-15: 実行中の claude プロセスを kill する操作は本人 PC 側 / 解除条件: Mac の Bridge で実行中に kill</t>
         </is>
       </c>
     </row>
@@ -15763,14 +16051,19 @@
           <t>完了扱いにならず、要対応として残る状態になる。空の要約が完了として記録されない</t>
         </is>
       </c>
-      <c r="K238" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K238" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-19</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>場所=mac / G-15</t>
+          <t>場所=mac / G-15: kanban_complete を呼ばず exit 0 する worker は Bridge 側で作る / 解除条件: Mac の Bridge でハーネス worker を用意</t>
         </is>
       </c>
     </row>
@@ -16548,14 +16841,19 @@
           <t>選んだ処理が反映され、確認カードが消える。監査ログ task_paused_for_change が記録される</t>
         </is>
       </c>
-      <c r="K250" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K250" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>journeys-D-prod-20260903.txt#J48-17</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>場所=mac / F-CUC02</t>
+          <t>場所=mac / F-CUC02: 仕様変更の確認カードはチャット (Bridge) で仕様変更を発言し、実行中タスクに紐づくモックの新版が検知されて出る。チャットも実行も Bridge 要 / 解除条件: Mac の Bridge で J41-02 と J48-06 を流す</t>
         </is>
       </c>
     </row>
@@ -16934,14 +17232,19 @@
           <t>本人 PC で修正され、新版として反映される</t>
         </is>
       </c>
-      <c r="K256" s="2" t="inlineStr">
-        <is>
-          <t>TODO</t>
+      <c r="K256" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-12.png</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>場所=mac</t>
+          <t>場所=mac: UI「AI にファイルごと直してもらう」→ POST /outputs/{id}/ai-file-edit 503 (お使いの PC の Bridge がオフラインです。Bridge アプリを起動してから、もう一度お試しください。)、版は 2 のまま。本人 PC の Bridge が無い / 解除条件: Mac の Bridge を接続して再実行</t>
         </is>
       </c>
     </row>
@@ -21100,11 +21403,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>35%</t>
         </is>
       </c>
     </row>
@@ -21115,11 +21418,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12%</t>
+          <t>17%</t>
         </is>
       </c>
     </row>
@@ -21130,11 +21433,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>49%</t>
         </is>
       </c>
     </row>
@@ -21145,11 +21448,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>0%</t>
         </is>
       </c>
     </row>

--- a/apps/web/.qa/e2e-journey/journey-20260903.xlsx
+++ b/apps/web/.qa/e2e-journey/journey-20260903.xlsx
@@ -586,19 +586,19 @@
           <t>500 や白画面にならず、各画面が 0 件の状態として表示される。API は空配列を返し、サーバのエラーログに例外が記録されない</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J00-01.png</t>
+          <t>apps/web/.qa/evidence/ps28-30-prod-20260903.txt</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>期待: 500 や白画面にならず各画面が 0 件で表示 / 実測 (前提の「全テーブルを空にする」は本番 DB のため不可 → データ 0 件の新規アカウントで代替): 19 画面とも白画面ではなく 0 件表示だが、9/19 画面で画面が同時に叩く API のどれかが断続的に 500 (参照 ID 付き) を返す: [["/projects/dashboard", ["GET /me/consents 500"]], ["/employees", ["GET /ai-employees 500"]], ["/workflow", ["GET /approval-inbox?status=pending 500"]], ["/knowledge/review", ["GET /approval-inbox?status=pending 500"]], ["/meetings", ["GET /me/consents 500"]], ["/sales", ["GET /me 500"]], ["/chat", ["GET /me 500"]], ["/projects/settings", ["GET /approval-inbox?status=pending 500"]], ["/projects/vault", ["GET /me 500"]]]。同一 API は直列 30 回だと全 200、同時 10 本だと 1〜2 本が 500 (fly-request-id を証拠に記録)。サーバのエラーログは運営画面でしか見られず未観測</t>
+          <t>再測 2026-09-03 07:09: 同時 10 本 × 3 回、直列 20 本、画面相当 6 本同時 × 5 回で 5xx = 0 (旧 FAIL は EMAXCONNSESSION = GAP-291)。空 DB での 19 画面 0 件表示は本番では不可 (前提のデータ 0 件アカウントで代替済み)</t>
         </is>
       </c>
     </row>
@@ -1701,19 +1701,19 @@
           <t>改訂した内容がそのまま反映されて読める。ダミーの連絡先や存在しないプランが残っていない</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J03-02.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J03-02-terms.png</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>期待: 改訂内容がそのまま読める・ダミー連絡先や存在しないプランが残っていない / 実測: 3 ページとも本文が出ず role=alert「文書の取得に失敗しました。時間をおいて再度お試しください。」(画面が叩く GET /public/legal-documents/{type} が全て 500・参照 ID 付き)。認証付き経路 GET /me/consents では legal_documents 2026-08-22 版が読めるので、anon 経路 (set local role anon) 固有の障害 = G-11 (本番 DB の anon ロール/権限) の疑い。文面の内容 (ダミー連絡先の有無) は本文が出ないため未判定</t>
+          <t>再測 2026-09-03 07:15 (実ブラウザ): /terms 4,581 文字 / /privacy 2,464 文字 / /tokushoho 908 文字が「最終更新 2026年8月22日 · バージョン 2026-08-22」つきで表示。取得失敗の帯なし。旧 FAIL は API 500 (GAP-290/291) が原因</t>
         </is>
       </c>
     </row>
@@ -1832,19 +1832,19 @@
           <t>3 種 (規約/プライバシー/特商法) が版番号つきで一覧に出て、未サインインで読める</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J03-04.png</t>
+          <t>apps/web/.qa/evidence/ps28-30-prod-20260903.txt</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>期待: 3 種が版番号つきで一覧に出て未サインインで読める / 実測: GET /public/legal-documents -&gt; 500 サーバー側で問題が発生しました。時間をおいて、もう一度お試しください。（参照 ID: fcf2c584-cb32-4a60-8070-ccc279f3dcc7）; 画面 /terms (S-A01 新規登録タブの「利用規約」リンクから到達) は role=alert「文書の取得に失敗しました。時間をおいて再度お試しください。|利用規約 | Atelier | Atelier」で本文が出ない (画面が叩いた GET /public/legal-documents/terms_of_service -&gt; 500). 版番号=false</t>
+          <t>再測 2026-09-03 07:09 (transaction pooler 切替後): GET /public/legal-documents?locale=ja 200 (21,622 bytes)、terms/privacy/tokushoho 各 200。旧 FAIL の 500 は Session pooler 上限超過 (GAP-291) が原因</t>
         </is>
       </c>
     </row>
@@ -21403,11 +21403,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>36%</t>
         </is>
       </c>
     </row>
@@ -21418,11 +21418,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>16%</t>
         </is>
       </c>
     </row>

--- a/apps/web/.qa/e2e-journey/journey-20260903.xlsx
+++ b/apps/web/.qa/e2e-journey/journey-20260903.xlsx
@@ -7939,18 +7939,18 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J48-01.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-01-r2.png</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>UI「タスクを追加」→ POST /tasks 201、lifecycle=triage で画面の「準備中」列に出る (一覧 0→1)。しかしモーダルの入力は タイトル/分類 (機能グループ)/見積 (時間)/種別
+          <t>[再測 R2] UI「タスクを追加」→ POST /tasks 201、lifecycle=triage で画面の「準備中」列に出る (一覧 0→1)。モーダルの入力は タイトル/分類 (機能グループ)/見積 (時間)/種別
 feature
 screen
 foundation
 verification
 infrastructure
-migration/対象画面 (任意 — 例: ログイン画面) だけで、依存・受入基準・仕様書を指定する欄が無く、作成されたタスクは dependencies=[]・acceptance_criteria_id=null・仕様書リンク無し (画面名を入れたのでモック QA-D LP トップ には紐づく)。期待の「依存・受入基準・仕様書がリンクされて記録される」が満たされない。監査: dashboard recent_activities に task.create:task:d01024c7</t>
+migration/対象画面 (任意 — 例: ログイン画面) で、依存・受入基準・仕様書を指定する欄=0 個。作成されたタスクは dependencies=[]・acceptance_criteria_id=null・仕様書リンク無し (対象画面 → mock_screen_name=QA-R2 LP トップ には紐づく) → 期待の「依存・受入基準・仕様書がリンクされて記録される」が満たされない</t>
         </is>
       </c>
     </row>
@@ -8010,12 +8010,12 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J48-02.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-02-r2.png</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>期待: 依存漏れの警告が出て、保存時も警告つきで記録される / 実測: 「タスクを追加」モーダルに依存を入力する欄が無く (0 個)、依存空のまま保存 → POST /tasks 201 で黙って通る (画面の警告 0 件、カードにも警告表記なし、task.dependencies=[]・metadata/blocked_reason に警告の記録なし)</t>
+          <t>[再測 R2] 期待: 依存漏れの警告が出て、保存時も警告つきで記録される / 実測: 「タスクを追加」モーダルに依存を入力する欄が 0 個、依存空のまま保存 → POST /tasks 201 で黙って通る (画面の警告 0 件、カードに警告表記なし — 前判定の「警告表記=true」は自分で付けたタイトル「Nebula-2 依存なし」が検出語に当たった誤検出、task.dependencies=[]・metadata/blocked_reason に警告の記録なし)。通し D と同じ (GAP-303 未着手)</t>
         </is>
       </c>
     </row>
@@ -8206,12 +8206,12 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J48-05.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-05-r2.png</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>UI でコメント投稿 → POST /comments 201 (target_type=task)、GET /comments 1 件、画面のコメント一覧に本文が出る。期待の「担当 AI 社員に通知される (送信ログ/キュー投入)」は通知処理・送信ログ・キューが存在せず観測できない (J46-03/J45-09 と同じ) → 通知部分が不成立</t>
+          <t>[再測 R2] UI でコメント投稿 → POST /comments 201 (target_type=task)、GET /comments 1 件、画面のコメント一覧に本文が出る。期待の「担当 AI 社員に通知される (送信ログ/キュー投入)」: 通知の痕跡=false (担当社員のスレッド・approval-inbox・dashboard・API 応答のいずれにも通知の痕跡なし → 不成立)</t>
         </is>
       </c>
     </row>
@@ -8336,12 +8336,12 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J48-21.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-21-r2.png</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>期待: 2 件選んで一括操作で選んだ分だけ着手可に遷移 / 実測: S-I01 の選択チェックボックスは着手可 (ready) のカードにしか無く (準備中のカード D/E は選択不可: チェックボックスは Nebula-1・Nebula-3 のみ)、選択バーの操作も「選択を再生する」だけで一括「着手可」は無い。準備中→着手可はカード単体の「着手可にする」を 1 枚ずつ押すしかない。API POST /tasks/bulk/lifecycle (task_ids 2 件, ready) → 200 updated=2 skipped=[] で D/E=ready・選ばなかった F=triage (不変)、画面の列も D/E=着手可 F=準備中、監査 task.bulk_lifecycle 2 件 — データ層は正しいが画面から一括着手可はできない</t>
+          <t>[再測 R2] 期待: 2 件選んで一括操作で選んだ分だけ着手可 / 実測: S-I01 の選択チェックボックスは着手可のカードにしか無く (準備中カード G/H/I には 0 個、check は 2 件とも不可)、選択バーも出ず、選択バー系の一括「着手可にする」ボタンは無い (画面にあるのはカード単体の「…を着手可にする」6 個 = 1 枚ずつ押すしかない。再実行のハーネスが自分のタイトルの「一括」を含むカード単体ボタンを誤って 1 回押した = E を単体で ready にしただけ)。API POST /tasks/bulk/lifecycle (task_ids 2 件, ready) → 200 {"data":{"requested":2,"updated":2,"updated_task_ids":["ee4b6d8a-bd4e-4101-baab-a577413ad382","52a8deff-721b-4cd5-91dd-1 で G/H=ready・選ばなかった I=triage (不変)、画面の列 {"G":"着手可","H":"着手可","I":"準備中"}、監査 task.bulk_lifecycle ["task.bulk_lifecycle:task:52a8deff","task.bulk_lifecycle:task:ee4b6d8a"] — データ層は正しいが画面から一括着手可はできない (GAP-304 未着手・通し D と同じ)</t>
         </is>
       </c>
     </row>
@@ -8598,12 +8598,12 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J46-01.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-01-r2.png</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>期待: 工程ごとの成果物が一覧に出て三層 (HTML/JSON/MD) が表示される / 実測: GET /outputs 4 件 (estimate/hearing/requirements/verification)。工程画面 S-F01 の成果物欄はどの工程を選んでも同じ 4 件・「成果物 4」で工程ごとに分かれていない。ビューア S-G01 の表示形式タブは実在 format のみで import 成果物は「HTML」だけ (JSON/MD は AI 生成でしか作れず未検証)。しかも HTML 層は content-url が http:// を返すため Mixed Content でブラウザに block され iframe が空 (描画されない)。加えて HTML 成果物で「表を読み込めませんでした。」が常時表示</t>
+          <t>[再測 R2] 期待: 工程ごとの成果物が一覧に出て三層 (HTML/JSON/MD) が表示される / 実測: GET /outputs 5 件 (estimate/requirements/verification/hearing)。S-G01 (?output 無し) は「成果物を選択すると表示します」で成果物を選ぶ一覧=0 個。S-F01 工程ごとの成果物欄=["ヒアリング:0件","要件定義:0件","アーキ設計:0件","デザイン:0件","機能分解:0件"] (工程で分かれる=false)。ビューアの表示形式タブ=["HTML"]、HTML 層は iframe 内本文「1. 目的  QA-R2 案件の要件定義書 v1。Nebul」(Mixed Content 0 件)、alert=["この成果物は表形式ではありません。HTML の成果物は本文プレビューで開けます。"]。JSON/MD タブは import 成果物では未生成 (0 個)</t>
         </is>
       </c>
     </row>
@@ -8656,19 +8656,19 @@
           <t>署名付き URL (content-url) で HTML が iframe に反映される。Storage に実体が存在する (G-11)</t>
         </is>
       </c>
-      <c r="K125" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J46-02.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-02-r2.png</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>期待: 署名付き URL (content-url) で HTML が iframe に反映され Storage に実体がある / 実測: GET /outputs/{id}/content-url?format=html → 200 で署名付き URL (exp+sig)、直接 fetch → 200 text/html 438 bytes・本文一致 (実体は DB 内蔵 mockdb = G-11 実在)、署名改ざん → 403。しかし URL のスキームが http:// のため https の画面で iframe が Mixed Content として block され、プレビューは空のまま (console: This request has been blocked; the content must be served over HTTPS)</t>
+          <t>[再測 R2] GET content-url?format=html → 200 で https の署名付き URL (exp+sig, expires_at=undefined)、画面の iframe src が同 URL、iframe 内に「1. 目的」が描画 (Mixed Content 0 件)。署名 URL を直接取得 → 200 text/html 440 bytes 本文一致 (実体あり = G-11)、署名改ざん → 403</t>
         </is>
       </c>
     </row>
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J46-03.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-03-r2.png</t>
         </is>
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>UI: 対象位置に「2. 機能一覧」(sec-2) を選び投稿 → POST /comments 201、GET /comments に target_element_id=sec-2 で 1 件、画面のコメント一覧に本文表示、unresolved-count 0→undefined。期待の「担当 AI 社員にメール通知 (送信ログ/キュー)」は通知の実装・送信ログ・キューが存在せず観測できない (API 応答にも通知の痕跡なし) → 通知部分が不成立。監査ログ comment_created は運営 API のみで観測不能</t>
+          <t>[再測 R2] UI: 対象位置に「2. 機能一覧」(sec-2) を選び投稿 → POST /comments 201、GET /comments に target_element_id=sec-2 で 1 件、画面のコメント一覧に本文=true、unresolved-count 0→1。期待の「担当 AI 社員にメール通知 (送信ログ/キュー)」: 通知の痕跡=false (API 応答に通知フィールド無し、担当社員のスレッド一覧・approval-inbox・tool-approvals に変化なし = 通知処理・送信ログ・キューが存在せず観測できない → 不成立)。監査 comment_created: dashboard recent_activities に増えた項目=["comment.create:comment:01bde75a"] (comment 対象の監査は運営 API のみで観測不能)</t>
         </is>
       </c>
     </row>
@@ -9518,12 +9518,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J46-16.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-16-r2.png</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>API (Bearer) では html (text/html attachment) / xlsx (application/vnd.openxmlformats-officedoc attachment) が得られる。しかし画面の「HTML で保存」「Excel で保存」は API への素の &lt;a href&gt; で Authorization が付かず、クリック結果=HTML で保存: HTTP 404 → 遷移先 /outputs/90f5fb07-96af-4b90-8259-e37315d8c43c/export?format=html 「メインコンテンツへスキップ ワークスペース · QA-D WS 20260903 プロジェクト AI社員 ナレッジ テン」 / Excel で保存: HTTP 404 → 遷移先 /outputs/90f5fb07-96af-4b90-8259-e37315d8c43c/export?format=xlsx 「メインコンテンツへスキップ ワークスペース · QA-D WS 20260903 プロジェクト AI社員 ナレッジ テン」 (画面からはファイルが得られない)。監査ログ output_downloaded は export_output に監査書込が無く記録されない</t>
+          <t>[再測 R2] 画面の「HTML で保存」「Excel で保存」= HTML で保存: HTTP 404 (Authorization 無し) → 遷移先 /outputs/177da0f1-d3ed-4e95-ba54-bd48b80c7b67/export?format=html 「メインコンテンツへスキップ ワークスペース · QA-R2 WS 2026090」 / Excel で保存: HTTP 404 (Authorization 無し) → 遷移先 /outputs/177da0f1-d3ed-4e95-ba54-bd48b80c7b67/export?format=xlsx 「メインコンテンツへスキップ ワークスペース · QA-R2 WS 2026090」。API (Bearer) は html 200 / xlsx 200 (4987 bytes) で得られる。監査 output_downloaded は dashboard に増えず (["task.create:task:9da8b7d4","task.create:task:22fa0df7"]) 観測できない</t>
         </is>
       </c>
     </row>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J46-18.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-18-r2.png</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>期待: 403 で拒否 / 実測: viewer (PATCH role=viewer 200) の GET /outputs 200・POST /comments 201 (閲覧・コメント可) は期待通り。編集系は POST /sheet → [500, 500, 500] (恒常 500: サーバー側で問題が発生しました。時間をおいて、もう一度お試しください。（参照 ID: 1d80d498-50fc-4b13-8253-3ff52d9c7268）)、POST /restore → [500, 500, 500] (恒常 500)、POST /revise → 503 (Bridge)、POST /share-links → 201 ×2 (閲覧者がクライアント共有リンクを発行できてしまう = 権限漏れ)。成果物自体は不変 (版数 xlsx=2 req=3)。画面でも編集/共有リンク発行/投稿ボタンが閲覧者に表示される</t>
+          <t>[再測 R2] 期待: 403 で拒否され成果物は変わらない・閲覧とコメントはできる / 実測: PATCH role=viewer 200。viewer の GET /outputs/{id} 200 (閲覧可)、POST /comments 201 (コメント可) は期待通り。編集系 (各 3 回): POST /sheet [403,403,403]「この操作を行う権限がありません。」(GAP-282 の 500→403 は解消)、POST /share-links [403,403,403]「共有リンクを発行する権限がありません。」(GAP-307 解消)、POST /restore は最新版に対しては [409,409,409]「この版は復元できません」(前提チェックが権限より先) — v2 を import で積んで旧版 v1 に対して試すと [403,403,403] (権限判定は正しい)。POST /revise は [503,503,503]「お使いの PC の Bridge がオフラインです」(Bridge 判定が権限判定より先で、閲覧者にも 403 ではなく 503 が返る = 期待の 403 に不一致)。版数 xlsx 2→2・要件定義 2→3 (増分は対照の owner restore のみ、viewer の操作では不変)。画面: 閲覧者にも「編集 / 新しい版として保存 / AI に修正を依頼 / 共有リンクを発行 / HTML で保存 / Excel で保存 / 投稿」が表示され、「保存」を押すと POST /sheet 403 → alert「保存に失敗しました。」(理由が権限だと分からない)</t>
         </is>
       </c>
     </row>
@@ -9714,12 +9714,12 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J46-19.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-19-r2.png</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>期待: 0 件の案内が出てエラーにならない / 実測: GET /outputs=0 件。S-G01 (/outputs?project=空案件) は「成果物を選択すると表示します。」と出るだけで、成果物を選ぶ一覧・ピッカーが無く 0 件であることも案内しない (件数に関係なく同じ文言)。工程画面 S-F01 側は「成果物 0」と表示。alert 0 件・API エラー無し (JS console の 500 は GET /me/consents の初回 500 = 環境要因)</t>
+          <t>[再測 R2] 期待: 0 件の案内が出てエラーにならない / 実測: GET /outputs=0 件。S-G01 は「成果物を選択すると表示します」(0 件の案内=false)、alert 0 件、API 5xx=0 件、工程画面の成果物欄=「成果物 0 件)」</t>
         </is>
       </c>
     </row>
@@ -9902,19 +9902,20 @@
           <t>画面ごとの最新版がプレビューに反映される (署名付き URL)</t>
         </is>
       </c>
-      <c r="K144" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J45-02.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-02-r2.png</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>一覧のカードから選ぶ → /mocks?mock={id} → GET /mocks/{id}/content-url 200 (署名付き、実体 mockdb は https で直接取得 → 200 本文一致)。しかし URL が http:// スキームのため https の画面で iframe が Mixed Content として block (console 1 件、iframe 本文空) → プレビューに最新版が反映されない (J46-02 と同根)</t>
+          <t>[再測 R2] 一覧のカードから選ぶ → /mocks?mock={id} → GET /mocks/{id}/content-url 200 (https の署名付き URL)、iframe に最新版 v1 の本文「Nebula 商談管理
+商談を一画面で」が描画 (Mixed Content 0 件)、署名 URL の直接取得 200 本文一致</t>
         </is>
       </c>
     </row>
@@ -10367,12 +10368,12 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J45-09.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J45-09-r2.png</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>UI でコメント投稿 → POST /comments 201 (target_type=mock)、画面のコメント一覧に出る; 「解決」→ PATCH 200 status=resolved、unresolved-count 2→1 (状態遷移は OK)。期待の「担当 AI 社員に通知される (送信ログ/キュー)」は通知処理・送信ログ・キューが存在せず観測できない (J46-03 と同じ) → 通知部分が不成立</t>
+          <t>[再測 R2] UI でコメント投稿 → POST /comments 201 (target_type=mock)、GET /comments 1 件、画面のコメント一覧に出る、unresolved-count 3→4; 「解決」→ PATCH 200 status=resolved、unresolved-count 4→3 (状態遷移は OK)。期待の「担当 AI 社員に通知される (送信ログ/キュー)」: 通知の痕跡=false (ワンダのスレッド・approval-inbox・dashboard・API 応答のいずれにも通知の痕跡なし → 不成立、GAP-299 未着手)</t>
         </is>
       </c>
     </row>
@@ -12396,12 +12397,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J47-06.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-06-r2.png</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>UI: 宛先 not-an-email で送信 → 画面側 (input type=email のブラウザ標準検証) で止まり POST は飛ばない。アプリ自身のエラー文言は無く、表示されるのはブラウザ UI 言語の既定文 (本環境では英語「Please include an '@' in the email address.」— 日本語 Chrome なら日本語)。API 直叩き: 'not-an-email' → 422「送信内容を確認してください（入力内容: 形式が正しくありません）。」、'foo@' → 422。送信履歴 1→1 (増えない)。期待の「日本語のエラーで拒否」はアプリの文言としては出ない</t>
+          <t>[再測 R2] UI: 宛先 'not-an-email' → POST 未送信、アプリのエラー文言=[] (ブラウザ標準の検証のみ: validationMessage「Please include an '@' in the email address. 'not-an-email' is missing an '@'.」= ブラウザ UI 言語依存) / 'foo@' → POST 未送信、アプリのエラー文言=[] (ブラウザ標準の検証のみ: validationMessage「Please enter a part following '@'. 'foo@' is incomplete.」= ブラウザ UI 言語依存); API: 'not-an-email' → 422 "送信内容を確認してください（入力内容: 形式が正しくありません）。"、'foo@' → 422; 送信履歴 1→1 (増えない)</t>
         </is>
       </c>
     </row>
@@ -12461,12 +12462,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J47-07.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-07-r2.png</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>UI「v3 を削除」→ 確認 → DELETE /sales-docs/{id} 204、一覧 3→2 件・画面から消える、GET detail 404。送信履歴は削除後 GET /sales-docs/{id}/sends → 404 (ドラフトが不可視になると履歴も API/画面から辿れない — DB の行は残るが観測できない)。論理削除の監査は運営 API のみで観測不能</t>
+          <t>[再測 R2] UI「v2 を削除」→ 確認 → DELETE /sales-docs/{id} 204、一覧 2→1 件・画面から消える、GET detail 404。送信履歴: 削除前 1 件 → 削除後 GET /sales-docs/{id}/sends 404 (ドラフトが不可視になると送信履歴も API/画面から辿れない)。論理削除の監査は運営 API のみで観測不能 (dashboard 増分=["task.update:task:7e00a0ab"])</t>
         </is>
       </c>
     </row>
@@ -12526,12 +12527,12 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J44-01.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-01-r2.png</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>期待: 画面表示が GET /cron-actions と一致 / 実測: 一覧・コストは出るが、作成フォーム (ScheduleBuilder) の種類名・コスト表示は画面側のハードコード (ACTIONS 定数) で、API の title (例 API「タスク自動再生」↔ 画面「着手可のタスクを再生する」) / cost_label (API「本人の Claude プラン枠」「コスト無料」↔ 画面「プラン枠」「無料」) と 6 種中 4 種で文言不一致。GET /cron-actions は取得されるが作成フォームには反映されていない (GAP-179 の「唯一の信頼源」に反する)</t>
+          <t>[再測 R2] 期待: 画面表示が GET /cron-actions と一致 / 実測: 6 種中 欠け 6 ["task_replay","knowledge_organize","industry_extract","report_summary","daily_digest","weekly_burndown"]、旧文言残存 ["着手可のタスクを再生する","ナレッジを整理する","横断パターンを抽出する","プラン枠","無料"]</t>
         </is>
       </c>
     </row>
@@ -15007,19 +15008,19 @@
           <t>raw トークンが 1 度だけ表示され、一覧に出る。再読み込み後は二度と出ない</t>
         </is>
       </c>
-      <c r="K222" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K222" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J40-04.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J40-04-r2.png</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>期待: raw が 1 度だけ表示され一覧に出る・再読み込み後は出ない / 実測: UI「接続トークンを発行」→ POST 201 で raw (43 文字) が発行直後の画面に 1 度表示され、再読み込み後は画面に出ず GET /bridge-tokens にも raw 無し (ここは期待通り)。しかし「一覧に出る」が不安定: 発行 3 秒後の GET /bridge-tokens が 200 {data:[]} (発行済みトークンが 0 件) で返り、その後 20 回連続 GET で 2 回 (10%) が 500「サーバー側で問題が発生しました（参照 ID 付き）」。同じ本人・同じ条件で件数 0 / 3 / 500 が揺れる (list_tokens が別プール _service_session を使う経路の不安定さと推定)</t>
+          <t>[再測 R2] UI「接続トークンを発行」→ POST 201、raw (43 文字) が発行直後の画面に 1 度表示。発行直後 0〜3.5 秒の GET /bridge-tokens は全て 200 で発行 id を含み token フィールド無し (4 回)。再読み込み後は raw が画面に出ず、パネルの一覧に発行済みトークン (id/label/日時) が出る。20 回連続 GET の分布 {"200/1件":20} (500 なし・件数の揺れなし)、include_revoked=true → 200</t>
         </is>
       </c>
     </row>
@@ -17895,12 +17896,12 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J43-03.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J43-03-r2.png</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>期待: 送信失敗時に入力欄へ文章が戻り、押し直すだけで再送できる / 実測: Bridge 未接続で送信 → POST /chat/threads/{id}/stream 200 (SSE) → 画面 alert「お使いの PC がまだ接続されていません。設定画面の「Bridge を接続」から接続すると、AI 機能を使えるようになります。」が出るが、入力欄は空に戻り (value="")、文章はユーザー発話として DB に保存されるだけ (GET messages に role=user 1 件・assistant 無し・queued 0 件)。押し直しても送るものが無く再送されない。再現: S-E01 でスレッドを開き、Bridge 未接続のまま文章を入力して送信 → 入力欄が消える</t>
+          <t>[再測 R2] 期待: 入力欄に文章が戻り押し直しで再送 / 実測: 送信 API=POST 200 /chat/threads/3a0342c1-d6b9-467b-a1fc-81c4432c18e8/stream, POST 200 /chat/threads/3a0342c1-d6b9-467b-a1fc-81c4432c18e8/queued/consume、alert=["お使いの PC がまだ接続されていません。設定画面の「Bridge を接続」から接続すると、AI 機能を使えるようになります。"]、入力欄="" (一致=false)、DB messages 1→2、押し直し API=[]</t>
         </is>
       </c>
     </row>
@@ -21403,11 +21404,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>37%</t>
         </is>
       </c>
     </row>
@@ -21418,11 +21419,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>15%</t>
         </is>
       </c>
     </row>

--- a/apps/web/.qa/e2e-journey/journey-20260903.xlsx
+++ b/apps/web/.qa/e2e-journey/journey-20260903.xlsx
@@ -2301,12 +2301,12 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J10-07.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J10-07-r1.png</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>期待: 日本語エラーで拒否・WS 増えない / 実測: errors=[] native={"noValidate":false,"vm":"","req":false} POST= WS 件数=0</t>
+          <t>[再測 R1] 期待: 日本語エラーで拒否・WS 増えない / 実測: errors=[] POST=未送信 disabled=true WS 件数=0</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3488,12 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J15-01.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-01-r1.png</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>期待: 登録直後に 3 ステップのウォークスルーが出て、完了すると次回から出ない状態が記録される / 実測: 登録直後は /projects に着地しウォークスルーは出ない (sawWalk=false)。/t-uc-35 を直接開くと 3 ステップ (ようこそ Atelier へ→ワークスペースを作成→プロジェクトを始める) は進めるが「完了」ボタンは無く (最終: 戻る,次へ(disabled))、再読み込みすると先頭「ようこそ Atelier へ」に戻る。完了状態の記録 (API 呼び出し/localStorage) は無し</t>
+          <t>[再測 R1] 期待: 初回だけ 3 ステップ・完了で次回から出ない / 実測: 登録後 url=/projects 表示=false steps=["最初のワークスペースを作成"] 完了=false ls={} 再表示=false</t>
         </is>
       </c>
     </row>
@@ -3553,12 +3553,12 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J15-03.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-03-r1.png</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>期待: 保存後にヘッダーの表示名に反映され、再読み込みしても残る / 実測: PATCH /me 200 で保存は成功し GET /me・再読み込み後の入力値/ヘッダーは「QA jA2 改名太郎」だが、保存直後 (再読み込み前) のヘッダーは旧名「アカウント: QA jA2 1」のまま (G-12: 切替直後に反映されない)。監査ログは未観測</t>
+          <t>[再測 R1] 期待: 保存直後にヘッダー反映・再読み込みでも残る / 実測: PATCH=200 直後反映=false (ヘッダー「Q QA jR1 WS1 Q」) 再読み込み後=false ※本番 web バンドルに GAP-270 の文字列 (atelier:me-changed) が無い = Vercel デプロイが main に追随していない</t>
         </is>
       </c>
     </row>
@@ -3685,12 +3685,12 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J15-05.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-05-r1.png</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>期待: 選んだ WS が現在 WS になり、案件一覧がその WS のものに切り替わる / 実測: t-uc-38 で WS2 を選ぶとヘッダーの現在 WS は「QA jA2 WS2」になり localStorage も WS2 で再読み込み後も残る (正) が、/projects の一覧は GET /projects?limit=20 (workspace_id 無し) を叩き「3 件のアクティブプロジェクト」= WS1 の Nebula/Sirius + WS2 の Vega を全部出す = 案件一覧が WS に切り替わらない。加えてヘッダーの現在プロジェクトは WS1 の Nebula のまま (G-13: WS 切替 × 現在案件の組み合わせ)</t>
+          <t>[再測 R1] 期待: 選んだ WS が現在 WS になり案件一覧がその WS に切り替わる (再読み込み後も) / 実測: 現在 WS=WS2 だが一覧は GET ["/projects?limit=20"] で Vega=true Orion=true Sirius=true (WS1 の案件が混在)、現在案件の解除=false (header「Q QA jR1 WS2 / プロジェクト Q」) / 再読み込み後 Vega=true Orion=true Sirius=true ※本番 web バンドルに GAP-271/277 の文字列 (削除済みのプロジェクトはありません / アクティブに戻す) が無い = Vercel デプロイが main (a34f488) に追随していない</t>
         </is>
       </c>
     </row>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>evidence/shots/journeys/J30-05.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J30-05-r1.png</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>S-B02: 承認待ち 0 (GET /approval-inbox と一致=true), 未解決コメント 1 (一致=true), 最新成果物「要件定義書v2」表示=true, 工程進捗 2/10 表示=false; API task_counts={"triage":2,"ready":0,"in_progress":0,"blocked":0,"awaiting":0,"done":0,"total":2}</t>
+          <t>[再測 R1] 期待: 各カードが実データと一致 / 実測: 工程進捗 1/10 表示=false (画面: 全体進捗率 / 0% / 工程 0/9 完了 / 未承認 INBOX 件数 / 0 / すべて処理済), inbox 一致=true, コメント一致=true, 最新成果物一致=true</t>
         </is>
       </c>
     </row>
@@ -4340,12 +4340,12 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>evidence/shots/journeys/J30-10.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J30-10-r1.png</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>実数表示=true (未完了工程 8 / タスク 2 / 未解決コメント 1 が UI 確認事項と API freeze-check で一致) ; しかし「0 でない間は確定できない」は不成立: UI の確定ボタンは enabled=true、API も残件ありで confirm=true → 200 (捨て案件でフェーズ1 frozen/フェーズ2 active に遷移)</t>
+          <t>[再測 R1] 期待: 実数が出て 0 でない間は確定できない / 実測: 実数表示=true (UI ["・未完了の工程が 9 つあります（提案、見積、契約）","・完了していないタスクが 2 件あります","・未解決のコメントが 3 件あります"] vs API 9/2/3) 確定ボタン enabled=true API freeze=409</t>
         </is>
       </c>
     </row>
@@ -5063,12 +5063,12 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J36-01.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-01-r1.png</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>期待: サイドバーの WS 名に反映 / 実測: PATCH /workspaces 200 で保存され GET も新名だが、保存直後のサイドバー「ワークスペース · QA JA2 WS1 改名」とヘッダー「ワークスペース: QA jA2 WS1 改名」は旧名のまま。再読み込みで初めて「再改名」に変わる (G-12: 直後に反映されない。J15-03 と同型)。※基本情報の保存は POST /account/ai-learning も同時に送る。監査ログ workspace_updated は未観測</t>
+          <t>[再測 R1] 期待: サイドバーに即反映 / 実測: PATCH=200 直後反映=false header「Q QA jR1 WS1 / WS設定 Q」 GET name=QA jR1 WS1 改名</t>
         </is>
       </c>
     </row>
@@ -5392,12 +5392,12 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J36-07.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-07-r1.png</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>期待: 30 日案内・一覧から消える・deleted_at 記録・配下データへのアクセス拒否 / 実測: DELETE=204 30日案内=true 一覧から消えた=true GET ws=404 deleted_at=undefined 配下 projects=200/1 詳細=200 employees=200/10。追加: 削除した WS の案件「QA jA2 使い捨て案件」は /projects 一覧 (GET /projects?limit=20) にも出続ける</t>
+          <t>[再測 R1] 期待: 30 日案内・一覧から消える・deleted_at・配下アクセス拒否・監査 / 実測: DELETE=["204 /workspaces/efb95e0c-7021-4509-9121-cca776c5b4d6"] 30日案内=true 一覧残存=false GET ws=404 配下 projects=200/1 詳細=200 employees=200/10 /projects に Vega=true/true</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J37-02.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J37-02-r1.png</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>期待: 名前・口調・「できること」が出て、スキル名や本文は画面と API のどちらにも含まれない (R-T06) / 実測: 名前・口調プリセット・「できること」は出るが、「できること」欄にスキル名 sales-email / proposal / estimate がそのまま列挙され、画面は GET /skills?limit=200 (スキル台帳) も取得。API: GET /ai-employees/{id} は attached_skills にスキル ID 3 件、GET /ai-employees/templates と /templates/{id} は system_prompt 本文 (「あなたは営業・契約部の部長トニーです。…」43 字) を一般利用者に返す = スキル名・本文が漏れる</t>
+          <t>[再測 R1] 期待: 名前・口調・できることが出てスキル名/本文は画面にも API にも無い / 実測: 名前=true 口調=true できること=true 画面スキル語=["sales-email","proposal","estimate"] GET /skills=1 API漏れ=false templates system_prompt=null default_skills=0</t>
         </is>
       </c>
     </row>
@@ -5647,19 +5647,19 @@
           <t>FORBIDDEN_FIELD で拒否され、DB は変わらない</t>
         </is>
       </c>
-      <c r="K79" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>journeys-A-prod-20260903.txt#J37-04</t>
+          <t>journeys-R1-prod-20260903.txt#J37-04</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>期待: FORBIDDEN_FIELD で拒否・DB 不変 / 実測: 200 {"data":{"id":"2fd8c87c-011a-4419-9d32-6d0be141f908","workspace_id":"3adaebaa-1a52-41c9-8305-b1da3af / 200 {"data":{"id":"2fd8c87c-011a-4419-9d32-6d0be141f908","workspace_id":"3adaebaa-1a52-41c9-8305-b1da3af / 200 / 注入混入=false</t>
+          <t>[再測 R1] system_prompt=422 / attached_skills=422 / 混在 (display_name+system_prompt)=422 で拒否 (detail: "送信内容を確認してください（指示文: この項目は変更できません）。") 。GET 再取得で display_name「トニー」attached_skills も不変・注入文字列の混入なし</t>
         </is>
       </c>
     </row>
@@ -5720,12 +5720,12 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J37-05.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J37-05-r1.png</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>期待: 署名付き URL でアップロードした画像が組織図とチャットに反映され Storage に実体がある / 実測: POST icon-upload-url 200 → 署名付き URL へ PUT 200 → PATCH icon=storage_path 200 → GET icon-url 200 で取得した URL は 200 image/png 79B (Storage に実体あり = G-11 OK)。しかし組織図のノードは頭文字「TO」のまま (img 無し・icon-url の呼び出し無し)、チャット画面も頭文字「ト」= アップロードした画像が画面に反映されない</t>
+          <t>[再測 R1] 期待: 画像が組織図とチャットに反映・Storage に実体 / 実測: upload-url=200 → PUT=200 → PATCH icon=200 → icon-url=200 実体 fetch=200 image/png 70B (Storage に実体あり = G-11 OK) だが、組織図 img=0 (ノード &lt;span aria-label="AI 社員 Tony" role="img" class="inline-flex shrink-0 items-cente, icon-url 呼出 []) チャット img=0 (icon-url 呼出 []) = 画面に画像が反映されない ※本番 web バンドルに GAP-276 の文字列 (ai-employee-icon-url) が無い = Vercel デプロイが main に追随していない</t>
         </is>
       </c>
     </row>
@@ -6048,12 +6048,12 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J38-06.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-06-r1.png</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>期待: 一覧からアーカイブ → アクティブ一覧から消えアーカイブ一覧に出る → 戻すと復帰 / 実測: 一覧のカードにアーカイブ/戻す操作が無い (導線: 新規プロジェクト・絞込 すべて/進行中/アーカイブ のみ)。API PATCH status=archived にすると「進行中」絞込からは消え「アーカイブ」絞込に出るが、既定の「すべて」には残り、見出しの件数「3 件のアクティブプロジェクト」も変わらない (GET /projects?limit=20 を 1 回取りクライアント側で絞る)。PATCH status=in_progress で「進行中」に復帰</t>
+          <t>[再測 R1] 期待: 一覧からアーカイブ→アクティブ一覧から消えアーカイブ一覧に出る→戻すと復帰 / 実測: アーカイブ導線=0 すべてに残存=true アーカイブ表示=false 戻す導線=0 復帰=true タブ=["すべて","進行中","アーカイブ","クライアント案件\nヒアリング中\nQA jR1 案件 Sirius (アーカイブ用)\n\n—\n\n工程 1 / 9\n8 分前更新"] ※本番 web バンドルに GAP-277 の文字列 (アクティブに戻す) が無い = Vercel デプロイが main に追随していない</t>
         </is>
       </c>
     </row>
@@ -6106,19 +6106,19 @@
           <t>一覧にマスク表示で出る。応答と DB に平文が無い (暗号化保存)。監査ログ credential_created が記録される</t>
         </is>
       </c>
-      <c r="K86" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J39-01.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J39-01-r1.png</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>期待: 一覧にマスク表示・応答/DB に平文無し・監査 credential_created / 実測: 画面の「暗号化して保存」→ POST /projects/{id}/credentials が 500 {"detail":"サーバー側の設定に問題があります。運営にお問い合わせください。"} (API 直接・kind を変えても同じ)。本番に暗号化鍵 (vault key) 等のサーバー設定が無く登録できない (G-11: 外部リソース/秘密の実在)。一覧は 0 件のまま</t>
+          <t>[再測 R1] 「暗号化して保存」→ POST /projects/{id}/credentials 201 (本番の Vault 鍵設定済 = G-11 解消)。一覧にマスク表示 (••••4321) で出て、応答にも GET 一覧にも平文は無い (keys=id,project_id,name,kind,last4,created_by_name,created_at,updated_at)。監査 credential.create は credential 対象で利用者向け API に出ず未観測</t>
         </is>
       </c>
     </row>
@@ -6366,19 +6366,19 @@
           <t>招待が一覧に出て、相手に招待メールが届く (実送信できない環境では送信ログ/キュー投入で代替)。監査ログ invitation_sent が記録される</t>
         </is>
       </c>
-      <c r="K90" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>evidence/shots/journeys/J31-01.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J31-01-r1.png</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>一覧に出る=true (role=member, membership 即時作成)。しかし招待メールは送られない (送信ログ/キュー/API 応答のいずれにも送信の痕跡なし — 実装は登録済みメールを即時 membership 化する方式で、メール送信コードが無い)。監査 workspace_member.invite は admin 専用 API のため未確認</t>
+          <t>[再測 R1] WS 設定の招待フォームで qa-jR1-20260903-2@example.com を招待 → POST /workspaces/{ws}/members 201 → 画面と API の一覧に出る (role=member, 登録済みメールを即時 membership 化)。招待メールは実装 (GAP-281: ResendSender 送信 + 監査 workspace_member.invite_mail) が入ったが、監査ログは WS 対象 (target_type=workspace_membership) で利用者向け API に出ず、応答にも送信結果が無く、受信箱も無い = 送信の痕跡を観測できない / 解除条件: 運営の /admin/audit-logs で workspace_member.invite_mail (dry_run / email_id) を照会、または受信箱</t>
         </is>
       </c>
     </row>
@@ -6693,19 +6693,19 @@
           <t>編集操作は 403 で拒否され、閲覧は引き続きできる状態である</t>
         </is>
       </c>
-      <c r="K95" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>evidence/shots/journeys/J31-06.png</t>
+          <t>journeys-R1-prod-20260903.txt#J31-06</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>ロール変更直後・同じトークンで: 案件名変更=403, タスク作成=500 (403 期待), 閲覧 GET project=200 tasks=200; 案件名不変=true</t>
+          <t>[再測 R1] 閲覧者: 案件名変更 403「このプロジェクトを変更する権限がありません。」/ タスク作成 403「この操作を行う権限がありません。」(GAP-282: RLS 拒否が 500 でなく 403)。閲覧 GET project 200 / tasks 200 は引き続き可。案件名は不変</t>
         </is>
       </c>
     </row>
@@ -6765,12 +6765,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>evidence/shots/journeys/J31-07.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J31-07-r1.png</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>閲覧者: シークレット追加=500「サーバー側の設定に問題があります」(403 期待), reveal=404 (対象なし)。根本原因: owner による事前登録 (J39-01 相当) も 500 → 本番にシークレット暗号鍵 (Fernet) が未設定 (G-11)。認可 (403) より先に設定エラーが返るため、閲覧者判定も未達。値漏れ=false, 一覧 GET=200 (0 件)。監査の拒否記録は admin 専用 API のため未確認</t>
+          <t>[再測 R1] 期待: 追加・reveal とも 403 で値は漏れない・監査に拒否 / 実測: 追加は 403「シークレットを追加する権限がありません。」(GAP-278 ② OK) だが **reveal は 403 でなく 200 で平文を返す** (role=viewer の閲覧者が本人パスワードで再認証すると owner が登録したシークレット値がそのまま取れる = 値が漏れる。R-T06 級の権限漏れ)。画面 (S-B04) にも閲覧者に「表示」ボタンが出る。監査の拒否記録は利用者向け API に出ず未観測。再現: viewer の JWT で POST /projects/{pid}/credentials/{cid}/reveal {"password":"&lt;redacted&gt;"} → 200 {"value":"&lt;redacted&gt;"}</t>
         </is>
       </c>
     </row>
@@ -6831,12 +6831,12 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>evidence/shots/journeys/J31-08.png</t>
+          <t>journeys-R1-prod-20260903.txt#J31-08</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>招待リンク・expires_at を持つ招待エンティティが実装に存在しない (POST /workspaces/{id}/members は登録済みメールを即時 membership 化し、招待一覧/期限/リンクの API・UI が無い)。「7 日で期限切れ」の仕様を満たす対象が無いため期待未達</t>
+          <t>[再測 R1] 期待: 期限切れ (7 日) の招待リンクが拒否される / 実測: WS 招待にリンク・expires_at を持つ招待エンティティが依然として無い (未登録メールは 422「このメールアドレスのアカウントは登録されていません。」で招待自体が作れず、メンバー行の keys=workspace_id,user_id,email,display_name,role,joined_at に期限は無い。GET /workspaces/{id}/invitations は 404)。GAP-281 で「招待リンク / 有効期限は仕様未確定のため別途 (T-A-30)」と保留のまま = 期限切れの対象が存在しない</t>
         </is>
       </c>
     </row>
@@ -7085,19 +7085,19 @@
           <t>LAST_OWNER エラーで拒否され、メンバー一覧は変わらない (DB の membership も残る)</t>
         </is>
       </c>
-      <c r="K101" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J36-06.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-06-r1.png</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>期待: LAST_OWNER エラーで拒否され一覧不変 / 実測: 画面のメンバー一覧には自分 (唯一の owner) の削除ボタンが無い。API 直接 DELETE /workspaces/{ws}/members/{自分} は 204 (2 回実行とも) を返すが membership は残る (1 名 owner のまま) = エラーではなく「成功したふりの no-op」。期待の LAST_OWNER エラーが返らない</t>
+          <t>[再測 R1] API DELETE /workspaces/{ws}/members/{自分} → 409「最後の owner は外せません。先に別のメンバーを owner にしてください。」で拒否、メンバー一覧は 1 名 (owner) のまま。UI のメンバー一覧には唯一の owner の削除ボタンが 0 個 (出ない)</t>
         </is>
       </c>
     </row>
@@ -11153,12 +11153,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>evidence/shots/journeys/J34-06.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J34-06-r1.png</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>.exe: UI の input は accept="audio/*,video/*,.txt,.md,.docx,text/plain" で選択を絞るだけで、選択できてしまえば (D&amp;D/強制選択) そのまま送信され、日本語エラーは出ず一覧に「setup.exe / 102 B / 解析中」で増えた (後の一覧再確認で表示を確認)。API も upload-url=200 / POST /meetings (mime application/x-msdownload)=201 で拒否しない → 期待 (日本語エラーで拒否・一覧に増えない) 未達</t>
+          <t>[再測 R1] 期待: 日本語エラーで拒否・一覧に増えない / 実測: 画面文言=「Atelier API POST /meetings/upload-url -&gt; 422 | エラー | 解析に失敗したため、結果を表示できません。」 一覧 exe=false API upload-url=422 POST=422</t>
         </is>
       </c>
     </row>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>evidence/journeys-B-prod-20260903.txt</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J35-01-r1.png</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>POST /knowledge 201 → GET /knowledge (workspace) 一覧に出る=True。しかし埋め込みは生成されない: GET /embedding-status provider=none state=unavailable indexed/total=0/1 semantic_enabled=false (本番に埋め込みプロバイダが未設定 = G-11)。監査ログ knowledge.create は利用者向け API に露出せず未確認</t>
+          <t>[再測 R1] 期待: 一覧に出て埋め込みが生成される (embedding-status に反映)・監査 / 実測: POST=201 一覧 (API/画面)=true/true だが埋め込みは生成されない: GET /embedding-status provider=none state=unavailable semantic_enabled=false reason=「意味検索の部品 (fastembed) がこのサーバーに入っていません (キーワード一致のみ)」= 本番に埋め込みプロバイダ (fastembed) が依然未導入 (G-11、GAP-285 ①は経営判断のまま)。監査 knowledge.create は利用者向け API に出ず未観測</t>
         </is>
       </c>
     </row>
@@ -11677,12 +11677,12 @@
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>evidence/shots/journeys/J35-07.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J35-07-r1.png</t>
         </is>
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>状態カードに何で動くか/費用=表示あり (意味検索は使えません（キーワード一致のみ） / 費用なし /  / 意味検索の部品 (fastembed) がこのサーバーに入っていません (キーワード一致のみ) /  / 埋め込); 「再試行する」押下 → 処理中に遷移=true, 完了 (ready)=false: サーバーに fastembed が無く provider=none/unavailable のまま (G-11: 本番に意味検索の部品が未導入)。検索はキーワード一致で 0 件</t>
+          <t>[再測 R1] 期待: 何で動いていて誰の費用かが出て、準備を押すと処理中→完了後に検索で引ける / 実測: 状態カードに何で動くか・費用=true (「意味検索は使えません（キーワード一致のみ） / 費用なし / 意味検索の部品 (fastembed) がこのサーバーに入っていません (キーワード一致のみ) / 埋め込み済み 0 」)。「再試行する」押下 → POST /embedding-status/prepare は 503 で理由を返し (GAP-285 ②: 「準備を開始しました」と偽らない=true)、状態は provider=none state=unavailable のまま = 本番に埋め込みプロバイダ (fastembed) が未導入で処理中→完了に遷移しない (G-11、GAP-285 ①は経営判断のまま)</t>
         </is>
       </c>
     </row>
@@ -13306,19 +13306,19 @@
           <t>トークンがローテーションされ新リンクがメールで届く (実送信できない環境では送信ログ/キュー投入で代替)。旧リンクは無効になる</t>
         </is>
       </c>
-      <c r="K196" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K196" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+          <t>journeys-R1-prod-20260903.txt#J20-05</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>resend が 409: {"detail": "この招待はすでに使われたか、取り消されています。"}</t>
+          <t>[再測 R1] 使用済み (used_at 有) の招待で再送 200 → token がローテーション (旧≠新)。旧リンク preview 401 / signin 401 で無効、新リンク preview 200 / signin 200。メール送信の痕跡は利用者向け API に露出せず未観測 (受信箱なし)。付記 (G-12): 再送前に発行済みのクライアント券は GET /client/projects → 200</t>
         </is>
       </c>
     </row>
@@ -13696,19 +13696,19 @@
           <t>招待者に更新のメールが届く (実送信できない環境では送信ログ/キュー投入で代替)。監査ログ client_notified_of_update が記録される</t>
         </is>
       </c>
-      <c r="K202" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K202" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+          <t>journeys-R1-prod-20260903.txt#J21-05</t>
         </is>
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>期待: 成果物の新版で招待者に更新メール + 監査ログ client_notified_of_update / 実測: 新版 (要件定義 v3) 作成は 200 だが、更新通知メールを送る実装が API に存在しない (ResendSender の呼出箇所に成果物更新が無い)。観測できる送信痕跡も無し。T-F-17 未実装扱い</t>
+          <t>[再測 R1] 新版 (要件定義 v2) の作成は 200。送信の実装 (services/outputs/client_notify.py) は入ったが、監査ログ output.client_notified_of_update は target=workflow_output で書かれ、利用者が読める API (dashboard recent_activities は project/task/comment 対象のみ) に出ない。import 応答 (keys=file_name,type,title,stage,version,target_id,error) にも送信結果が無く、受信箱も無い / 解除条件: 運営の /admin/audit-logs で action=output.client_notified_of_update を照会するか、dashboard の監査に成果物対象を含める</t>
         </is>
       </c>
     </row>
@@ -14023,19 +14023,19 @@
           <t>コメントが自分の画面の一覧に出る。担当者に通知メールが届く (実送信できない環境では送信ログ/キュー投入で代替)。監査ログ comment_created が記録される</t>
         </is>
       </c>
-      <c r="K207" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K207" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+          <t>journeys-R1-prod-20260903.txt#J23-01</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>期待: 一覧に出る + 担当者に通知メール + 監査ログ comment_created / 実測: POST /client/projects/PE1/comments 201、自分の一覧に出る (is_client_author=true) は OK。しかし担当者への通知メールを送る実装が API に無い (services/client_signin・comments に Resend/notify 呼出なし, grep 0 件) → 送信痕跡も無し。監査ログは admin 専用で未確認</t>
+          <t>[再測 R1] POST /client/projects/{id}/comments 201 → 自分の一覧に出る (is_client_author=true)。担当者 (WS owner) への通知は監査ログ client.comment.staff_notified が owner のダッシュボード recent_activities に記録された (client.comment.staff_notified,client.comment.create) = 送信 (dry-run 含む) の痕跡。受信箱は無いので実受信は未確認</t>
         </is>
       </c>
     </row>
@@ -14162,12 +14162,12 @@
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J23-03-r1.png</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>期待: 自分のコメントは編集・削除できる / 実測: クライアント用の編集・削除 endpoint が無い (PATCH/DELETE /client/projects/{id}/comments/{id} → 404 Not Found、社内 PATCH/DELETE /comments/{id} は client 券で 401)。S-L03 にも編集/削除ボタン 0 個。他人 (社内メモ) の編集は 401 で拒否され content 不変 (こちらは OK)</t>
+          <t>[再測 R1] 期待: 自分のものは編集・削除が反映、他人のものは拒否 / 実測: API 直では PATCH/DELETE /client/projects/{pid}/comments/{cid} が 自分=200/204 (反映 true/true)・他人=404/404 (不変 true) で期待どおり (GAP-267 API 稼働、監査 client.comment.update/delete あり) だが、画面 S-L03 に「修正」0 個・「取り消す」0 個 = クライアントは画面から編集・削除できない ※本番 web バンドルが main に追随しておらず GAP-267 web 側が未反映</t>
         </is>
       </c>
     </row>
@@ -14557,12 +14557,12 @@
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J38-03.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-03-r1.png</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>期待: 30 日カウントダウンつきで一覧から消え (deleted_at 記録)、クライアント招待が無効化、監査 project_deleted / 実測: 設定の危険な操作から削除 (DELETE 204) でアクティブ一覧から消え include_deleted で deleted_at=2026-09-03T05:23:54Z。削除後の招待 token は POST /client/auth/preview 401 (削除前は 200) で無効化 (ただし GET 招待の revoked_at は null のまま = 暗黙無効)。不足: 削除後に「残り N 日」のカウントダウンや削除済み一覧が画面のどこにも無い (30 日の文言は削除前の確認ダイアログのみ)。監査 project.delete は削除後ダッシュボードが 404 で観測不可</t>
+          <t>[再測 R1] 期待: 30 日カウントダウンつきで一覧から消える (deleted_at)・クライアント招待無効化・監査 project_deleted / 実測: DELETE=204 アクティブ一覧から消えた=true deleted_at=2026-09-03T07:46:48.129161Z (API は記録)・招待 preview 200→401 / 発行済み券 GET 401 (無効化 OK) だが、画面に「削除済み」タブ/カウントダウンが無い (タブ=["すべて","進行中","アーカイブ"], 30 日の文言は削除前の確認「危険な操作 / プロジェクト削除は 30 日後にハード削除されます。30 日以内であればキャンセル可能。 / プロジェク」のみ) ※本番 web バンドルに GAP-277 の文字列が無い = Vercel デプロイが main に追随していない</t>
         </is>
       </c>
     </row>
@@ -14622,12 +14622,12 @@
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J38-04.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-04-r1.png</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>期待: 削除済み一覧から復元し、元の状態に戻り成果物・タスク・コメントが残る / 実測: 画面 (/projects) に削除済み一覧も復元ボタンも無く、利用者は画面から復元できない。API POST /projects/{id}/restore は 200 で deleted_at が消えて一覧に戻り、タスク「QA jA2 タスク Nebula-TASK-1」とコメントは残っている (データ面は正)</t>
+          <t>[再測 R1] 期待: 削除済み一覧から復元し元の状態に戻る / 実測: 画面に削除済み一覧・復元導線が無い (UI 復元=null)。API POST /projects/{id}/restore 200 で deleted_at が消え一覧に戻り、タスク 2 件・成果物 3 件・コメント 4 件は残る (データ面は正)。J38-03 の監査 project.delete が dashboard に出る=true ※本番 web バンドルに GAP-277 の文字列が無い = Vercel デプロイが main に追随していない</t>
         </is>
       </c>
     </row>
@@ -18804,19 +18804,19 @@
           <t>入れない状態で、理由が日本語で分かる。復元の導線だけが出る</t>
         </is>
       </c>
-      <c r="K280" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K280" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J52-03-r1.png</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>期待: 入れず理由が日本語で分かる・復元導線だけが出る / 実測: 退会後 signin は 401『メールアドレスまたはパスワードが違います。』(API/UI とも) で『退会中』という理由が分からない (パスワード誤りと区別不能)。復元リンクはサインイン画面に常時ある汎用リンクで、退会中に限って出るものではない。※存在秘匿の設計判断ならその旨を正本に明記して期待を改訂する</t>
+          <t>[再測 R1] 退会申込後に正しいパスワードで UI サインイン → API 403、画面に「このアカウントは退会手続き中です。サインイン画面の「退会済みアカウントの復元」から 30 日以内であれば復元できます。」と日本語で理由が出て入れない。復元の導線 ["退会済みアカウントの復元"] が出る。対照: 誤パスワードは従来どおり 401「メールアドレスまたはパスワードが違います。」(存在を漏らさない)</t>
         </is>
       </c>
     </row>
@@ -19073,12 +19073,12 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>evidence/shots/journeys/J30-15.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J30-15-r1.png</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>共有リンク発行 → 公開 GET /share/{token} (認証なし)=200 で最終版が見える (クライアント側 J21 の代替); 納品工程 confirm なし 403 / confirm あり 200 → flow delivery=done。しかし案件の状態は納品済みにならない: GET /projects/{id}.status=draft, 一覧 status=draft, dashboard status=draft current_phase=hearing; 画面 (一覧/ダッシュボード) に納品済み表記=false</t>
+          <t>[再測 R1] 期待: 納品工程 done・案件が納品済みとして一覧とダッシュボードに反映・クライアントに最終版 / 実測: delivery complete=200 flow delivery=done API current_phase=delivery/delivery/delivery status=draft (API は納品済み=true) / 画面: 一覧カード「のアクティブプロジェクト / 新規プロジェクト / プロジェクトを検索 / すべて / 進行中 / アーカイブ / クライアント案件 / 納品済 / QA jR」 ダッシュボード「プロジェクトダッシュボード / QA jR1 案件 Orion · クライアント案件 · 第 1 段階 ヒアリング中 / 全体進捗率 / 0% / 工程 0/9」 進捗「全体進捗率 / 0% / 工程 0/9 完了 / 未承認 INBOX 件数 / 0 / すべて処理済」 (画面は納品済み=false) / クライアント delivery=true ※本番 web バンドルが main に追随していない (GAP-279 の web 側「進捗カードも flow を優先」未反映の可能性)</t>
         </is>
       </c>
     </row>
@@ -19132,19 +19132,19 @@
           <t>owner 側のボードとダッシュボードに完了とコメントが反映される。監査ログ task_status_changed / comment_created が記録される</t>
         </is>
       </c>
-      <c r="K285" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K285" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>evidence/shots/journeys/J31-12.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J31-12-r1.png</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>タスク完了=200/done, コメント=201; owner ダッシュボード done=1 未解決コメント=2 (画面反映=true); 監査 recent_activities=["project.flow.thread","task.create","task.create","project.flow.complete"] → task 系=false, comment 系=false (comment_created 相当は project/task 対象の audit にしか出ないため未確認)</t>
+          <t>[再測 R1] メンバーがタスク A を done (PATCH 200) にしコメント (201) → owner のダッシュボード API で done 0→1・未解決コメント 3→4、画面のダッシュボードも「未解決コメント / 4 / 確定 0 · 未確認 0 件 / 工程の流れ」。監査 recent_activities に task.update / comment.create (メンバーの行為) が出る (comment.create,task.update,task.create)</t>
         </is>
       </c>
     </row>
@@ -19205,12 +19205,12 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/journeys-E-prod-20260903.txt</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J23-05-r1.png</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>返信は自分のコメントの下に表示 (OK)。しかし納品成果物は S-L03 に『納品書 2026/09/03 · v1 · HTML』の行として出るだけで、開く導線 (リンク/ボタン) が無く、client 用の content/content-url API も openapi に無い → 『納品された最終版の成果物が閲覧できる状態』を満たさない (行をクリックしても遷移・API 呼出なし)</t>
+          <t>[再測 R1] 期待: 返信が自分のコメントの下・納品最終版が閲覧できる / 実測: 返信の表示=false、納品成果物の行=true だが「開く」導線=0 個 (content-url 呼出 []) = 画面からは開けない。API 側は GET /client/projects/{pid}/outputs/{oid}/content-url → 200 で実体 200 本文に納品物あり (GAP-268 の API は稼働) ※本番 web バンドルが main に追随しておらず S-L03 の「開く」(GAP-268 web 側) が未反映</t>
         </is>
       </c>
     </row>
@@ -21404,11 +21404,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>39%</t>
         </is>
       </c>
     </row>
@@ -21419,11 +21419,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>11%</t>
         </is>
       </c>
     </row>
@@ -21434,11 +21434,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>50%</t>
         </is>
       </c>
     </row>

--- a/apps/web/.qa/e2e-journey/journey-20260903.xlsx
+++ b/apps/web/.qa/e2e-journey/journey-20260903.xlsx
@@ -2294,19 +2294,19 @@
           <t>日本語のエラーで拒否され、ワークスペースは増えない</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J10-07-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J10-07-r3.png</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 日本語エラーで拒否・WS 増えない / 実測: errors=[] POST=未送信 disabled=true WS 件数=0</t>
+          <t>[再測 R3] 名前を空のまま作成すると画面に日本語のエラー ["ワークスペース名を入力してください。"] が出て拒否される (GAP-263)。POST /workspaces は 送信されず、GET /workspaces も 0 件のままでワークスペースは増えない</t>
         </is>
       </c>
     </row>
@@ -3481,19 +3481,19 @@
           <t>初回だけ 3 ステップのウォークスルーが出る。完了すると次回から出ない状態が記録される</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J15-01-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-01-r3.png</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 初回だけ 3 ステップ・完了で次回から出ない / 実測: 登録後 url=/projects 表示=false steps=["最初のワークスペースを作成"] 完了=false ls={} 再表示=false</t>
+          <t>[再測 R3] 新規登録の直後に /t-uc-35 のウォークスルーが出て、3 ステップ ["ようこそ Atelier へ","ワークスペースを作成","プロジェクトを始める"] を「完了」まで進めると /projects へ戻る。完了状態が localStorage atelier_walkthrough_done=1 に記録され、以後 /t-uc-35 を直接開いても /t-uc-35 へ抜け、/projects を再読み込みしてもウォークスルーは出ない (GAP-262)</t>
         </is>
       </c>
     </row>
@@ -3546,19 +3546,19 @@
           <t>保存後にヘッダーの表示名に反映され、再読み込みしても残る。監査ログに記録される</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J15-03-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-03-r3.png</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 保存直後にヘッダー反映・再読み込みでも残る / 実測: PATCH=200 直後反映=false (ヘッダー「Q QA jR1 WS1 Q」) 再読み込み後=false ※本番 web バンドルに GAP-270 の文字列 (atelier:me-changed) が無い = Vercel デプロイが main に追随していない</t>
+          <t>[再測 R3] T-UC-37 で表示名を保存 (PATCH /me 200) → 再読み込みなしでヘッダーのアカウント表示が「アカウント: QA jR3 改名花子」に変わり (GAP-270 の atelier:me-changed でシェルが /me を読み直す)、メニューの氏名行も新名。再読み込み後も「アカウント: QA jR3 改名花子」・GET /me も同じ。監査ログは利用者向け API に露出せず未観測</t>
         </is>
       </c>
     </row>
@@ -3678,19 +3678,19 @@
           <t>選んだワークスペースが現在のワークスペースとして反映され、案件一覧がそのワークスペースのものに切り替わる。再読み込み後も残る</t>
         </is>
       </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J15-05-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J15-05-r3.png</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 選んだ WS が現在 WS になり案件一覧がその WS に切り替わる (再読み込み後も) / 実測: 現在 WS=WS2 だが一覧は GET ["/projects?limit=20"] で Vega=true Orion=true Sirius=true (WS1 の案件が混在)、現在案件の解除=false (header「Q QA jR1 WS2 / プロジェクト Q」) / 再読み込み後 Vega=true Orion=true Sirius=true ※本番 web バンドルに GAP-271/277 の文字列 (削除済みのプロジェクトはありません / アクティブに戻す) が無い = Vercel デプロイが main (a34f488) に追随していない</t>
+          <t>[再測 R3] t-uc-38 の切替で WS2 を選ぶと現在 WS が WS2 になり (ヘッダーも WS2)、/projects は GET /projects?limit=20&amp;include_deleted=true&amp;workspace_id=a6e16ef で WS2 の Vega だけ (WS1 の Orion / Sirius は出ない = GAP-271)。現在案件も旧 WS の Orion から解除。再読み込み後も WS2・Vega のまま</t>
         </is>
       </c>
     </row>
@@ -4005,19 +4005,19 @@
           <t>各カードが実データと一致して反映される。承認待ちの件数は GET /approval-inbox の件数と同じ</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J30-05-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J30-05-r3.png</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 各カードが実データと一致 / 実測: 工程進捗 1/10 表示=false (画面: 全体進捗率 / 0% / 工程 0/9 完了 / 未承認 INBOX 件数 / 0 / すべて処理済), inbox 一致=true, コメント一致=true, 最新成果物一致=true</t>
+          <t>[再測 R3] S-B02: 工程進捗「工程 1/10」(flow の done 数と一致・GAP-279)、承認待ち 0 (GET /approval-inbox と一致)、未解決コメント 3 (unresolved-count と一致)、最新成果物「要件定義書 QA-R3」が実データと一致。project.current_phase=hearing</t>
         </is>
       </c>
     </row>
@@ -4333,19 +4333,19 @@
           <t>未完了工程・タスク・未解決コメントの実数が出る。0 でない間は確定できない状態である</t>
         </is>
       </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J30-10-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J30-10-r3.png</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 実数が出て 0 でない間は確定できない / 実測: 実数表示=true (UI ["・未完了の工程が 9 つあります（提案、見積、契約）","・完了していないタスクが 2 件あります","・未解決のコメントが 3 件あります"] vs API 9/2/3) 確定ボタン enabled=true API freeze=409</t>
+          <t>[再測 R3] 確定前チェックに未完了工程 9 / タスク 2 / 未解決コメント 3 の実数 (API freeze-check と一致) が出て、確定ボタンは無効 (残件を承知するチェックまで押せない・GAP-280)。API も残件ありの confirm=true は 409「残っている作業があるため確定できません（未完了の工程が 9 つあります（提案、見積、契約） / 完了していないタスクが 2 件あります / 」で確定できない (フェーズは active のまま)</t>
         </is>
       </c>
     </row>
@@ -5056,19 +5056,19 @@
           <t>サイドバーのワークスペース名に反映され、監査ログ workspace_updated が記録される</t>
         </is>
       </c>
-      <c r="K70" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J36-01-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-01-r3.png</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: サイドバーに即反映 / 実測: PATCH=200 直後反映=false header「Q QA jR1 WS1 / WS設定 Q」 GET name=QA jR1 WS1 改名</t>
+          <t>[再測 R3] PATCH /workspaces 200 → 保存直後 (再読み込みなし) にサイドバー/ヘッダーが「QA jR3 WS1 改名」に変わり (GAP-270)、GET も新名。監査ログ workspace.update は WS 対象で利用者向け API (dashboard) に出ず未観測</t>
         </is>
       </c>
     </row>
@@ -5385,19 +5385,19 @@
           <t>30 日保持の案内が出て一覧から消える。DB に deleted_at が記録され、そのワークスペースのデータへのアクセスは拒否される。監査ログ workspace_deleted が記録される</t>
         </is>
       </c>
-      <c r="K75" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J36-07-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J36-07-r3.png</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 30 日案内・一覧から消える・deleted_at・配下アクセス拒否・監査 / 実測: DELETE=["204 /workspaces/efb95e0c-7021-4509-9121-cca776c5b4d6"] 30日案内=true 一覧残存=false GET ws=404 配下 projects=200/1 詳細=200 employees=200/10 /projects に Vega=true/true</t>
+          <t>[再測 R3] WS 設定の退会タブに「ワークスペースの削除 / Danger Zone / ワークスペース削除は 30 日後にハード削除されます。30 日以内であればキャンセル可能。 / ワークスペースを削除 / アカ」と 30 日保持の案内が出た上で削除 (DELETE 204) → GET /workspaces から消え、GET /workspaces/{id} は 404。配下へのアクセスも拒否され (GET /projects?workspace_id → 200 0 件 / GET /projects/{Vega} → 404 / GET /ai-employees?workspace_id → 200 0 名)、/projects?limit=20 にも画面の一覧にも Vega は出ない = GAP-273 の RLS helper が migration 改名 (t-d-99zt) で本番に効いている (R1 では配下が 200 で読めていた)。deleted_at は 削除後は 404 で API から直接読めない (削除の事実は 404 と配下拒否で確認)。監査 workspace.delete は WS 対象で利用者向け API に出ず未観測</t>
         </is>
       </c>
     </row>
@@ -5523,12 +5523,12 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J37-02-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J37-02-r3.png</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 名前・口調・できることが出てスキル名/本文は画面にも API にも無い / 実測: 名前=true 口調=true できること=true 画面スキル語=["sales-email","proposal","estimate"] GET /skills=1 API漏れ=false templates system_prompt=null default_skills=0</t>
+          <t>[再測 R3] 期待: 名前・口調・できること が出て、スキル名や本文は画面と API 応答のどちらにも含まれない / 実測: 画面は改善 (名前=true 口調=true できること=true、チップは説明文「成 / 提案書作成 / 見積作成 / 担当範囲 / 役職 / 部長 / 所属 / 営業・契約部 / レポート対象 / ジャービス / 直属の部下 / メンバー 」でスキル名の露出=0 個・GAP-274 の web 側は反映済) だが、**この画面は今も GET /skills を 1 回呼び、その応答 (200, 23 件, keys=id,name,version,description,is_active) に内部スキル名が入っている** (この社員の attached_skills 3 件 = ["sales-email","proposal","estimate"])。= API 応答にスキル名が含まれる状態のまま (R-T06)。templates 側は system_prompt=null / default_skills=0 で秘匿済み</t>
         </is>
       </c>
     </row>
@@ -5713,19 +5713,19 @@
           <t>署名付き URL でアップロードした画像が組織図とチャットに反映される。Storage に実体が存在する (G-11)</t>
         </is>
       </c>
-      <c r="K80" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K80" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J37-05-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J37-05-r3.png</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 画像が組織図とチャットに反映・Storage に実体 / 実測: upload-url=200 → PUT=200 → PATCH icon=200 → icon-url=200 実体 fetch=200 image/png 70B (Storage に実体あり = G-11 OK) だが、組織図 img=0 (ノード &lt;span aria-label="AI 社員 Tony" role="img" class="inline-flex shrink-0 items-cente, icon-url 呼出 []) チャット img=0 (icon-url 呼出 []) = 画面に画像が反映されない ※本番 web バンドルに GAP-276 の文字列 (ai-employee-icon-url) が無い = Vercel デプロイが main に追随していない</t>
+          <t>[再測 R3] (ui2 の FAIL 行を上書き) 署名 URL 発行 200 → PUT 200 → PATCH icon 200 → GET icon-url 200 → 実体 200 image/png 70B (Storage に実在 = G-11 OK)。組織図 (S-C01) は署名 URL の img 1 枚で画像に差し替わる (icon-url 呼出 200 = GAP-276 の web 側は本番に反映済)。チャット (S-E01) も icon-url を 200 で引き iconSrc を ChatPanel へ渡しているが、**アップロード画像が描画されるのは assistant ロールのメッセージ行だけ**で、AI 応答が 1 件も無いスレッドでは img が 0 のまま = 画面上で確認できない。GET /bridge/status は running/queued 0・active_worker_pids [] で AI を動かせない / 解除条件: Bridge (場所=mac) で AI 応答を 1 件出したスレッドを開き、その行のアイコンが画像かを見る</t>
         </is>
       </c>
     </row>
@@ -6041,19 +6041,19 @@
           <t>アクティブ一覧から消えアーカイブ一覧に出る。戻すとアクティブ一覧に反映される</t>
         </is>
       </c>
-      <c r="K85" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J38-06-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-06-r3.png</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 一覧からアーカイブ→アクティブ一覧から消えアーカイブ一覧に出る→戻すと復帰 / 実測: アーカイブ導線=0 すべてに残存=true アーカイブ表示=false 戻す導線=0 復帰=true タブ=["すべて","進行中","アーカイブ","クライアント案件\nヒアリング中\nQA jR1 案件 Sirius (アーカイブ用)\n\n—\n\n工程 1 / 9\n8 分前更新"] ※本番 web バンドルに GAP-277 の文字列 (アクティブに戻す) が無い = Vercel デプロイが main に追随していない</t>
+          <t>[再測 R3] 一覧カードの「アーカイブ」(PATCH 200) で Sirius がアクティブ (すべて) から消え「アーカイブ」タブに出る。「アクティブに戻す」(PATCH 200) で「すべて」に復帰 (API status=in_progress) — GAP-277 の web 側が反映済</t>
         </is>
       </c>
     </row>
@@ -6765,12 +6765,12 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J31-07-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J31-07-r3.png</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 追加・reveal とも 403 で値は漏れない・監査に拒否 / 実測: 追加は 403「シークレットを追加する権限がありません。」(GAP-278 ② OK) だが **reveal は 403 でなく 200 で平文を返す** (role=viewer の閲覧者が本人パスワードで再認証すると owner が登録したシークレット値がそのまま取れる = 値が漏れる。R-T06 級の権限漏れ)。画面 (S-B04) にも閲覧者に「表示」ボタンが出る。監査の拒否記録は利用者向け API に出ず未観測。再現: viewer の JWT で POST /projects/{pid}/credentials/{cid}/reveal {"password":"&lt;redacted&gt;"} → 200 {"value":"&lt;redacted&gt;"}</t>
+          <t>[再測 R3] (ui3 の行を詳細化) 期待: 追加と表示のどちらも 403 で拒否され値は漏れない・監査に拒否が記録される。実測: **API は両方 403 に直った** — 閲覧者 (role=viewer) の POST /projects/{p}/credentials → 403「シークレットを追加する権限がありません。」、POST /projects/{p}/credentials/{c}/reveal は本人パスワードつきでも無しでも 403「シークレットの値を表示する権限がありません。」で平文は返らない (GAP-313 修正が本番で効いている。R1 では 200 で平文が返っていた)。一覧 GET は 200 でマスク (last4 のみ)、owner 側の一覧も 1 件のままで閲覧者の追加は入らない。**しかし画面 S-B04 は閲覧者にも「表示」ボタン 1 個と追加フォーム (#cred-name / #cred-kind / #cred-value / 「暗号化して保存」) と「QA jR3 顧客 API キー を削除」を出したまま** = 押せば 403 になるだけの操作を見せている (GAP-313 の「画面側の『表示』非表示」は未実装。app/projects/s_b04/_components/CredentialList.tsx / CredentialForm.tsx にロール判定が無い)。監査ログの拒否記録は credential 対象で利用者向け API に出ず未観測。再現: viewer の JWT で /projects/vault?project={pid} を開く → 「表示」ボタンと追加フォームが出る</t>
         </is>
       </c>
     </row>
@@ -11146,19 +11146,19 @@
           <t>日本語のエラーで拒否され、一覧に増えない</t>
         </is>
       </c>
-      <c r="K163" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J34-06-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J34-06-r3.png</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 日本語エラーで拒否・一覧に増えない / 実測: 画面文言=「Atelier API POST /meetings/upload-url -&gt; 422 | エラー | 解析に失敗したため、結果を表示できません。」 一覧 exe=false API upload-url=422 POST=422</t>
+          <t>[再測 R3] .exe を選んで送ると画面に「対応していない形式です (.exe)。音声・動画・テキスト (.txt / .md)・Word (.docx) のみ登録できます。 | エラー | 解析に失敗したため、結果を表示できません。」と日本語だけで拒否され (GAP-314: 内部の英語メソッド/パス/status は出ない)、一覧に増えない (0 件のまま)。API 直でも upload-url / POST /meetings とも 422「対応していない形式です (.exe)。音声・動画・テキスト (.txt / .md)・Word (.docx) のみ登録」</t>
         </is>
       </c>
     </row>
@@ -14155,19 +14155,19 @@
           <t>自分のものは編集・削除が反映される。他人のものは拒否される</t>
         </is>
       </c>
-      <c r="K209" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K209" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J23-03-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J23-03-r3.png</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 自分のものは編集・削除が反映、他人のものは拒否 / 実測: API 直では PATCH/DELETE /client/projects/{pid}/comments/{cid} が 自分=200/204 (反映 true/true)・他人=404/404 (不変 true) で期待どおり (GAP-267 API 稼働、監査 client.comment.update/delete あり) だが、画面 S-L03 に「修正」0 個・「取り消す」0 個 = クライアントは画面から編集・削除できない ※本番 web バンドルが main に追随しておらず GAP-267 web 側が未反映</t>
+          <t>[再測 R3] S-L03 の自分のコメントに「修正」2 個・「取り消す」2 個が出る (GAP-267 の web 側が本番に反映済)。画面から修正 → PATCH 200 で表示も API 再取得も修正後の本文に、画面から取り消す → DELETE 204 で画面と API 一覧から消える。社内 (他人) の返信には操作導線が出ず、API 直でも PATCH 404 / DELETE 404 で拒否され本文は不変。監査 client.comment.delete,client.comment.update</t>
         </is>
       </c>
     </row>
@@ -14550,19 +14550,19 @@
           <t>30 日カウントダウンつきで一覧から消える (deleted_at が記録)。その案件のクライアント招待は無効化され、監査ログ project_deleted が記録される</t>
         </is>
       </c>
-      <c r="K215" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K215" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J38-03-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-03-r3.png</t>
         </is>
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 30 日カウントダウンつきで一覧から消える (deleted_at)・クライアント招待無効化・監査 project_deleted / 実測: DELETE=204 アクティブ一覧から消えた=true deleted_at=2026-09-03T07:46:48.129161Z (API は記録)・招待 preview 200→401 / 発行済み券 GET 401 (無効化 OK) だが、画面に「削除済み」タブ/カウントダウンが無い (タブ=["すべて","進行中","アーカイブ"], 30 日の文言は削除前の確認「危険な操作 / プロジェクト削除は 30 日後にハード削除されます。30 日以内であればキャンセル可能。 / プロジェク」のみ) ※本番 web バンドルに GAP-277 の文字列が無い = Vercel デプロイが main に追随していない</t>
+          <t>[再測 R3] 案件設定の危険な操作 (「プロジェクト削除は 30 日後にハード削除されます。30 日以内であればキャンセル可能。」) から削除 (DELETE 204) → アクティブ一覧から消え「削除済み」タブに「30 日後に完全に削除 / 復元する（残り 30 日）」のカウントダウンつきで出る (GAP-277 の web 側が本番に反映済)。API も deleted_at=2026-09-03T10:46:34Z を記録し GET 詳細は 404。クライアント招待は preview 200→401・発行済みの券で GET /client/projects 401 で無効化。監査 project.delete は復元後 (J38-04) のダッシュボード活動に出る。※付記 (G-14 / 正本に無い観点・別途 QA 用アカウントで再現済): **案件を削除しても、その成果物に発行済みの公開共有リンク (GET /share/{token}) は失効しない** — 案件 DELETE 204 の直後も、さらに WS を DELETE 204 した後も公開 GET は 200 で納品物の本文を返し続けた (410 になるのは所有者が退会したときだけ)。services/outputs/sharing.resolve_share_token が output.deleted_at しか見ておらず、project / workspace の削除を見ていない</t>
         </is>
       </c>
     </row>
@@ -14615,19 +14615,19 @@
           <t>元の状態に戻り、成果物・タスク・コメントが残っている</t>
         </is>
       </c>
-      <c r="K216" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K216" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J38-04-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J38-04-r3.png</t>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 削除済み一覧から復元し元の状態に戻る / 実測: 画面に削除済み一覧・復元導線が無い (UI 復元=null)。API POST /projects/{id}/restore 200 で deleted_at が消え一覧に戻り、タスク 2 件・成果物 3 件・コメント 4 件は残る (データ面は正)。J38-03 の監査 project.delete が dashboard に出る=true ※本番 web バンドルに GAP-277 の文字列が無い = Vercel デプロイが main に追随していない</t>
+          <t>[再測 R3] 「削除済み」タブの「QA jR3 案件 Orion を復元する（残り 30 日）」で復元 (POST /projects/{id}/restore 200) → アクティブ一覧に戻り (deleted_at=null, current_phase=delivery)、タスク 2 件・成果物 2 件・コメント 3 件がそのまま残っている。J38-03 の監査 project.delete もダッシュボードの活動に出る=true</t>
         </is>
       </c>
     </row>
@@ -19066,19 +19066,19 @@
           <t>納品工程が done に遷移し、案件の状態が納品済みとして一覧とダッシュボードに反映される。クライアント側 (J21) に最終版の成果物が見える</t>
         </is>
       </c>
-      <c r="K284" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K284" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J30-15-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J30-15-r3.png</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 納品工程 done・案件が納品済みとして一覧とダッシュボードに反映・クライアントに最終版 / 実測: delivery complete=200 flow delivery=done API current_phase=delivery/delivery/delivery status=draft (API は納品済み=true) / 画面: 一覧カード「のアクティブプロジェクト / 新規プロジェクト / プロジェクトを検索 / すべて / 進行中 / アーカイブ / クライアント案件 / 納品済 / QA jR」 ダッシュボード「プロジェクトダッシュボード / QA jR1 案件 Orion · クライアント案件 · 第 1 段階 ヒアリング中 / 全体進捗率 / 0% / 工程 0/9」 進捗「全体進捗率 / 0% / 工程 0/9 完了 / 未承認 INBOX 件数 / 0 / すべて処理済」 (画面は納品済み=false) / クライアント delivery=true ※本番 web バンドルが main に追随していない (GAP-279 の web 側「進捗カードも flow を優先」未反映の可能性)</t>
+          <t>[再測 R3] (ui3 / ui3b の FAIL 行を上書き) 納品成果物の共有リンクを発行済み (計 2 件・認証なしの公開 GET 200 text/html; charset=utf-8・本文に納品物=true) を確認し、納品工程を確認つきで完了 (confirm なし 403「重要な確認が必要です」/ confirm あり 200) → flow delivery=done。current_phase=delivery が API 詳細・一覧・ダッシュボードで一致 (GAP-279)。画面も 一覧カードに「納品済」バッジ、ダッシュボード「第 10 段階 納品・請求中 / 全体進捗率 100% / 工程 10/10 完了」で納品済みとして反映。クライアント (J21/J23) 側 outputs に delivery v1 が見える。※付記: 一覧カードの工程表記は「工程 9 / 9」でダッシュボードの「工程 10/10」と分母が食い違う (画面間の不一致・正本に無い観点)</t>
         </is>
       </c>
     </row>
@@ -19205,12 +19205,12 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J23-05-r1.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J23-05-r3.png</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>[再測 R1] 期待: 返信が自分のコメントの下・納品最終版が閲覧できる / 実測: 返信の表示=false、納品成果物の行=true だが「開く」導線=0 個 (content-url 呼出 []) = 画面からは開けない。API 側は GET /client/projects/{pid}/outputs/{oid}/content-url → 200 で実体 200 本文に納品物あり (GAP-268 の API は稼働) ※本番 web バンドルが main に追随しておらず S-L03 の「開く」(GAP-268 web 側) が未反映</t>
+          <t>[再測 R3] (ui4 の行を上書き・より正確に) 期待: 社内の返信が自分のコメントの下に出ている / 納品された最終版の成果物が閲覧できる。実測: **納品成果物は閲覧できる** — S-L03 に「要件定義書 を HTML で開く」「納品書 を HTML で開く」があり、押すと GET /client/projects/{pid}/outputs/{oid}/content-url 200 → 別タブで納品物の本文が開く (GAP-268 の web 側が本番に反映済)。**返信の位置は期待と逆** — 社内の返信「【社内 R3 返信】…」が自分のコメントの **上** に出る (画面の並び ["運営 · QA jR3 改名花子 / 2026/09/03 / 要件","QA クライアント R3 / 2026/09/03 / 要件定義書 "])。原因は API 側 services/client_signin/content.py の list_comments が "order by c.created_at desc" の平坦な一覧を返し、parent_comment_id を返さず画面もスレッド化しないため、返信が「自分のコメントの下」に置かれない。再現: クライアントがコメント → 社内が parent_comment_id つきで返信 → ポータル /portal を開く</t>
         </is>
       </c>
     </row>
@@ -21404,11 +21404,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>43%</t>
         </is>
       </c>
     </row>
@@ -21419,11 +21419,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>7%</t>
         </is>
       </c>
     </row>
@@ -21434,7 +21434,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/apps/web/.qa/e2e-journey/journey-20260903.xlsx
+++ b/apps/web/.qa/e2e-journey/journey-20260903.xlsx
@@ -8329,19 +8329,19 @@
           <t>選んだ分だけ着手可に遷移し、選んでいないものは変わらない</t>
         </is>
       </c>
-      <c r="K120" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J48-21-r2.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J48-21-r4.png</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>[再測 R2] 期待: 2 件選んで一括操作で選んだ分だけ着手可 / 実測: S-I01 の選択チェックボックスは着手可のカードにしか無く (準備中カード G/H/I には 0 個、check は 2 件とも不可)、選択バーも出ず、選択バー系の一括「着手可にする」ボタンは無い (画面にあるのはカード単体の「…を着手可にする」6 個 = 1 枚ずつ押すしかない。再実行のハーネスが自分のタイトルの「一括」を含むカード単体ボタンを誤って 1 回押した = E を単体で ready にしただけ)。API POST /tasks/bulk/lifecycle (task_ids 2 件, ready) → 200 {"data":{"requested":2,"updated":2,"updated_task_ids":["ee4b6d8a-bd4e-4101-baab-a577413ad382","52a8deff-721b-4cd5-91dd-1 で G/H=ready・選ばなかった I=triage (不変)、画面の列 {"G":"着手可","H":"着手可","I":"準備中"}、監査 task.bulk_lifecycle ["task.bulk_lifecycle:task:52a8deff","task.bulk_lifecycle:task:ee4b6d8a"] — データ層は正しいが画面から一括着手可はできない (GAP-304 未着手・通し D と同じ)</t>
+          <t>[再測 R4] 準備中カード 3 件のうち 2 件 (G/H) を画面のチェックボックスで選択 → 選択バー「準備中のタスク 2 件を選択中」の「着手可にする2」を押す → POST 200 /tasks/bulk/lifecycle。選んだ G/H だけ ready、選ばなかった I は triage のまま。画面の列 {"G":"着手可","H":"着手可","I":"準備中"}、監査 ["task.bulk_lifecycle:task:e96f3e75","task.bulk_lifecycle:task:e84b7af3"] (GAP-304 解消)</t>
         </is>
       </c>
     </row>
@@ -8591,19 +8591,19 @@
           <t>工程ごとの成果物が一覧に出て、三層がそれぞれ表示された状態になる</t>
         </is>
       </c>
-      <c r="K124" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>BLOCKED</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J46-01-r2.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-01-r4.png</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>[再測 R2] 期待: 工程ごとの成果物が一覧に出て三層 (HTML/JSON/MD) が表示される / 実測: GET /outputs 5 件 (estimate/requirements/verification/hearing)。S-G01 (?output 無し) は「成果物を選択すると表示します」で成果物を選ぶ一覧=0 個。S-F01 工程ごとの成果物欄=["ヒアリング:0件","要件定義:0件","アーキ設計:0件","デザイン:0件","機能分解:0件"] (工程で分かれる=false)。ビューアの表示形式タブ=["HTML"]、HTML 層は iframe 内本文「1. 目的  QA-R2 案件の要件定義書 v1。Nebul」(Mixed Content 0 件)、alert=["この成果物は表形式ではありません。HTML の成果物は本文プレビューで開けます。"]。JSON/MD タブは import 成果物では未生成 (0 個)</t>
+          <t>[再測 R4] 一覧は満たす (GAP-302 解消): S-G01 に「成果物を選ぶ」一覧が 4 行 (stage 毎の最新版 = 見積書v2 / ヒアリングサマリーv1 / 要件定義書v1 / 検証レポートv1) 出て、3 行目を開くと /outputs?output=a7b2adb5-2437-4f33-9a97-f1a456da494e で要件定義書が表示される。S-F01 は工程ごとに中身が変わる: ヒアリング=成果物1(hearing) / 要件定義=成果物1(requirements) / アーキ設計=成果物0 / デザイン=成果物0 / 検証=成果物1(verification) / 納品=成果物0。三層は判定不能 / 理由: 場所=mac — JSON 層 (json_path) と MD 層 (md_path) は AI 実行 (Bridge) が生成するもので、この環境で作れる成果物 (POST /projects/{id}/import) は html_path のみ (対象成果物 json_path=null md_path=null)。そのため S-G01 の表示形式タブは ["HTML"] の 1 層だけ、S-F01 の HTML/JSON/MD も JSON・MD が disabled。解除条件: Mac の Bridge で AI に成果物を生成させ json_path / md_path を持つ成果物で開く</t>
         </is>
       </c>
     </row>
@@ -9518,12 +9518,12 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J46-16-r2.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-16-r4.png</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>[再測 R2] 画面の「HTML で保存」「Excel で保存」= HTML で保存: HTTP 404 (Authorization 無し) → 遷移先 /outputs/177da0f1-d3ed-4e95-ba54-bd48b80c7b67/export?format=html 「メインコンテンツへスキップ ワークスペース · QA-R2 WS 2026090」 / Excel で保存: HTTP 404 (Authorization 無し) → 遷移先 /outputs/177da0f1-d3ed-4e95-ba54-bd48b80c7b67/export?format=xlsx 「メインコンテンツへスキップ ワークスペース · QA-R2 WS 2026090」。API (Bearer) は html 200 / xlsx 200 (4987 bytes) で得られる。監査 output_downloaded は dashboard に増えず (["task.create:task:9da8b7d4","task.create:task:22fa0df7"]) 観測できない</t>
+          <t>[再測 R4] 期待: ファイルが得られ、監査ログ output_downloaded が記録される / 実測 (ファイル): 画面の「HTML で保存」「Excel で保存」は認証付き fetch (GAP-300) になったが、叩き先が ["WEB オリジン/outputs/a7b2adb5-2437-4f33-9a97-f1a456da494e/export?format=html","WEB オリジン/outputs/a7b2adb5-2437-4f33-9a97-f1a456da494e/export?format=xlsx"] = **API ではなく web オリジン** で 404 (text/html の Next.js 404 ページ) を返し、ダウンロードは発生せず alert「書き出しに失敗しました。時間をおいてもう一度お試しください。」。原因: ShareExportPanel.tsx の apiBase が `process.env.NEXT_PUBLIC_API_URL ?? ""` で、他の全 API 呼び出しが使う lib/auth/connector.ts の API_BASE (未設定なら本番は https://atelier-api-eb.fly.dev) の本番フォールバックを持たないため、Vercel で NEXT_PUBLIC_API_URL 未設定だと相対 URL になる。対照: 同じ成果物に API を Bearer で直接叩くと html 200 544 bytes / xlsx 200 4988 bytes で得られる (API 側は正常)。実測 (監査): dashboard の増分=[] で output_downloaded は記録されず、API 実装 (routes/outputs/__init__.py export_output) にも監査書き込みが無い = 未実装</t>
         </is>
       </c>
     </row>
@@ -9649,12 +9649,12 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J46-18-r2.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-18-r4.png</t>
         </is>
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>[再測 R2] 期待: 403 で拒否され成果物は変わらない・閲覧とコメントはできる / 実測: PATCH role=viewer 200。viewer の GET /outputs/{id} 200 (閲覧可)、POST /comments 201 (コメント可) は期待通り。編集系 (各 3 回): POST /sheet [403,403,403]「この操作を行う権限がありません。」(GAP-282 の 500→403 は解消)、POST /share-links [403,403,403]「共有リンクを発行する権限がありません。」(GAP-307 解消)、POST /restore は最新版に対しては [409,409,409]「この版は復元できません」(前提チェックが権限より先) — v2 を import で積んで旧版 v1 に対して試すと [403,403,403] (権限判定は正しい)。POST /revise は [503,503,503]「お使いの PC の Bridge がオフラインです」(Bridge 判定が権限判定より先で、閲覧者にも 403 ではなく 503 が返る = 期待の 403 に不一致)。版数 xlsx 2→2・要件定義 2→3 (増分は対照の owner restore のみ、viewer の操作では不変)。画面: 閲覧者にも「編集 / 新しい版として保存 / AI に修正を依頼 / 共有リンクを発行 / HTML で保存 / Excel で保存 / 投稿」が表示され、「保存」を押すと POST /sheet 403 → alert「保存に失敗しました。」(理由が権限だと分からない)</t>
+          <t>[再測 R4] 期待: 403 で拒否され成果物は変わらない・閲覧とコメントはできる / 実測: PATCH role=viewer 後、viewer の GET /outputs {req,xlsx}=[200,200] (閲覧可)・POST /comments 201・GET /comments 200 (コメント可)。編集系 (各 3 回): sheet [403,403,403] / restore 旧版 v1 [403,403,403] / restore 最新版 v2 [403,403,403] / share-links [403,403,403] / revise [403,403,403] = すべて 403 で、R2 で権限より先に出ていた 503 (revise) と 409 (restore 最新版) は解消 (GAP-311 確認)。画面の「保存」も POST /sheet 403 {detail: この操作を行う権限がありません。} → 画面に「権限がありません。」のトーストが出る (失敗理由が権限だと分かる)。版数 xlsx 1→1・要件定義 2→2 (成果物は不変)、viewer が発行した共有リンク 0 件。**残る不一致 (新規)**: POST /outputs/{id}/ai-file-edit だけ [503,503,503]「お使いの PC の Bridge がオフラインです」で、Bridge 判定が権限判定より先に出る (apps/api/src/routes/outputs/__init__.py の request_output_file_edit に _can_write_output の判定が無い。restore/revise/share-links は line 454/530/683 で判定済み)。閲覧者の画面にも「AI に修正を依頼」ボタンが出ているので実際に踏める経路。GAP-311 と同じ壊れ方が同じ画面の別ボタンに残っている = この 1 点だけで FAIL。併記: 閲覧者の画面に編集系ボタン (編集 / 新しい版として保存 / AI に修正を依頼 / 共有リンクを発行 / 投稿) が出たままなのは GAP-311 が「別途」とした既知事項</t>
         </is>
       </c>
     </row>
@@ -9707,19 +9707,19 @@
           <t>0 件の案内が出る状態になり、エラーにならない</t>
         </is>
       </c>
-      <c r="K141" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J46-19-r2.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J46-19-r4.png</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>[再測 R2] 期待: 0 件の案内が出てエラーにならない / 実測: GET /outputs=0 件。S-G01 は「成果物を選択すると表示します」(0 件の案内=false)、alert 0 件、API 5xx=0 件、工程画面の成果物欄=「成果物 0 件)」</t>
+          <t>[再測 R4] 成果物 0 件の案件で S-G01 を開くと「この案件にはまだ成果物がありません。工程を進めるかチャットで作成すると、ここに並びます。」と 0 件の案内が出る (GAP-302)。alert 0 件・JS エラー 0 件・API 4xx/5xx 0 件、S-F01 の成果物欄も「成果物 0 件)」でエラーにならない</t>
         </is>
       </c>
     </row>
@@ -12390,19 +12390,19 @@
           <t>日本語のエラーで拒否され、送信履歴に増えない</t>
         </is>
       </c>
-      <c r="K182" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J47-06-r2.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-06-r4.png</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>[再測 R2] UI: 宛先 'not-an-email' → POST 未送信、アプリのエラー文言=[] (ブラウザ標準の検証のみ: validationMessage「Please include an '@' in the email address. 'not-an-email' is missing an '@'.」= ブラウザ UI 言語依存) / 'foo@' → POST 未送信、アプリのエラー文言=[] (ブラウザ標準の検証のみ: validationMessage「Please enter a part following '@'. 'foo@' is incomplete.」= ブラウザ UI 言語依存); API: 'not-an-email' → 422 "送信内容を確認してください（入力内容: 形式が正しくありません）。"、'foo@' → 422; 送信履歴 1→1 (増えない)</t>
+          <t>[再測 R4] UI: 宛先 'not-an-email' → POST 未送信、アプリのエラー文言=["宛先メールアドレスの形式が正しくありません（例: client@example.com）。"] / 'foo@' → POST 未送信、アプリのエラー文言=["宛先メールアドレスの形式が正しくありません（例: client@example.com）。"]; API: 'not-an-email' → 422 "送信内容を確認してください（入力内容: 形式が正しくありません）。"、'foo@' → 422; 送信履歴 1→1 (増えない)</t>
         </is>
       </c>
     </row>
@@ -12455,19 +12455,19 @@
           <t>一覧から消え、論理削除が記録される。送信履歴は残る</t>
         </is>
       </c>
-      <c r="K183" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J47-07-r2.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J47-07-r4.png</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>[再測 R2] UI「v2 を削除」→ 確認 → DELETE /sales-docs/{id} 204、一覧 2→1 件・画面から消える、GET detail 404。送信履歴: 削除前 1 件 → 削除後 GET /sales-docs/{id}/sends 404 (ドラフトが不可視になると送信履歴も API/画面から辿れない)。論理削除の監査は運営 API のみで観測不能 (dashboard 増分=["task.update:task:7e00a0ab"])</t>
+          <t>[再測 R4] UI「v2 を削除」→ 確認 → DELETE /sales-docs/{id} 204、一覧 2→1 件・画面から「見積書 Nebula」が消える、GET detail 404。送信履歴: 削除前 1 件 → 削除後も GET /sales-docs/{id}/sends 200 で同じ 1 件が読める (GAP-306 解消。R2 は 404 だった)。論理削除: 削除後に同じ案件・同じ doc_type で新しいドラフトを作ると version=3 が採番される (next_version は deleted_at で絞らない max(version)+1) = 削除した v2 の行が DB に残っている (物理削除ではない)。実装も delete_sales_doc が 'set deleted_at = now()' + AuditWriter(action=sales_doc.delete)。監査行そのものは target_type=workflow_output で、GET /projects/{id}/dashboard の recent_activities (project/task/comment のみ) に出ないため運営 API 無しでは読めない (dashboard 増分=[])</t>
         </is>
       </c>
     </row>
@@ -12520,19 +12520,19 @@
           <t>実行できる種類とコストが一覧に出て、画面表示が GET /cron-actions と一致した状態である</t>
         </is>
       </c>
-      <c r="K184" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J44-01-r2.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J44-01-r4.png</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>[再測 R2] 期待: 画面表示が GET /cron-actions と一致 / 実測: 6 種中 欠け 6 ["task_replay","knowledge_organize","industry_extract","report_summary","daily_digest","weekly_burndown"]、旧文言残存 ["着手可のタスクを再生する","ナレッジを整理する","横断パターンを抽出する","プラン枠","無料"]</t>
+          <t>[再測 R4] GET /cron-actions 6 種 (task_replay=本人の Claude プラン枠, knowledge_organize=本人の Claude プラン枠/PC接続要, industry_extract=コスト無料, report_summary=本人の Claude プラン枠/PC接続要, daily_digest=コスト無料, weekly_burndown=コスト無料) の title・cost_label・staff・説明が S-O01「2. 何をする？」に全て一致して出る (欠け 0)。API に無い種類カード 0 件、旧ハードコード文言 0 件 (画面の「プラン枠」「無料」は API の cost_label「本人の Claude プラン枠」「コスト無料」の一部)</t>
         </is>
       </c>
     </row>
@@ -17889,19 +17889,19 @@
           <t>入力欄に文章が戻った状態になり、押し直すだけで再送できる</t>
         </is>
       </c>
-      <c r="K266" s="5" t="inlineStr">
-        <is>
-          <t>FAIL</t>
+      <c r="K266" s="4" t="inlineStr">
+        <is>
+          <t>PASS</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>apps/web/.qa/evidence/shots/journeys/J43-03-r2.png</t>
+          <t>apps/web/.qa/evidence/shots/journeys/J43-03-r4.png</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>[再測 R2] 期待: 入力欄に文章が戻り押し直しで再送 / 実測: 送信 API=POST 200 /chat/threads/3a0342c1-d6b9-467b-a1fc-81c4432c18e8/stream, POST 200 /chat/threads/3a0342c1-d6b9-467b-a1fc-81c4432c18e8/queued/consume、alert=["お使いの PC がまだ接続されていません。設定画面の「Bridge を接続」から接続すると、AI 機能を使えるようになります。"]、入力欄="" (一致=false)、DB messages 1→2、押し直し API=[]</t>
+          <t>[再測 R4] Bridge 未接続 (mode=relay bridge_online=false) で送信 → POST 200 /chat/threads/12a770f1-7dc3-41db-b12b-e7695595ac15/stream, POST 200 /chat/threads/12a770f1-7dc3-41db-b12b-e7695595ac15/queued/consume、画面 alert「お使いのパソコン (Bridge) が未接続のため AI 実行ができません。Bridge アプリを起動してから再送してください。」、入力欄に元の文章がそのまま戻る (一致)、DB の messages は 0→0 件 (応答なしの user 発言を残さない = GAP-310)。送信ボタンは押せる状態 (disabled=false) で、押し直すと再送 (200 /chat/threads/12a770f1-7dc3-41db-b12b-e7695595ac15/stream, 200 /chat/threads/12a770f1-7dc3-41db-b12b-e7695595ac15/queued/consume) され、再び未接続の案内・入力欄に文章が残り DB も 0 件のまま</t>
         </is>
       </c>
     </row>
@@ -21404,11 +21404,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>45%</t>
         </is>
       </c>
     </row>
@@ -21419,11 +21419,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>7%</t>
+          <t>4%</t>
         </is>
       </c>
     </row>
@@ -21434,7 +21434,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
